--- a/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.03713499344692005</v>
+        <v>0.0124070772470885</v>
       </c>
       <c r="H2">
-        <v>0.03591087811271297</v>
+        <v>0.01112118968926701</v>
       </c>
       <c r="I2">
-        <v>-0.05307994757536042</v>
+        <v>-0.05997129491810362</v>
       </c>
       <c r="J2">
-        <v>-0.05307994757536042</v>
+        <v>-0.05997129491810362</v>
       </c>
       <c r="K2">
-        <v>-73.90000000000001</v>
+        <v>-104.4</v>
       </c>
       <c r="L2">
-        <v>-0.09685452162516384</v>
+        <v>-0.09070720340308402</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>514.2</v>
+        <v>311.158</v>
       </c>
       <c r="V2">
-        <v>0.2412838440242129</v>
+        <v>0.3089643530930395</v>
+      </c>
+      <c r="W2">
+        <v>-3.709712859158444</v>
       </c>
       <c r="X2">
-        <v>0.07213061399612694</v>
+        <v>0.1249838875925618</v>
+      </c>
+      <c r="Y2">
+        <v>-3.834696746751006</v>
+      </c>
+      <c r="Z2">
+        <v>1.02676964064348</v>
+      </c>
+      <c r="AA2">
+        <v>-0.6858734202042377</v>
       </c>
       <c r="AB2">
-        <v>0.06073264452448788</v>
+        <v>0.1042487468587564</v>
+      </c>
+      <c r="AC2">
+        <v>-0.790122167062994</v>
       </c>
       <c r="AD2">
-        <v>707.1</v>
+        <v>773.3199999999999</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2.096608568804454</v>
       </c>
       <c r="AF2">
-        <v>707.1</v>
+        <v>775.4166085688045</v>
       </c>
       <c r="AG2">
-        <v>192.9</v>
+        <v>464.2586085688044</v>
       </c>
       <c r="AH2">
-        <v>0.2491367768303855</v>
+        <v>0.4350122769354683</v>
       </c>
       <c r="AI2">
-        <v>0.4378599294073937</v>
+        <v>0.4498776611422115</v>
       </c>
       <c r="AJ2">
-        <v>0.08300344234079172</v>
+        <v>0.3155305619344494</v>
       </c>
       <c r="AK2">
-        <v>0.1752521122921777</v>
+        <v>0.3286882927063057</v>
       </c>
       <c r="AL2">
-        <v>24.5</v>
+        <v>28.869</v>
       </c>
       <c r="AM2">
-        <v>22.07</v>
+        <v>22.209</v>
       </c>
       <c r="AN2">
-        <v>24.89788732394366</v>
+        <v>37.7321297877531</v>
       </c>
       <c r="AO2">
-        <v>-1.653061224489796</v>
+        <v>-2.386643111988639</v>
       </c>
       <c r="AP2">
-        <v>6.79225352112676</v>
+        <v>22.65228634148838</v>
       </c>
       <c r="AQ2">
-        <v>-1.835070231082918</v>
+        <v>-3.102345895808006</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.03713499344692005</v>
+        <v>0.02979833101529902</v>
       </c>
       <c r="H3">
-        <v>0.03591087811271297</v>
+        <v>0.02851182197496523</v>
       </c>
       <c r="I3">
-        <v>-0.05307994757536042</v>
+        <v>-0.03711752433936022</v>
       </c>
       <c r="J3">
-        <v>-0.05307994757536042</v>
+        <v>-0.03711752433936022</v>
       </c>
       <c r="K3">
-        <v>-73.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.09685452162516384</v>
+        <v>-0.06658553546592488</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,198 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>514.2</v>
+        <v>310.6</v>
       </c>
       <c r="V3">
-        <v>0.2412838440242129</v>
+        <v>0.3231041298241965</v>
+      </c>
+      <c r="W3">
+        <v>-0.08433337003192777</v>
       </c>
       <c r="X3">
-        <v>0.07213061399612694</v>
+        <v>0.1427139031703059</v>
+      </c>
+      <c r="Y3">
+        <v>-0.2270472732022336</v>
+      </c>
+      <c r="Z3">
+        <v>1.044678532509989</v>
+      </c>
+      <c r="AA3">
+        <v>-0.03877588085724664</v>
       </c>
       <c r="AB3">
-        <v>0.06073264452448788</v>
+        <v>0.09929048574590842</v>
+      </c>
+      <c r="AC3">
+        <v>-0.138066366603155</v>
       </c>
       <c r="AD3">
-        <v>707.1</v>
+        <v>770.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>707.1</v>
+        <v>770.3</v>
       </c>
       <c r="AG3">
-        <v>192.9</v>
+        <v>459.6999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.2491367768303855</v>
+        <v>0.4448486948486948</v>
       </c>
       <c r="AI3">
-        <v>0.4378599294073937</v>
+        <v>0.4518418582824965</v>
       </c>
       <c r="AJ3">
-        <v>0.08300344234079172</v>
+        <v>0.3235045742434904</v>
       </c>
       <c r="AK3">
-        <v>0.1752521122921777</v>
+        <v>0.3297231387175441</v>
       </c>
       <c r="AL3">
-        <v>24.5</v>
+        <v>28.6</v>
       </c>
       <c r="AM3">
-        <v>22.07</v>
+        <v>21.94</v>
       </c>
       <c r="AN3">
-        <v>24.89788732394366</v>
+        <v>17.87238979118329</v>
       </c>
       <c r="AO3">
-        <v>-1.653061224489796</v>
+        <v>-1.493006993006993</v>
       </c>
       <c r="AP3">
-        <v>6.79225352112676</v>
+        <v>10.66589327146172</v>
       </c>
       <c r="AQ3">
-        <v>-1.835070231082918</v>
+        <v>-1.946216955332726</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Astrocast SA (OB:ASTRO)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-35.97122302158273</v>
+      </c>
+      <c r="H4">
+        <v>-35.97122302158273</v>
+      </c>
+      <c r="I4">
+        <v>-47.34590236287929</v>
+      </c>
+      <c r="J4">
+        <v>-47.34590236287929</v>
+      </c>
+      <c r="K4">
+        <v>-27.8</v>
+      </c>
+      <c r="L4">
+        <v>-50</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="V4">
+        <v>0.01218340611353712</v>
+      </c>
+      <c r="W4">
+        <v>-7.33509234828496</v>
+      </c>
+      <c r="X4">
+        <v>0.1072538720148177</v>
+      </c>
+      <c r="Y4">
+        <v>-7.442346220299778</v>
+      </c>
+      <c r="Z4">
+        <v>0.02815388223746942</v>
+      </c>
+      <c r="AA4">
+        <v>-1.332970959551229</v>
+      </c>
+      <c r="AB4">
+        <v>0.1092070079716044</v>
+      </c>
+      <c r="AC4">
+        <v>-1.442177967522833</v>
+      </c>
+      <c r="AD4">
+        <v>3.02</v>
+      </c>
+      <c r="AE4">
+        <v>2.096608568804454</v>
+      </c>
+      <c r="AF4">
+        <v>5.116608568804454</v>
+      </c>
+      <c r="AG4">
+        <v>4.558608568804455</v>
+      </c>
+      <c r="AH4">
+        <v>0.1004899719880262</v>
+      </c>
+      <c r="AI4">
+        <v>0.2719198069139378</v>
+      </c>
+      <c r="AJ4">
+        <v>0.09052292544135875</v>
+      </c>
+      <c r="AK4">
+        <v>0.2496690014261555</v>
+      </c>
+      <c r="AL4">
+        <v>0.269</v>
+      </c>
+      <c r="AM4">
+        <v>0.269</v>
+      </c>
+      <c r="AN4">
+        <v>-0.1335987613359876</v>
+      </c>
+      <c r="AO4">
+        <v>-97.39776951672862</v>
+      </c>
+      <c r="AP4">
+        <v>-0.2016637278834088</v>
+      </c>
+      <c r="AQ4">
+        <v>-97.39776951672862</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="swx_aero" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.0124070772470885</v>
+        <v>0.03930659996930704</v>
       </c>
       <c r="H2">
-        <v>0.01112118968926701</v>
+        <v>0.03650504964752056</v>
       </c>
       <c r="I2">
-        <v>-0.05997129491810362</v>
+        <v>-0.006110959801239524</v>
       </c>
       <c r="J2">
-        <v>-0.05997129491810362</v>
+        <v>-0.006110959801239524</v>
       </c>
       <c r="K2">
-        <v>-104.4</v>
+        <v>-33.59999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.09070720340308402</v>
+        <v>-0.02194221231049536</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +629,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>311.158</v>
+        <v>329.095</v>
       </c>
       <c r="V2">
-        <v>0.3089643530930395</v>
+        <v>0.2522399957077926</v>
       </c>
       <c r="W2">
-        <v>-3.709712859158444</v>
+        <v>-0.4313669803155502</v>
       </c>
       <c r="X2">
-        <v>0.1249838875925618</v>
+        <v>0.1342934614046997</v>
       </c>
       <c r="Y2">
-        <v>-3.834696746751006</v>
+        <v>-0.5656604417202499</v>
       </c>
       <c r="Z2">
-        <v>1.02676964064348</v>
+        <v>1.079556357626491</v>
       </c>
       <c r="AA2">
-        <v>-0.6858734202042377</v>
+        <v>-0.4910612383641623</v>
       </c>
       <c r="AB2">
-        <v>0.1042487468587564</v>
+        <v>0.1015046584756229</v>
       </c>
       <c r="AC2">
-        <v>-0.790122167062994</v>
+        <v>-0.5925658968397851</v>
       </c>
       <c r="AD2">
-        <v>773.3199999999999</v>
+        <v>718.27</v>
       </c>
       <c r="AE2">
-        <v>2.096608568804454</v>
+        <v>2.388410944195384</v>
       </c>
       <c r="AF2">
-        <v>775.4166085688045</v>
+        <v>720.6584109441955</v>
       </c>
       <c r="AG2">
-        <v>464.2586085688044</v>
+        <v>391.5634109441955</v>
       </c>
       <c r="AH2">
-        <v>0.4350122769354683</v>
+        <v>0.3558194763182658</v>
       </c>
       <c r="AI2">
-        <v>0.4498776611422115</v>
+        <v>0.419099920279468</v>
       </c>
       <c r="AJ2">
-        <v>0.3155305619344494</v>
+        <v>0.2308401612741561</v>
       </c>
       <c r="AK2">
-        <v>0.3286882927063057</v>
+        <v>0.2816104617147275</v>
       </c>
       <c r="AL2">
-        <v>28.869</v>
+        <v>43.317</v>
       </c>
       <c r="AM2">
-        <v>22.209</v>
+        <v>33.117</v>
       </c>
       <c r="AN2">
-        <v>37.7321297877531</v>
+        <v>7.188450760608487</v>
       </c>
       <c r="AO2">
-        <v>-2.386643111988639</v>
+        <v>-0.2123877461504721</v>
       </c>
       <c r="AP2">
-        <v>22.65228634148838</v>
+        <v>3.918769124741748</v>
       </c>
       <c r="AQ2">
-        <v>-3.102345895808006</v>
+        <v>-0.2778029410876589</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02979833101529902</v>
+        <v>0.05048993990070552</v>
       </c>
       <c r="H3">
-        <v>0.02851182197496523</v>
+        <v>0.04768748366866998</v>
       </c>
       <c r="I3">
-        <v>-0.03711752433936022</v>
+        <v>0.008688267572511106</v>
       </c>
       <c r="J3">
-        <v>-0.03711752433936022</v>
+        <v>0.008688267572511106</v>
       </c>
       <c r="K3">
-        <v>-76.59999999999999</v>
+        <v>-10.7</v>
       </c>
       <c r="L3">
-        <v>-0.06658553546592488</v>
+        <v>-0.006989809250065325</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +754,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>310.6</v>
+        <v>328.9</v>
       </c>
       <c r="V3">
-        <v>0.3231041298241965</v>
+        <v>0.253</v>
       </c>
       <c r="W3">
-        <v>-0.08433337003192777</v>
+        <v>-0.01143284538946469</v>
       </c>
       <c r="X3">
-        <v>0.1427139031703059</v>
+        <v>0.09884679736047158</v>
       </c>
       <c r="Y3">
-        <v>-0.2270472732022336</v>
+        <v>-0.1102796427499363</v>
       </c>
       <c r="Z3">
-        <v>1.044678532509989</v>
+        <v>1.096875895672112</v>
       </c>
       <c r="AA3">
-        <v>-0.03877588085724664</v>
+        <v>0.00952995127543709</v>
       </c>
       <c r="AB3">
-        <v>0.09929048574590842</v>
+        <v>0.07929675148392563</v>
       </c>
       <c r="AC3">
-        <v>-0.138066366603155</v>
+        <v>-0.06976680020848855</v>
       </c>
       <c r="AD3">
-        <v>770.3</v>
+        <v>708.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>770.3</v>
+        <v>708.6</v>
       </c>
       <c r="AG3">
-        <v>459.6999999999999</v>
+        <v>379.7</v>
       </c>
       <c r="AH3">
-        <v>0.4448486948486948</v>
+        <v>0.3527830329582795</v>
       </c>
       <c r="AI3">
-        <v>0.4518418582824965</v>
+        <v>0.4158938842587158</v>
       </c>
       <c r="AJ3">
-        <v>0.3235045742434904</v>
+        <v>0.2260522712389117</v>
       </c>
       <c r="AK3">
-        <v>0.3297231387175441</v>
+        <v>0.27616553931195</v>
       </c>
       <c r="AL3">
-        <v>28.6</v>
+        <v>42.8</v>
       </c>
       <c r="AM3">
-        <v>21.94</v>
+        <v>32.59999999999999</v>
       </c>
       <c r="AN3">
-        <v>17.87238979118329</v>
+        <v>6.071979434447301</v>
       </c>
       <c r="AO3">
-        <v>-1.493006993006993</v>
+        <v>0.3107476635514019</v>
       </c>
       <c r="AP3">
-        <v>10.66589327146172</v>
+        <v>3.253641816623822</v>
       </c>
       <c r="AQ3">
-        <v>-1.946216955332726</v>
+        <v>0.4079754601226995</v>
       </c>
     </row>
     <row r="4">
@@ -838,22 +840,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-35.97122302158273</v>
+        <v>-34.54545454545455</v>
       </c>
       <c r="H4">
-        <v>-35.97122302158273</v>
+        <v>-34.54545454545455</v>
       </c>
       <c r="I4">
-        <v>-47.34590236287929</v>
+        <v>-45.77309533098803</v>
       </c>
       <c r="J4">
-        <v>-47.34590236287929</v>
+        <v>-45.77309533098803</v>
       </c>
       <c r="K4">
-        <v>-27.8</v>
+        <v>-22.9</v>
       </c>
       <c r="L4">
-        <v>-50</v>
+        <v>-46.26262626262626</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,73 +879,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.5580000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="V4">
-        <v>0.01218340611353712</v>
+        <v>0.04157782515991471</v>
       </c>
       <c r="W4">
-        <v>-7.33509234828496</v>
+        <v>-0.8513011152416357</v>
       </c>
       <c r="X4">
-        <v>0.1072538720148177</v>
+        <v>0.1697401254489279</v>
       </c>
       <c r="Y4">
-        <v>-7.442346220299778</v>
+        <v>-1.021041240690564</v>
       </c>
       <c r="Z4">
-        <v>0.02815388223746942</v>
+        <v>0.02166452630815248</v>
       </c>
       <c r="AA4">
-        <v>-1.332970959551229</v>
+        <v>-0.9916524280037616</v>
       </c>
       <c r="AB4">
-        <v>0.1092070079716044</v>
+        <v>0.1237125654673201</v>
       </c>
       <c r="AC4">
-        <v>-1.442177967522833</v>
+        <v>-1.115364993471082</v>
       </c>
       <c r="AD4">
-        <v>3.02</v>
+        <v>9.67</v>
       </c>
       <c r="AE4">
-        <v>2.096608568804454</v>
+        <v>2.388410944195384</v>
       </c>
       <c r="AF4">
-        <v>5.116608568804454</v>
+        <v>12.05841094419538</v>
       </c>
       <c r="AG4">
-        <v>4.558608568804455</v>
+        <v>11.86341094419538</v>
       </c>
       <c r="AH4">
-        <v>0.1004899719880262</v>
+        <v>0.7199734341588121</v>
       </c>
       <c r="AI4">
-        <v>0.2719198069139378</v>
+        <v>0.7661771564455653</v>
       </c>
       <c r="AJ4">
-        <v>0.09052292544135875</v>
+        <v>0.7166747073572414</v>
       </c>
       <c r="AK4">
-        <v>0.2496690014261555</v>
+        <v>0.7632437298857958</v>
       </c>
       <c r="AL4">
-        <v>0.269</v>
+        <v>0.517</v>
       </c>
       <c r="AM4">
-        <v>0.269</v>
+        <v>0.517</v>
       </c>
       <c r="AN4">
-        <v>-0.1335987613359876</v>
+        <v>-0.5762812872467222</v>
       </c>
       <c r="AO4">
-        <v>-97.39776951672862</v>
+        <v>-43.52030947775629</v>
       </c>
       <c r="AP4">
-        <v>-0.2016637278834088</v>
+        <v>-0.7069970765313101</v>
       </c>
       <c r="AQ4">
-        <v>-97.39776951672862</v>
+        <v>-43.52030947775629</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Montana Aerospace AG (SWX:AERO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SWX:AERO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.0257009345794391</v>
+      </c>
+      <c r="F2">
+        <v>10.471711089187</v>
+      </c>
+      <c r="G2">
+        <v>6.0719794344473</v>
+      </c>
+      <c r="H2">
+        <v>2.06539845758355</v>
+      </c>
+      <c r="I2">
+        <v>0.352783032958279</v>
+      </c>
+      <c r="J2">
+        <v>0.12</v>
+      </c>
+      <c r="K2">
+        <v>1300</v>
+      </c>
+      <c r="L2">
+        <v>1776.04355611956</v>
+      </c>
+      <c r="M2">
+        <v>1679.7</v>
+      </c>
+      <c r="N2">
+        <v>1688.17555611956</v>
+      </c>
+      <c r="O2">
+        <v>708.6</v>
+      </c>
+      <c r="P2">
+        <v>241.032</v>
+      </c>
+      <c r="Q2">
+        <v>0.07929675148392561</v>
+      </c>
+      <c r="R2">
+        <v>0.0790934358461545</v>
+      </c>
+      <c r="S2">
+        <v>0.04343017</v>
+      </c>
+      <c r="T2">
+        <v>0.0391132</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0988467973604716</v>
+      </c>
+      <c r="X2">
+        <v>0.084545286188812</v>
+      </c>
+      <c r="Y2">
+        <v>1.30536516001025</v>
+      </c>
+      <c r="Z2">
+        <v>0.994462743235043</v>
+      </c>
+      <c r="AA2">
+        <v>708.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>-0.02570093457943912</v>
+      </c>
+      <c r="AD2">
+        <v>708.6</v>
+      </c>
+      <c r="AE2">
+        <v>42.8</v>
+      </c>
+      <c r="AF2">
+        <v>117.8</v>
+      </c>
+      <c r="AG2">
+        <v>116.7</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1300</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.146</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>76.70100000000002</v>
+      </c>
+      <c r="AR2">
+        <v>42.8</v>
+      </c>
+      <c r="AS2">
+        <v>708.6</v>
+      </c>
+      <c r="AT2">
+        <v>328.9</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07977371126756222</v>
+      </c>
+      <c r="C2">
+        <v>1989.047234976036</v>
+      </c>
+      <c r="D2">
+        <v>1660.147234976036</v>
+      </c>
+      <c r="E2">
+        <v>-708.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>328.9</v>
+      </c>
+      <c r="H2">
+        <v>1300</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>233.4</v>
+      </c>
+      <c r="K2">
+        <v>117.8</v>
+      </c>
+      <c r="L2">
+        <v>115.6</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>115.6</v>
+      </c>
+      <c r="O2">
+        <v>16.8776</v>
+      </c>
+      <c r="P2">
+        <v>98.72240000000001</v>
+      </c>
+      <c r="Q2">
+        <v>216.5224</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07977371126756222</v>
+      </c>
+      <c r="T2">
+        <v>0.8907328536426569</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.146</v>
+      </c>
+      <c r="W2">
+        <v>0.0381738</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07970762764911159</v>
+      </c>
+      <c r="C3">
+        <v>1971.643095126644</v>
+      </c>
+      <c r="D3">
+        <v>1662.829095126644</v>
+      </c>
+      <c r="E3">
+        <v>-688.514</v>
+      </c>
+      <c r="F3">
+        <v>20.086</v>
+      </c>
+      <c r="G3">
+        <v>328.9</v>
+      </c>
+      <c r="H3">
+        <v>1300</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>233.4</v>
+      </c>
+      <c r="K3">
+        <v>117.8</v>
+      </c>
+      <c r="L3">
+        <v>115.6</v>
+      </c>
+      <c r="M3">
+        <v>0.8978442</v>
+      </c>
+      <c r="N3">
+        <v>114.7021558</v>
+      </c>
+      <c r="O3">
+        <v>16.7465147468</v>
+      </c>
+      <c r="P3">
+        <v>97.95564105320001</v>
+      </c>
+      <c r="Q3">
+        <v>215.7556410532</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08012716126172886</v>
+      </c>
+      <c r="T3">
+        <v>0.8984165491680187</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.146</v>
+      </c>
+      <c r="W3">
+        <v>0.0381738</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>128.7528504388624</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07964154403066093</v>
+      </c>
+      <c r="C4">
+        <v>1954.247634039386</v>
+      </c>
+      <c r="D4">
+        <v>1665.519634039387</v>
+      </c>
+      <c r="E4">
+        <v>-668.428</v>
+      </c>
+      <c r="F4">
+        <v>40.172</v>
+      </c>
+      <c r="G4">
+        <v>328.9</v>
+      </c>
+      <c r="H4">
+        <v>1300</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>233.4</v>
+      </c>
+      <c r="K4">
+        <v>117.8</v>
+      </c>
+      <c r="L4">
+        <v>115.6</v>
+      </c>
+      <c r="M4">
+        <v>1.7956884</v>
+      </c>
+      <c r="N4">
+        <v>113.8043116</v>
+      </c>
+      <c r="O4">
+        <v>16.6154294936</v>
+      </c>
+      <c r="P4">
+        <v>97.1888821064</v>
+      </c>
+      <c r="Q4">
+        <v>214.9888821064</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08048782452108258</v>
+      </c>
+      <c r="T4">
+        <v>0.906257054806143</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.146</v>
+      </c>
+      <c r="W4">
+        <v>0.0381738</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>64.37642521943117</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07957546041221029</v>
+      </c>
+      <c r="C5">
+        <v>1936.860893910525</v>
+      </c>
+      <c r="D5">
+        <v>1668.218893910526</v>
+      </c>
+      <c r="E5">
+        <v>-648.342</v>
+      </c>
+      <c r="F5">
+        <v>60.258</v>
+      </c>
+      <c r="G5">
+        <v>328.9</v>
+      </c>
+      <c r="H5">
+        <v>1300</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>233.4</v>
+      </c>
+      <c r="K5">
+        <v>117.8</v>
+      </c>
+      <c r="L5">
+        <v>115.6</v>
+      </c>
+      <c r="M5">
+        <v>2.6935326</v>
+      </c>
+      <c r="N5">
+        <v>112.9064674</v>
+      </c>
+      <c r="O5">
+        <v>16.4843442404</v>
+      </c>
+      <c r="P5">
+        <v>96.42212315960001</v>
+      </c>
+      <c r="Q5">
+        <v>214.2221231596</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08085592413629927</v>
+      </c>
+      <c r="T5">
+        <v>0.9142592203543319</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.146</v>
+      </c>
+      <c r="W5">
+        <v>0.0381738</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>42.91761681295412</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07950937679375965</v>
+      </c>
+      <c r="C6">
+        <v>1919.482917210313</v>
+      </c>
+      <c r="D6">
+        <v>1670.926917210313</v>
+      </c>
+      <c r="E6">
+        <v>-628.2560000000001</v>
+      </c>
+      <c r="F6">
+        <v>80.34399999999999</v>
+      </c>
+      <c r="G6">
+        <v>328.9</v>
+      </c>
+      <c r="H6">
+        <v>1300</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>233.4</v>
+      </c>
+      <c r="K6">
+        <v>117.8</v>
+      </c>
+      <c r="L6">
+        <v>115.6</v>
+      </c>
+      <c r="M6">
+        <v>3.5913768</v>
+      </c>
+      <c r="N6">
+        <v>112.0086232</v>
+      </c>
+      <c r="O6">
+        <v>16.3532589872</v>
+      </c>
+      <c r="P6">
+        <v>95.65536421280001</v>
+      </c>
+      <c r="Q6">
+        <v>213.4553642128</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08123169249349964</v>
+      </c>
+      <c r="T6">
+        <v>0.9224280976847747</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.146</v>
+      </c>
+      <c r="W6">
+        <v>0.0381738</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>32.18821260971558</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07944329317530902</v>
+      </c>
+      <c r="C7">
+        <v>1902.113746685217</v>
+      </c>
+      <c r="D7">
+        <v>1673.643746685217</v>
+      </c>
+      <c r="E7">
+        <v>-608.1700000000001</v>
+      </c>
+      <c r="F7">
+        <v>100.43</v>
+      </c>
+      <c r="G7">
+        <v>328.9</v>
+      </c>
+      <c r="H7">
+        <v>1300</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>233.4</v>
+      </c>
+      <c r="K7">
+        <v>117.8</v>
+      </c>
+      <c r="L7">
+        <v>115.6</v>
+      </c>
+      <c r="M7">
+        <v>4.489221000000001</v>
+      </c>
+      <c r="N7">
+        <v>111.110779</v>
+      </c>
+      <c r="O7">
+        <v>16.222173734</v>
+      </c>
+      <c r="P7">
+        <v>94.88860526600001</v>
+      </c>
+      <c r="Q7">
+        <v>212.688605266</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08161537176348317</v>
+      </c>
+      <c r="T7">
+        <v>0.9307689513800689</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.146</v>
+      </c>
+      <c r="W7">
+        <v>0.0381738</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>25.75057008777247</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07937720955685836</v>
+      </c>
+      <c r="C8">
+        <v>1884.753425360171</v>
+      </c>
+      <c r="D8">
+        <v>1676.369425360171</v>
+      </c>
+      <c r="E8">
+        <v>-588.0840000000001</v>
+      </c>
+      <c r="F8">
+        <v>120.516</v>
+      </c>
+      <c r="G8">
+        <v>328.9</v>
+      </c>
+      <c r="H8">
+        <v>1300</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>233.4</v>
+      </c>
+      <c r="K8">
+        <v>117.8</v>
+      </c>
+      <c r="L8">
+        <v>115.6</v>
+      </c>
+      <c r="M8">
+        <v>5.3870652</v>
+      </c>
+      <c r="N8">
+        <v>110.2129348</v>
+      </c>
+      <c r="O8">
+        <v>16.0910884808</v>
+      </c>
+      <c r="P8">
+        <v>94.12184631920002</v>
+      </c>
+      <c r="Q8">
+        <v>211.9218463192</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08200721442218975</v>
+      </c>
+      <c r="T8">
+        <v>0.9392872700476035</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.146</v>
+      </c>
+      <c r="W8">
+        <v>0.0381738</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>21.45880840647706</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07931112593840774</v>
+      </c>
+      <c r="C9">
+        <v>1867.401996540844</v>
+      </c>
+      <c r="D9">
+        <v>1679.103996540844</v>
+      </c>
+      <c r="E9">
+        <v>-567.998</v>
+      </c>
+      <c r="F9">
+        <v>140.602</v>
+      </c>
+      <c r="G9">
+        <v>328.9</v>
+      </c>
+      <c r="H9">
+        <v>1300</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>233.4</v>
+      </c>
+      <c r="K9">
+        <v>117.8</v>
+      </c>
+      <c r="L9">
+        <v>115.6</v>
+      </c>
+      <c r="M9">
+        <v>6.284909400000001</v>
+      </c>
+      <c r="N9">
+        <v>109.3150906</v>
+      </c>
+      <c r="O9">
+        <v>15.9600032276</v>
+      </c>
+      <c r="P9">
+        <v>93.35508737240001</v>
+      </c>
+      <c r="Q9">
+        <v>211.1550873724</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.0824074838047395</v>
+      </c>
+      <c r="T9">
+        <v>0.9479887783639022</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.146</v>
+      </c>
+      <c r="W9">
+        <v>0.0381738</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>18.3932643484089</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07924504231995709</v>
+      </c>
+      <c r="C10">
+        <v>1850.05950381594</v>
+      </c>
+      <c r="D10">
+        <v>1681.84750381594</v>
+      </c>
+      <c r="E10">
+        <v>-547.912</v>
+      </c>
+      <c r="F10">
+        <v>160.688</v>
+      </c>
+      <c r="G10">
+        <v>328.9</v>
+      </c>
+      <c r="H10">
+        <v>1300</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>233.4</v>
+      </c>
+      <c r="K10">
+        <v>117.8</v>
+      </c>
+      <c r="L10">
+        <v>115.6</v>
+      </c>
+      <c r="M10">
+        <v>7.1827536</v>
+      </c>
+      <c r="N10">
+        <v>108.4172464</v>
+      </c>
+      <c r="O10">
+        <v>15.8289179744</v>
+      </c>
+      <c r="P10">
+        <v>92.58832842560001</v>
+      </c>
+      <c r="Q10">
+        <v>210.3883284256</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08281645469560553</v>
+      </c>
+      <c r="T10">
+        <v>0.956879449904468</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.146</v>
+      </c>
+      <c r="W10">
+        <v>0.0381738</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.0941063048578</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07917895870150646</v>
+      </c>
+      <c r="C11">
+        <v>1832.725991059504</v>
+      </c>
+      <c r="D11">
+        <v>1684.599991059504</v>
+      </c>
+      <c r="E11">
+        <v>-527.826</v>
+      </c>
+      <c r="F11">
+        <v>180.774</v>
+      </c>
+      <c r="G11">
+        <v>328.9</v>
+      </c>
+      <c r="H11">
+        <v>1300</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>233.4</v>
+      </c>
+      <c r="K11">
+        <v>117.8</v>
+      </c>
+      <c r="L11">
+        <v>115.6</v>
+      </c>
+      <c r="M11">
+        <v>8.0805978</v>
+      </c>
+      <c r="N11">
+        <v>107.5194022</v>
+      </c>
+      <c r="O11">
+        <v>15.6978327212</v>
+      </c>
+      <c r="P11">
+        <v>91.8215694788</v>
+      </c>
+      <c r="Q11">
+        <v>209.6215694788</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0832344139576994</v>
+      </c>
+      <c r="T11">
+        <v>0.965965520819552</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.146</v>
+      </c>
+      <c r="W11">
+        <v>0.0381738</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.3058722709847</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0791128750830558</v>
+      </c>
+      <c r="C12">
+        <v>1815.401502433273</v>
+      </c>
+      <c r="D12">
+        <v>1687.361502433273</v>
+      </c>
+      <c r="E12">
+        <v>-507.74</v>
+      </c>
+      <c r="F12">
+        <v>200.86</v>
+      </c>
+      <c r="G12">
+        <v>328.9</v>
+      </c>
+      <c r="H12">
+        <v>1300</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>233.4</v>
+      </c>
+      <c r="K12">
+        <v>117.8</v>
+      </c>
+      <c r="L12">
+        <v>115.6</v>
+      </c>
+      <c r="M12">
+        <v>8.978442000000001</v>
+      </c>
+      <c r="N12">
+        <v>106.621558</v>
+      </c>
+      <c r="O12">
+        <v>15.566747468</v>
+      </c>
+      <c r="P12">
+        <v>91.054810532</v>
+      </c>
+      <c r="Q12">
+        <v>208.854810532</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08366166120339534</v>
+      </c>
+      <c r="T12">
+        <v>0.9752535044216378</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.146</v>
+      </c>
+      <c r="W12">
+        <v>0.0381738</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>12.87528504388623</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07915012546460516</v>
+      </c>
+      <c r="C13">
+        <v>1793.757766018488</v>
+      </c>
+      <c r="D13">
+        <v>1685.803766018488</v>
+      </c>
+      <c r="E13">
+        <v>-487.654</v>
+      </c>
+      <c r="F13">
+        <v>220.946</v>
+      </c>
+      <c r="G13">
+        <v>328.9</v>
+      </c>
+      <c r="H13">
+        <v>1300</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>233.4</v>
+      </c>
+      <c r="K13">
+        <v>117.8</v>
+      </c>
+      <c r="L13">
+        <v>115.6</v>
+      </c>
+      <c r="M13">
+        <v>10.1193268</v>
+      </c>
+      <c r="N13">
+        <v>105.4806732</v>
+      </c>
+      <c r="O13">
+        <v>15.4001782872</v>
+      </c>
+      <c r="P13">
+        <v>90.08049491280001</v>
+      </c>
+      <c r="Q13">
+        <v>207.8804949128</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08409850951079231</v>
+      </c>
+      <c r="T13">
+        <v>0.9847502067563548</v>
+      </c>
+      <c r="U13">
+        <v>0.0458</v>
+      </c>
+      <c r="V13">
+        <v>0.146</v>
+      </c>
+      <c r="W13">
+        <v>0.0391132</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.42368482456758</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07909343584615453</v>
+      </c>
+      <c r="C14">
+        <v>1776.043556119564</v>
+      </c>
+      <c r="D14">
+        <v>1688.175556119564</v>
+      </c>
+      <c r="E14">
+        <v>-467.568</v>
+      </c>
+      <c r="F14">
+        <v>241.032</v>
+      </c>
+      <c r="G14">
+        <v>328.9</v>
+      </c>
+      <c r="H14">
+        <v>1300</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>233.4</v>
+      </c>
+      <c r="K14">
+        <v>117.8</v>
+      </c>
+      <c r="L14">
+        <v>115.6</v>
+      </c>
+      <c r="M14">
+        <v>11.0392656</v>
+      </c>
+      <c r="N14">
+        <v>104.5607344</v>
+      </c>
+      <c r="O14">
+        <v>15.2658672224</v>
+      </c>
+      <c r="P14">
+        <v>89.29486717760001</v>
+      </c>
+      <c r="Q14">
+        <v>207.0948671776</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08454528618881196</v>
+      </c>
+      <c r="T14">
+        <v>0.9944627432350426</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.146</v>
+      </c>
+      <c r="W14">
+        <v>0.0391132</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.47171108918695</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07928099022770388</v>
+      </c>
+      <c r="C15">
+        <v>1748.13599047619</v>
+      </c>
+      <c r="D15">
+        <v>1680.35399047619</v>
+      </c>
+      <c r="E15">
+        <v>-447.482</v>
+      </c>
+      <c r="F15">
+        <v>261.118</v>
+      </c>
+      <c r="G15">
+        <v>328.9</v>
+      </c>
+      <c r="H15">
+        <v>1300</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>233.4</v>
+      </c>
+      <c r="K15">
+        <v>117.8</v>
+      </c>
+      <c r="L15">
+        <v>115.6</v>
+      </c>
+      <c r="M15">
+        <v>12.533664</v>
+      </c>
+      <c r="N15">
+        <v>103.066336</v>
+      </c>
+      <c r="O15">
+        <v>15.047685056</v>
+      </c>
+      <c r="P15">
+        <v>88.018650944</v>
+      </c>
+      <c r="Q15">
+        <v>205.818650944</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08500233359506194</v>
+      </c>
+      <c r="T15">
+        <v>1.00439855641439</v>
+      </c>
+      <c r="U15">
+        <v>0.048</v>
+      </c>
+      <c r="V15">
+        <v>0.146</v>
+      </c>
+      <c r="W15">
+        <v>0.040992</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.223160920860812</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07924308860925325</v>
+      </c>
+      <c r="C16">
+        <v>1729.624749922096</v>
+      </c>
+      <c r="D16">
+        <v>1681.928749922096</v>
+      </c>
+      <c r="E16">
+        <v>-427.396</v>
+      </c>
+      <c r="F16">
+        <v>281.204</v>
+      </c>
+      <c r="G16">
+        <v>328.9</v>
+      </c>
+      <c r="H16">
+        <v>1300</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>233.4</v>
+      </c>
+      <c r="K16">
+        <v>117.8</v>
+      </c>
+      <c r="L16">
+        <v>115.6</v>
+      </c>
+      <c r="M16">
+        <v>13.497792</v>
+      </c>
+      <c r="N16">
+        <v>102.102208</v>
+      </c>
+      <c r="O16">
+        <v>14.906922368</v>
+      </c>
+      <c r="P16">
+        <v>87.19528563200001</v>
+      </c>
+      <c r="Q16">
+        <v>204.995285632</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08547001001075959</v>
+      </c>
+      <c r="T16">
+        <v>1.014565435016513</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.146</v>
+      </c>
+      <c r="W16">
+        <v>0.040992</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.564363712227896</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0792051869908026</v>
+      </c>
+      <c r="C17">
+        <v>1711.116463737781</v>
+      </c>
+      <c r="D17">
+        <v>1683.506463737781</v>
+      </c>
+      <c r="E17">
+        <v>-407.3100000000001</v>
+      </c>
+      <c r="F17">
+        <v>301.29</v>
+      </c>
+      <c r="G17">
+        <v>328.9</v>
+      </c>
+      <c r="H17">
+        <v>1300</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>233.4</v>
+      </c>
+      <c r="K17">
+        <v>117.8</v>
+      </c>
+      <c r="L17">
+        <v>115.6</v>
+      </c>
+      <c r="M17">
+        <v>14.46192</v>
+      </c>
+      <c r="N17">
+        <v>101.13808</v>
+      </c>
+      <c r="O17">
+        <v>14.76615968</v>
+      </c>
+      <c r="P17">
+        <v>86.37192032</v>
+      </c>
+      <c r="Q17">
+        <v>204.17192032</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08594869057741483</v>
+      </c>
+      <c r="T17">
+        <v>1.024971534291627</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.146</v>
+      </c>
+      <c r="W17">
+        <v>0.040992</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>7.993406131412704</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07937224537235195</v>
+      </c>
+      <c r="C18">
+        <v>1684.098536195226</v>
+      </c>
+      <c r="D18">
+        <v>1676.574536195226</v>
+      </c>
+      <c r="E18">
+        <v>-387.224</v>
+      </c>
+      <c r="F18">
+        <v>321.376</v>
+      </c>
+      <c r="G18">
+        <v>328.9</v>
+      </c>
+      <c r="H18">
+        <v>1300</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>233.4</v>
+      </c>
+      <c r="K18">
+        <v>117.8</v>
+      </c>
+      <c r="L18">
+        <v>115.6</v>
+      </c>
+      <c r="M18">
+        <v>15.908112</v>
+      </c>
+      <c r="N18">
+        <v>99.69188800000001</v>
+      </c>
+      <c r="O18">
+        <v>14.555015648</v>
+      </c>
+      <c r="P18">
+        <v>85.13687235200001</v>
+      </c>
+      <c r="Q18">
+        <v>202.936872352</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08643876830041899</v>
+      </c>
+      <c r="T18">
+        <v>1.035625397835196</v>
+      </c>
+      <c r="U18">
+        <v>0.0495</v>
+      </c>
+      <c r="V18">
+        <v>0.146</v>
+      </c>
+      <c r="W18">
+        <v>0.042273</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.266732846738821</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07934715375390132</v>
+      </c>
+      <c r="C19">
+        <v>1665.050043508849</v>
+      </c>
+      <c r="D19">
+        <v>1677.612043508849</v>
+      </c>
+      <c r="E19">
+        <v>-367.138</v>
+      </c>
+      <c r="F19">
+        <v>341.462</v>
+      </c>
+      <c r="G19">
+        <v>328.9</v>
+      </c>
+      <c r="H19">
+        <v>1300</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>233.4</v>
+      </c>
+      <c r="K19">
+        <v>117.8</v>
+      </c>
+      <c r="L19">
+        <v>115.6</v>
+      </c>
+      <c r="M19">
+        <v>16.902369</v>
+      </c>
+      <c r="N19">
+        <v>98.697631</v>
+      </c>
+      <c r="O19">
+        <v>14.409854126</v>
+      </c>
+      <c r="P19">
+        <v>84.287776874</v>
+      </c>
+      <c r="Q19">
+        <v>202.087776874</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08694065512518231</v>
+      </c>
+      <c r="T19">
+        <v>1.046535980982224</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.146</v>
+      </c>
+      <c r="W19">
+        <v>0.042273</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.839277973401243</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07932206213545068</v>
+      </c>
+      <c r="C20">
+        <v>1646.002835689839</v>
+      </c>
+      <c r="D20">
+        <v>1678.65083568984</v>
+      </c>
+      <c r="E20">
+        <v>-347.0520000000001</v>
+      </c>
+      <c r="F20">
+        <v>361.5479999999999</v>
+      </c>
+      <c r="G20">
+        <v>328.9</v>
+      </c>
+      <c r="H20">
+        <v>1300</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>233.4</v>
+      </c>
+      <c r="K20">
+        <v>117.8</v>
+      </c>
+      <c r="L20">
+        <v>115.6</v>
+      </c>
+      <c r="M20">
+        <v>17.896626</v>
+      </c>
+      <c r="N20">
+        <v>97.70337400000001</v>
+      </c>
+      <c r="O20">
+        <v>14.264692604</v>
+      </c>
+      <c r="P20">
+        <v>83.43868139600001</v>
+      </c>
+      <c r="Q20">
+        <v>201.238681396</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08745478309201302</v>
+      </c>
+      <c r="T20">
+        <v>1.057712675913327</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.146</v>
+      </c>
+      <c r="W20">
+        <v>0.042273</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.459318085990065</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07952413451700005</v>
+      </c>
+      <c r="C21">
+        <v>1617.587402144331</v>
+      </c>
+      <c r="D21">
+        <v>1670.321402144331</v>
+      </c>
+      <c r="E21">
+        <v>-326.966</v>
+      </c>
+      <c r="F21">
+        <v>381.634</v>
+      </c>
+      <c r="G21">
+        <v>328.9</v>
+      </c>
+      <c r="H21">
+        <v>1300</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>233.4</v>
+      </c>
+      <c r="K21">
+        <v>117.8</v>
+      </c>
+      <c r="L21">
+        <v>115.6</v>
+      </c>
+      <c r="M21">
+        <v>19.4251706</v>
+      </c>
+      <c r="N21">
+        <v>96.17482940000001</v>
+      </c>
+      <c r="O21">
+        <v>14.0415250924</v>
+      </c>
+      <c r="P21">
+        <v>82.13330430760001</v>
+      </c>
+      <c r="Q21">
+        <v>199.9333043076</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08798160557654328</v>
+      </c>
+      <c r="T21">
+        <v>1.069165338620506</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.146</v>
+      </c>
+      <c r="W21">
+        <v>0.0434686</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.95104168608949</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07951099889854941</v>
+      </c>
+      <c r="C22">
+        <v>1598.040340151801</v>
+      </c>
+      <c r="D22">
+        <v>1670.860340151801</v>
+      </c>
+      <c r="E22">
+        <v>-306.88</v>
+      </c>
+      <c r="F22">
+        <v>401.72</v>
+      </c>
+      <c r="G22">
+        <v>328.9</v>
+      </c>
+      <c r="H22">
+        <v>1300</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>233.4</v>
+      </c>
+      <c r="K22">
+        <v>117.8</v>
+      </c>
+      <c r="L22">
+        <v>115.6</v>
+      </c>
+      <c r="M22">
+        <v>20.447548</v>
+      </c>
+      <c r="N22">
+        <v>95.15245200000001</v>
+      </c>
+      <c r="O22">
+        <v>13.892257992</v>
+      </c>
+      <c r="P22">
+        <v>81.26019400800001</v>
+      </c>
+      <c r="Q22">
+        <v>199.060194008</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08852159862318676</v>
+      </c>
+      <c r="T22">
+        <v>1.080904317895364</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.146</v>
+      </c>
+      <c r="W22">
+        <v>0.0434686</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.653489601785016</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07949786328009877</v>
+      </c>
+      <c r="C23">
+        <v>1578.493626053901</v>
+      </c>
+      <c r="D23">
+        <v>1671.399626053901</v>
+      </c>
+      <c r="E23">
+        <v>-286.794</v>
+      </c>
+      <c r="F23">
+        <v>421.806</v>
+      </c>
+      <c r="G23">
+        <v>328.9</v>
+      </c>
+      <c r="H23">
+        <v>1300</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>233.4</v>
+      </c>
+      <c r="K23">
+        <v>117.8</v>
+      </c>
+      <c r="L23">
+        <v>115.6</v>
+      </c>
+      <c r="M23">
+        <v>21.4699254</v>
+      </c>
+      <c r="N23">
+        <v>94.1300746</v>
+      </c>
+      <c r="O23">
+        <v>13.7429908916</v>
+      </c>
+      <c r="P23">
+        <v>80.3870837084</v>
+      </c>
+      <c r="Q23">
+        <v>198.1870837084</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08907526237987184</v>
+      </c>
+      <c r="T23">
+        <v>1.092940486518953</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.146</v>
+      </c>
+      <c r="W23">
+        <v>0.0434686</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.384275811223825</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07948472766164812</v>
+      </c>
+      <c r="C24">
+        <v>1558.947260187598</v>
+      </c>
+      <c r="D24">
+        <v>1671.939260187599</v>
+      </c>
+      <c r="E24">
+        <v>-266.708</v>
+      </c>
+      <c r="F24">
+        <v>441.892</v>
+      </c>
+      <c r="G24">
+        <v>328.9</v>
+      </c>
+      <c r="H24">
+        <v>1300</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>233.4</v>
+      </c>
+      <c r="K24">
+        <v>117.8</v>
+      </c>
+      <c r="L24">
+        <v>115.6</v>
+      </c>
+      <c r="M24">
+        <v>22.4923028</v>
+      </c>
+      <c r="N24">
+        <v>93.1076972</v>
+      </c>
+      <c r="O24">
+        <v>13.5937237912</v>
+      </c>
+      <c r="P24">
+        <v>79.5139734088</v>
+      </c>
+      <c r="Q24">
+        <v>197.3139734088</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08964312264313862</v>
+      </c>
+      <c r="T24">
+        <v>1.105285274850839</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.146</v>
+      </c>
+      <c r="W24">
+        <v>0.0434686</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.139536001622742</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07947159204319748</v>
+      </c>
+      <c r="C25">
+        <v>1539.401242890295</v>
+      </c>
+      <c r="D25">
+        <v>1672.479242890295</v>
+      </c>
+      <c r="E25">
+        <v>-246.622</v>
+      </c>
+      <c r="F25">
+        <v>461.978</v>
+      </c>
+      <c r="G25">
+        <v>328.9</v>
+      </c>
+      <c r="H25">
+        <v>1300</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>233.4</v>
+      </c>
+      <c r="K25">
+        <v>117.8</v>
+      </c>
+      <c r="L25">
+        <v>115.6</v>
+      </c>
+      <c r="M25">
+        <v>23.5146802</v>
+      </c>
+      <c r="N25">
+        <v>92.08531980000001</v>
+      </c>
+      <c r="O25">
+        <v>13.4444566908</v>
+      </c>
+      <c r="P25">
+        <v>78.64086310920001</v>
+      </c>
+      <c r="Q25">
+        <v>196.4408631092</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09022573252363308</v>
+      </c>
+      <c r="T25">
+        <v>1.117950707035502</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.146</v>
+      </c>
+      <c r="W25">
+        <v>0.0434686</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.916077914595666</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07945845642474683</v>
+      </c>
+      <c r="C26">
+        <v>1519.855574499832</v>
+      </c>
+      <c r="D26">
+        <v>1673.019574499831</v>
+      </c>
+      <c r="E26">
+        <v>-226.5360000000001</v>
+      </c>
+      <c r="F26">
+        <v>482.064</v>
+      </c>
+      <c r="G26">
+        <v>328.9</v>
+      </c>
+      <c r="H26">
+        <v>1300</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>233.4</v>
+      </c>
+      <c r="K26">
+        <v>117.8</v>
+      </c>
+      <c r="L26">
+        <v>115.6</v>
+      </c>
+      <c r="M26">
+        <v>24.5370576</v>
+      </c>
+      <c r="N26">
+        <v>91.06294240000001</v>
+      </c>
+      <c r="O26">
+        <v>13.2951895904</v>
+      </c>
+      <c r="P26">
+        <v>77.76775280960001</v>
+      </c>
+      <c r="Q26">
+        <v>195.5677528096</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09082367424308793</v>
+      </c>
+      <c r="T26">
+        <v>1.130949440067129</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.146</v>
+      </c>
+      <c r="W26">
+        <v>0.0434686</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.711241334820848</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.0794453208062962</v>
+      </c>
+      <c r="C27">
+        <v>1500.310255354481</v>
+      </c>
+      <c r="D27">
+        <v>1673.560255354482</v>
+      </c>
+      <c r="E27">
+        <v>-206.45</v>
+      </c>
+      <c r="F27">
+        <v>502.15</v>
+      </c>
+      <c r="G27">
+        <v>328.9</v>
+      </c>
+      <c r="H27">
+        <v>1300</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>233.4</v>
+      </c>
+      <c r="K27">
+        <v>117.8</v>
+      </c>
+      <c r="L27">
+        <v>115.6</v>
+      </c>
+      <c r="M27">
+        <v>25.559435</v>
+      </c>
+      <c r="N27">
+        <v>90.04056500000002</v>
+      </c>
+      <c r="O27">
+        <v>13.14592249</v>
+      </c>
+      <c r="P27">
+        <v>76.89464251000001</v>
+      </c>
+      <c r="Q27">
+        <v>194.69464251</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0914375610750616</v>
+      </c>
+      <c r="T27">
+        <v>1.1442948059796</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.146</v>
+      </c>
+      <c r="W27">
+        <v>0.0434686</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.522791681428013</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08000948918784555</v>
+      </c>
+      <c r="C28">
+        <v>1457.312790075579</v>
+      </c>
+      <c r="D28">
+        <v>1650.648790075578</v>
+      </c>
+      <c r="E28">
+        <v>-186.364</v>
+      </c>
+      <c r="F28">
+        <v>522.236</v>
+      </c>
+      <c r="G28">
+        <v>328.9</v>
+      </c>
+      <c r="H28">
+        <v>1300</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>233.4</v>
+      </c>
+      <c r="K28">
+        <v>117.8</v>
+      </c>
+      <c r="L28">
+        <v>115.6</v>
+      </c>
+      <c r="M28">
+        <v>27.939626</v>
+      </c>
+      <c r="N28">
+        <v>87.660374</v>
+      </c>
+      <c r="O28">
+        <v>12.798414604</v>
+      </c>
+      <c r="P28">
+        <v>74.861959396</v>
+      </c>
+      <c r="Q28">
+        <v>192.661959396</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09206803944303453</v>
+      </c>
+      <c r="T28">
+        <v>1.158000857457272</v>
+      </c>
+      <c r="U28">
+        <v>0.0535</v>
+      </c>
+      <c r="V28">
+        <v>0.146</v>
+      </c>
+      <c r="W28">
+        <v>0.045689</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.137492749545038</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08064112356939492</v>
+      </c>
+      <c r="C29">
+        <v>1412.308565163539</v>
+      </c>
+      <c r="D29">
+        <v>1625.730565163539</v>
+      </c>
+      <c r="E29">
+        <v>-166.278</v>
+      </c>
+      <c r="F29">
+        <v>542.322</v>
+      </c>
+      <c r="G29">
+        <v>328.9</v>
+      </c>
+      <c r="H29">
+        <v>1300</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>233.4</v>
+      </c>
+      <c r="K29">
+        <v>117.8</v>
+      </c>
+      <c r="L29">
+        <v>115.6</v>
+      </c>
+      <c r="M29">
+        <v>30.4784964</v>
+      </c>
+      <c r="N29">
+        <v>85.12150360000001</v>
+      </c>
+      <c r="O29">
+        <v>12.4277395256</v>
+      </c>
+      <c r="P29">
+        <v>72.69376407440001</v>
+      </c>
+      <c r="Q29">
+        <v>190.4937640744</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09271579119095194</v>
+      </c>
+      <c r="T29">
+        <v>1.172082417194607</v>
+      </c>
+      <c r="U29">
+        <v>0.0562</v>
+      </c>
+      <c r="V29">
+        <v>0.146</v>
+      </c>
+      <c r="W29">
+        <v>0.0479948</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.792838022022635</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08067324995094427</v>
+      </c>
+      <c r="C30">
+        <v>1390.975257144838</v>
+      </c>
+      <c r="D30">
+        <v>1624.483257144838</v>
+      </c>
+      <c r="E30">
+        <v>-146.192</v>
+      </c>
+      <c r="F30">
+        <v>562.408</v>
+      </c>
+      <c r="G30">
+        <v>328.9</v>
+      </c>
+      <c r="H30">
+        <v>1300</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>233.4</v>
+      </c>
+      <c r="K30">
+        <v>117.8</v>
+      </c>
+      <c r="L30">
+        <v>115.6</v>
+      </c>
+      <c r="M30">
+        <v>31.6073296</v>
+      </c>
+      <c r="N30">
+        <v>83.99267040000001</v>
+      </c>
+      <c r="O30">
+        <v>12.2629298784</v>
+      </c>
+      <c r="P30">
+        <v>71.72974052160001</v>
+      </c>
+      <c r="Q30">
+        <v>189.5297405216</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09338153604297816</v>
+      </c>
+      <c r="T30">
+        <v>1.186555131369091</v>
+      </c>
+      <c r="U30">
+        <v>0.0562</v>
+      </c>
+      <c r="V30">
+        <v>0.146</v>
+      </c>
+      <c r="W30">
+        <v>0.0479948</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.657379521236113</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08070537633249361</v>
+      </c>
+      <c r="C31">
+        <v>1369.643861601186</v>
+      </c>
+      <c r="D31">
+        <v>1623.237861601186</v>
+      </c>
+      <c r="E31">
+        <v>-126.1060000000001</v>
+      </c>
+      <c r="F31">
+        <v>582.4939999999999</v>
+      </c>
+      <c r="G31">
+        <v>328.9</v>
+      </c>
+      <c r="H31">
+        <v>1300</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>233.4</v>
+      </c>
+      <c r="K31">
+        <v>117.8</v>
+      </c>
+      <c r="L31">
+        <v>115.6</v>
+      </c>
+      <c r="M31">
+        <v>32.7361628</v>
+      </c>
+      <c r="N31">
+        <v>82.86383720000001</v>
+      </c>
+      <c r="O31">
+        <v>12.0981202312</v>
+      </c>
+      <c r="P31">
+        <v>70.76571696880001</v>
+      </c>
+      <c r="Q31">
+        <v>188.5657169688</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09406603427111779</v>
+      </c>
+      <c r="T31">
+        <v>1.201435527632996</v>
+      </c>
+      <c r="U31">
+        <v>0.0562</v>
+      </c>
+      <c r="V31">
+        <v>0.146</v>
+      </c>
+      <c r="W31">
+        <v>0.0479948</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.531262986021074</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.081941642714043</v>
+      </c>
+      <c r="C32">
+        <v>1303.042377458473</v>
+      </c>
+      <c r="D32">
+        <v>1576.722377458473</v>
+      </c>
+      <c r="E32">
+        <v>-106.0200000000001</v>
+      </c>
+      <c r="F32">
+        <v>602.5799999999999</v>
+      </c>
+      <c r="G32">
+        <v>328.9</v>
+      </c>
+      <c r="H32">
+        <v>1300</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>233.4</v>
+      </c>
+      <c r="K32">
+        <v>117.8</v>
+      </c>
+      <c r="L32">
+        <v>115.6</v>
+      </c>
+      <c r="M32">
+        <v>36.697122</v>
+      </c>
+      <c r="N32">
+        <v>78.90287800000002</v>
+      </c>
+      <c r="O32">
+        <v>11.519820188</v>
+      </c>
+      <c r="P32">
+        <v>67.38305781200002</v>
+      </c>
+      <c r="Q32">
+        <v>185.183057812</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09477008959149</v>
+      </c>
+      <c r="T32">
+        <v>1.216741078075869</v>
+      </c>
+      <c r="U32">
+        <v>0.0609</v>
+      </c>
+      <c r="V32">
+        <v>0.146</v>
+      </c>
+      <c r="W32">
+        <v>0.0520086</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.150110790704514</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08201390709559234</v>
+      </c>
+      <c r="C33">
+        <v>1280.319706184339</v>
+      </c>
+      <c r="D33">
+        <v>1574.085706184339</v>
+      </c>
+      <c r="E33">
+        <v>-85.93400000000008</v>
+      </c>
+      <c r="F33">
+        <v>622.6659999999999</v>
+      </c>
+      <c r="G33">
+        <v>328.9</v>
+      </c>
+      <c r="H33">
+        <v>1300</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>233.4</v>
+      </c>
+      <c r="K33">
+        <v>117.8</v>
+      </c>
+      <c r="L33">
+        <v>115.6</v>
+      </c>
+      <c r="M33">
+        <v>37.9203594</v>
+      </c>
+      <c r="N33">
+        <v>77.67964060000001</v>
+      </c>
+      <c r="O33">
+        <v>11.3412275276</v>
+      </c>
+      <c r="P33">
+        <v>66.33841307240002</v>
+      </c>
+      <c r="Q33">
+        <v>184.1384130724</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09549455231245269</v>
+      </c>
+      <c r="T33">
+        <v>1.232490267662015</v>
+      </c>
+      <c r="U33">
+        <v>0.0609</v>
+      </c>
+      <c r="V33">
+        <v>0.146</v>
+      </c>
+      <c r="W33">
+        <v>0.0520086</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.048494313585014</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0846276754771417</v>
+      </c>
+      <c r="C34">
+        <v>1170.456177522088</v>
+      </c>
+      <c r="D34">
+        <v>1484.308177522088</v>
+      </c>
+      <c r="E34">
+        <v>-65.84800000000007</v>
+      </c>
+      <c r="F34">
+        <v>642.752</v>
+      </c>
+      <c r="G34">
+        <v>328.9</v>
+      </c>
+      <c r="H34">
+        <v>1300</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>233.4</v>
+      </c>
+      <c r="K34">
+        <v>117.8</v>
+      </c>
+      <c r="L34">
+        <v>115.6</v>
+      </c>
+      <c r="M34">
+        <v>45.1211904</v>
+      </c>
+      <c r="N34">
+        <v>70.47880960000001</v>
+      </c>
+      <c r="O34">
+        <v>10.2899062016</v>
+      </c>
+      <c r="P34">
+        <v>60.1889033984</v>
+      </c>
+      <c r="Q34">
+        <v>177.9889033984</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09624032276050251</v>
+      </c>
+      <c r="T34">
+        <v>1.248702668706577</v>
+      </c>
+      <c r="U34">
+        <v>0.0702</v>
+      </c>
+      <c r="V34">
+        <v>0.146</v>
+      </c>
+      <c r="W34">
+        <v>0.0599508</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.561989144683559</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08610391585869107</v>
+      </c>
+      <c r="C35">
+        <v>1104.048522527019</v>
+      </c>
+      <c r="D35">
+        <v>1437.986522527019</v>
+      </c>
+      <c r="E35">
+        <v>-45.76200000000006</v>
+      </c>
+      <c r="F35">
+        <v>662.838</v>
+      </c>
+      <c r="G35">
+        <v>328.9</v>
+      </c>
+      <c r="H35">
+        <v>1300</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>233.4</v>
+      </c>
+      <c r="K35">
+        <v>117.8</v>
+      </c>
+      <c r="L35">
+        <v>115.6</v>
+      </c>
+      <c r="M35">
+        <v>49.6465662</v>
+      </c>
+      <c r="N35">
+        <v>65.95343380000001</v>
+      </c>
+      <c r="O35">
+        <v>9.629201334800001</v>
+      </c>
+      <c r="P35">
+        <v>56.32423246520001</v>
+      </c>
+      <c r="Q35">
+        <v>174.1242324652</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09700835501297175</v>
+      </c>
+      <c r="T35">
+        <v>1.265399022021125</v>
+      </c>
+      <c r="U35">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V35">
+        <v>0.146</v>
+      </c>
+      <c r="W35">
+        <v>0.0639646</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.328459123120584</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08629574024024042</v>
+      </c>
+      <c r="C36">
+        <v>1078.154825374289</v>
+      </c>
+      <c r="D36">
+        <v>1432.178825374289</v>
+      </c>
+      <c r="E36">
+        <v>-25.67600000000004</v>
+      </c>
+      <c r="F36">
+        <v>682.924</v>
+      </c>
+      <c r="G36">
+        <v>328.9</v>
+      </c>
+      <c r="H36">
+        <v>1300</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>233.4</v>
+      </c>
+      <c r="K36">
+        <v>117.8</v>
+      </c>
+      <c r="L36">
+        <v>115.6</v>
+      </c>
+      <c r="M36">
+        <v>51.15100759999999</v>
+      </c>
+      <c r="N36">
+        <v>64.44899240000001</v>
+      </c>
+      <c r="O36">
+        <v>9.409552890400001</v>
+      </c>
+      <c r="P36">
+        <v>55.03943950960001</v>
+      </c>
+      <c r="Q36">
+        <v>172.8394395096</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09779966097006126</v>
+      </c>
+      <c r="T36">
+        <v>1.282601325436114</v>
+      </c>
+      <c r="U36">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V36">
+        <v>0.146</v>
+      </c>
+      <c r="W36">
+        <v>0.0639646</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.259975031264096</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08648756462178978</v>
+      </c>
+      <c r="C37">
+        <v>1052.307851425958</v>
+      </c>
+      <c r="D37">
+        <v>1426.417851425958</v>
+      </c>
+      <c r="E37">
+        <v>-5.590000000000032</v>
+      </c>
+      <c r="F37">
+        <v>703.01</v>
+      </c>
+      <c r="G37">
+        <v>328.9</v>
+      </c>
+      <c r="H37">
+        <v>1300</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>233.4</v>
+      </c>
+      <c r="K37">
+        <v>117.8</v>
+      </c>
+      <c r="L37">
+        <v>115.6</v>
+      </c>
+      <c r="M37">
+        <v>52.655449</v>
+      </c>
+      <c r="N37">
+        <v>62.94455100000001</v>
+      </c>
+      <c r="O37">
+        <v>9.189904446000002</v>
+      </c>
+      <c r="P37">
+        <v>53.75464655400001</v>
+      </c>
+      <c r="Q37">
+        <v>171.554646554</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09861531480275351</v>
+      </c>
+      <c r="T37">
+        <v>1.300332930494642</v>
+      </c>
+      <c r="U37">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V37">
+        <v>0.146</v>
+      </c>
+      <c r="W37">
+        <v>0.0639646</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.195404316085122</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08667938900333914</v>
+      </c>
+      <c r="C38">
+        <v>1026.507039105322</v>
+      </c>
+      <c r="D38">
+        <v>1420.703039105322</v>
+      </c>
+      <c r="E38">
+        <v>14.49599999999987</v>
+      </c>
+      <c r="F38">
+        <v>723.0959999999999</v>
+      </c>
+      <c r="G38">
+        <v>328.9</v>
+      </c>
+      <c r="H38">
+        <v>1300</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>233.4</v>
+      </c>
+      <c r="K38">
+        <v>117.8</v>
+      </c>
+      <c r="L38">
+        <v>115.6</v>
+      </c>
+      <c r="M38">
+        <v>54.15989039999999</v>
+      </c>
+      <c r="N38">
+        <v>61.44010960000002</v>
+      </c>
+      <c r="O38">
+        <v>8.970256001600003</v>
+      </c>
+      <c r="P38">
+        <v>52.46985359840002</v>
+      </c>
+      <c r="Q38">
+        <v>170.2698535984</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09945645781771742</v>
+      </c>
+      <c r="T38">
+        <v>1.318618648211248</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.146</v>
+      </c>
+      <c r="W38">
+        <v>0.0639646</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.134420862860535</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08687121338488851</v>
+      </c>
+      <c r="C39">
+        <v>1000.751835799393</v>
+      </c>
+      <c r="D39">
+        <v>1415.033835799392</v>
+      </c>
+      <c r="E39">
+        <v>34.58199999999988</v>
+      </c>
+      <c r="F39">
+        <v>743.1819999999999</v>
+      </c>
+      <c r="G39">
+        <v>328.9</v>
+      </c>
+      <c r="H39">
+        <v>1300</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>233.4</v>
+      </c>
+      <c r="K39">
+        <v>117.8</v>
+      </c>
+      <c r="L39">
+        <v>115.6</v>
+      </c>
+      <c r="M39">
+        <v>55.66433179999999</v>
+      </c>
+      <c r="N39">
+        <v>59.93566820000002</v>
+      </c>
+      <c r="O39">
+        <v>8.750607557200002</v>
+      </c>
+      <c r="P39">
+        <v>51.18506064280002</v>
+      </c>
+      <c r="Q39">
+        <v>168.9850606428</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1003243037855373</v>
+      </c>
+      <c r="T39">
+        <v>1.337484864902985</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.146</v>
+      </c>
+      <c r="W39">
+        <v>0.0639646</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.076733812512954</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08706303776643785</v>
+      </c>
+      <c r="C40">
+        <v>975.0416976807514</v>
+      </c>
+      <c r="D40">
+        <v>1409.409697680752</v>
+      </c>
+      <c r="E40">
+        <v>54.66800000000001</v>
+      </c>
+      <c r="F40">
+        <v>763.268</v>
+      </c>
+      <c r="G40">
+        <v>328.9</v>
+      </c>
+      <c r="H40">
+        <v>1300</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>233.4</v>
+      </c>
+      <c r="K40">
+        <v>117.8</v>
+      </c>
+      <c r="L40">
+        <v>115.6</v>
+      </c>
+      <c r="M40">
+        <v>57.1687732</v>
+      </c>
+      <c r="N40">
+        <v>58.43122680000001</v>
+      </c>
+      <c r="O40">
+        <v>8.530959112800002</v>
+      </c>
+      <c r="P40">
+        <v>49.90026768720001</v>
+      </c>
+      <c r="Q40">
+        <v>167.7002676872</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1012201447845772</v>
+      </c>
+      <c r="T40">
+        <v>1.356959669229939</v>
+      </c>
+      <c r="U40">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V40">
+        <v>0.146</v>
+      </c>
+      <c r="W40">
+        <v>0.0639646</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.022082922709981</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09268374014798723</v>
+      </c>
+      <c r="C41">
+        <v>807.9378325033115</v>
+      </c>
+      <c r="D41">
+        <v>1262.391832503312</v>
+      </c>
+      <c r="E41">
+        <v>74.75400000000002</v>
+      </c>
+      <c r="F41">
+        <v>783.354</v>
+      </c>
+      <c r="G41">
+        <v>328.9</v>
+      </c>
+      <c r="H41">
+        <v>1300</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>233.4</v>
+      </c>
+      <c r="K41">
+        <v>117.8</v>
+      </c>
+      <c r="L41">
+        <v>115.6</v>
+      </c>
+      <c r="M41">
+        <v>71.44188480000001</v>
+      </c>
+      <c r="N41">
+        <v>44.1581152</v>
+      </c>
+      <c r="O41">
+        <v>6.4470848192</v>
+      </c>
+      <c r="P41">
+        <v>37.7110303808</v>
+      </c>
+      <c r="Q41">
+        <v>155.5110303808</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1021453576196512</v>
+      </c>
+      <c r="T41">
+        <v>1.377072991731548</v>
+      </c>
+      <c r="U41">
+        <v>0.0912</v>
+      </c>
+      <c r="V41">
+        <v>0.146</v>
+      </c>
+      <c r="W41">
+        <v>0.0778848</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.618098407168563</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09301476652953658</v>
+      </c>
+      <c r="C42">
+        <v>780.1438771405719</v>
+      </c>
+      <c r="D42">
+        <v>1254.683877140572</v>
+      </c>
+      <c r="E42">
+        <v>94.84000000000003</v>
+      </c>
+      <c r="F42">
+        <v>803.4400000000001</v>
+      </c>
+      <c r="G42">
+        <v>328.9</v>
+      </c>
+      <c r="H42">
+        <v>1300</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>233.4</v>
+      </c>
+      <c r="K42">
+        <v>117.8</v>
+      </c>
+      <c r="L42">
+        <v>115.6</v>
+      </c>
+      <c r="M42">
+        <v>73.27372800000001</v>
+      </c>
+      <c r="N42">
+        <v>42.326272</v>
+      </c>
+      <c r="O42">
+        <v>6.179635712</v>
+      </c>
+      <c r="P42">
+        <v>36.146636288</v>
+      </c>
+      <c r="Q42">
+        <v>153.946636288</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.103101410882561</v>
+      </c>
+      <c r="T42">
+        <v>1.397856758316543</v>
+      </c>
+      <c r="U42">
+        <v>0.0912</v>
+      </c>
+      <c r="V42">
+        <v>0.146</v>
+      </c>
+      <c r="W42">
+        <v>0.0778848</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.577645946989349</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09334579291108594</v>
+      </c>
+      <c r="C43">
+        <v>752.4434775384764</v>
+      </c>
+      <c r="D43">
+        <v>1247.069477538477</v>
+      </c>
+      <c r="E43">
+        <v>114.926</v>
+      </c>
+      <c r="F43">
+        <v>823.5260000000001</v>
+      </c>
+      <c r="G43">
+        <v>328.9</v>
+      </c>
+      <c r="H43">
+        <v>1300</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>233.4</v>
+      </c>
+      <c r="K43">
+        <v>117.8</v>
+      </c>
+      <c r="L43">
+        <v>115.6</v>
+      </c>
+      <c r="M43">
+        <v>75.10557120000001</v>
+      </c>
+      <c r="N43">
+        <v>40.49442879999999</v>
+      </c>
+      <c r="O43">
+        <v>5.912186604799999</v>
+      </c>
+      <c r="P43">
+        <v>34.5822421952</v>
+      </c>
+      <c r="Q43">
+        <v>152.3822421952</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1040898727306541</v>
+      </c>
+      <c r="T43">
+        <v>1.419345059362046</v>
+      </c>
+      <c r="U43">
+        <v>0.0912</v>
+      </c>
+      <c r="V43">
+        <v>0.146</v>
+      </c>
+      <c r="W43">
+        <v>0.0778848</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.539166777550585</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.0936768192926353</v>
+      </c>
+      <c r="C44">
+        <v>724.8349406638655</v>
+      </c>
+      <c r="D44">
+        <v>1239.546940663865</v>
+      </c>
+      <c r="E44">
+        <v>135.0119999999999</v>
+      </c>
+      <c r="F44">
+        <v>843.612</v>
+      </c>
+      <c r="G44">
+        <v>328.9</v>
+      </c>
+      <c r="H44">
+        <v>1300</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>233.4</v>
+      </c>
+      <c r="K44">
+        <v>117.8</v>
+      </c>
+      <c r="L44">
+        <v>115.6</v>
+      </c>
+      <c r="M44">
+        <v>76.93741439999999</v>
+      </c>
+      <c r="N44">
+        <v>38.66258560000001</v>
+      </c>
+      <c r="O44">
+        <v>5.644737497600001</v>
+      </c>
+      <c r="P44">
+        <v>33.01784810240001</v>
+      </c>
+      <c r="Q44">
+        <v>150.8178481024</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1051124194700608</v>
+      </c>
+      <c r="T44">
+        <v>1.441574336305671</v>
+      </c>
+      <c r="U44">
+        <v>0.0912</v>
+      </c>
+      <c r="V44">
+        <v>0.146</v>
+      </c>
+      <c r="W44">
+        <v>0.0778848</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.502519949513666</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1198265209412355</v>
+      </c>
+      <c r="C45">
+        <v>304.7097645859077</v>
+      </c>
+      <c r="D45">
+        <v>839.5077645859077</v>
+      </c>
+      <c r="E45">
+        <v>155.098</v>
+      </c>
+      <c r="F45">
+        <v>863.698</v>
+      </c>
+      <c r="G45">
+        <v>328.9</v>
+      </c>
+      <c r="H45">
+        <v>1300</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>233.4</v>
+      </c>
+      <c r="K45">
+        <v>117.8</v>
+      </c>
+      <c r="L45">
+        <v>115.6</v>
+      </c>
+      <c r="M45">
+        <v>135.2551068</v>
+      </c>
+      <c r="N45">
+        <v>-19.65510680000001</v>
+      </c>
+      <c r="O45">
+        <v>-2.869645592800002</v>
+      </c>
+      <c r="P45">
+        <v>-16.78546120720001</v>
+      </c>
+      <c r="Q45">
+        <v>101.0145387928</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1068266481869764</v>
+      </c>
+      <c r="T45">
+        <v>1.478840177977748</v>
+      </c>
+      <c r="U45">
+        <v>0.1566</v>
+      </c>
+      <c r="V45">
+        <v>0.1247834584534889</v>
+      </c>
+      <c r="W45">
+        <v>0.1370589104061837</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8546812222841702</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1210045209412355</v>
+      </c>
+      <c r="C46">
+        <v>272.593524212764</v>
+      </c>
+      <c r="D46">
+        <v>827.4775242127641</v>
+      </c>
+      <c r="E46">
+        <v>175.184</v>
+      </c>
+      <c r="F46">
+        <v>883.784</v>
+      </c>
+      <c r="G46">
+        <v>328.9</v>
+      </c>
+      <c r="H46">
+        <v>1300</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>233.4</v>
+      </c>
+      <c r="K46">
+        <v>117.8</v>
+      </c>
+      <c r="L46">
+        <v>115.6</v>
+      </c>
+      <c r="M46">
+        <v>138.4005744</v>
+      </c>
+      <c r="N46">
+        <v>-22.8005744</v>
+      </c>
+      <c r="O46">
+        <v>-3.3288838624</v>
+      </c>
+      <c r="P46">
+        <v>-19.4716905376</v>
+      </c>
+      <c r="Q46">
+        <v>98.3283094624</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1080414097617438</v>
+      </c>
+      <c r="T46">
+        <v>1.505248038298779</v>
+      </c>
+      <c r="U46">
+        <v>0.1566</v>
+      </c>
+      <c r="V46">
+        <v>0.1219474707613641</v>
+      </c>
+      <c r="W46">
+        <v>0.1375030260787704</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8352566490504392</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1221825209412355</v>
+      </c>
+      <c r="C47">
+        <v>240.8172021582219</v>
+      </c>
+      <c r="D47">
+        <v>815.7872021582219</v>
+      </c>
+      <c r="E47">
+        <v>195.27</v>
+      </c>
+      <c r="F47">
+        <v>903.87</v>
+      </c>
+      <c r="G47">
+        <v>328.9</v>
+      </c>
+      <c r="H47">
+        <v>1300</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>233.4</v>
+      </c>
+      <c r="K47">
+        <v>117.8</v>
+      </c>
+      <c r="L47">
+        <v>115.6</v>
+      </c>
+      <c r="M47">
+        <v>141.546042</v>
+      </c>
+      <c r="N47">
+        <v>-25.94604200000002</v>
+      </c>
+      <c r="O47">
+        <v>-3.788122132000002</v>
+      </c>
+      <c r="P47">
+        <v>-22.15791986800002</v>
+      </c>
+      <c r="Q47">
+        <v>95.64208013199998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1093003444846846</v>
+      </c>
+      <c r="T47">
+        <v>1.532616184449666</v>
+      </c>
+      <c r="U47">
+        <v>0.1566</v>
+      </c>
+      <c r="V47">
+        <v>0.1192375269666671</v>
+      </c>
+      <c r="W47">
+        <v>0.1379274032770199</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8166953901826516</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1479221513914819</v>
+      </c>
+      <c r="C48">
+        <v>28.30408409067809</v>
+      </c>
+      <c r="D48">
+        <v>623.3600840906781</v>
+      </c>
+      <c r="E48">
+        <v>215.356</v>
+      </c>
+      <c r="F48">
+        <v>923.956</v>
+      </c>
+      <c r="G48">
+        <v>328.9</v>
+      </c>
+      <c r="H48">
+        <v>1300</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>233.4</v>
+      </c>
+      <c r="K48">
+        <v>117.8</v>
+      </c>
+      <c r="L48">
+        <v>115.6</v>
+      </c>
+      <c r="M48">
+        <v>192.9220128</v>
+      </c>
+      <c r="N48">
+        <v>-77.3220128</v>
+      </c>
+      <c r="O48">
+        <v>-11.2890138688</v>
+      </c>
+      <c r="P48">
+        <v>-66.0329989312</v>
+      </c>
+      <c r="Q48">
+        <v>51.7670010688</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1116237405867092</v>
+      </c>
+      <c r="T48">
+        <v>1.583124795363243</v>
+      </c>
+      <c r="U48">
+        <v>0.2088</v>
+      </c>
+      <c r="V48">
+        <v>0.0874840551114134</v>
+      </c>
+      <c r="W48">
+        <v>0.1905333292927369</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.599205856927489</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1496221513914819</v>
+      </c>
+      <c r="C49">
+        <v>-1.344193212626578</v>
+      </c>
+      <c r="D49">
+        <v>613.7978067873735</v>
+      </c>
+      <c r="E49">
+        <v>235.442</v>
+      </c>
+      <c r="F49">
+        <v>944.042</v>
+      </c>
+      <c r="G49">
+        <v>328.9</v>
+      </c>
+      <c r="H49">
+        <v>1300</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>233.4</v>
+      </c>
+      <c r="K49">
+        <v>117.8</v>
+      </c>
+      <c r="L49">
+        <v>115.6</v>
+      </c>
+      <c r="M49">
+        <v>197.1159696</v>
+      </c>
+      <c r="N49">
+        <v>-81.51596960000002</v>
+      </c>
+      <c r="O49">
+        <v>-11.9013315616</v>
+      </c>
+      <c r="P49">
+        <v>-69.61463803840002</v>
+      </c>
+      <c r="Q49">
+        <v>48.18536196159998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1129977734279679</v>
+      </c>
+      <c r="T49">
+        <v>1.61299507452104</v>
+      </c>
+      <c r="U49">
+        <v>0.2088</v>
+      </c>
+      <c r="V49">
+        <v>0.08562269223670246</v>
+      </c>
+      <c r="W49">
+        <v>0.1909219818609765</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5864567961417977</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1513221513914819</v>
+      </c>
+      <c r="C50">
+        <v>-30.70353413825615</v>
+      </c>
+      <c r="D50">
+        <v>604.5244658617438</v>
+      </c>
+      <c r="E50">
+        <v>255.5279999999999</v>
+      </c>
+      <c r="F50">
+        <v>964.1279999999999</v>
+      </c>
+      <c r="G50">
+        <v>328.9</v>
+      </c>
+      <c r="H50">
+        <v>1300</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>233.4</v>
+      </c>
+      <c r="K50">
+        <v>117.8</v>
+      </c>
+      <c r="L50">
+        <v>115.6</v>
+      </c>
+      <c r="M50">
+        <v>201.3099264</v>
+      </c>
+      <c r="N50">
+        <v>-85.70992639999999</v>
+      </c>
+      <c r="O50">
+        <v>-12.5136492544</v>
+      </c>
+      <c r="P50">
+        <v>-73.19627714559999</v>
+      </c>
+      <c r="Q50">
+        <v>44.6037228544</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.114424653686198</v>
+      </c>
+      <c r="T50">
+        <v>1.644014210569522</v>
+      </c>
+      <c r="U50">
+        <v>0.2088</v>
+      </c>
+      <c r="V50">
+        <v>0.08383888614843783</v>
+      </c>
+      <c r="W50">
+        <v>0.1912944405722062</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5742389462221771</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1530221513914819</v>
+      </c>
+      <c r="C51">
+        <v>-59.7868396472611</v>
+      </c>
+      <c r="D51">
+        <v>595.5271603527389</v>
+      </c>
+      <c r="E51">
+        <v>275.6139999999999</v>
+      </c>
+      <c r="F51">
+        <v>984.2139999999999</v>
+      </c>
+      <c r="G51">
+        <v>328.9</v>
+      </c>
+      <c r="H51">
+        <v>1300</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>233.4</v>
+      </c>
+      <c r="K51">
+        <v>117.8</v>
+      </c>
+      <c r="L51">
+        <v>115.6</v>
+      </c>
+      <c r="M51">
+        <v>205.5038832</v>
+      </c>
+      <c r="N51">
+        <v>-89.90388319999998</v>
+      </c>
+      <c r="O51">
+        <v>-13.1259669472</v>
+      </c>
+      <c r="P51">
+        <v>-76.77791625279998</v>
+      </c>
+      <c r="Q51">
+        <v>41.02208374720001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1159074900329862</v>
+      </c>
+      <c r="T51">
+        <v>1.676249783325787</v>
+      </c>
+      <c r="U51">
+        <v>0.2088</v>
+      </c>
+      <c r="V51">
+        <v>0.08212788847193911</v>
+      </c>
+      <c r="W51">
+        <v>0.1916516968870591</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5625197840543774</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1547221513914819</v>
+      </c>
+      <c r="C52">
+        <v>-88.60625392958127</v>
+      </c>
+      <c r="D52">
+        <v>586.7937460704187</v>
+      </c>
+      <c r="E52">
+        <v>295.6999999999999</v>
+      </c>
+      <c r="F52">
+        <v>1004.3</v>
+      </c>
+      <c r="G52">
+        <v>328.9</v>
+      </c>
+      <c r="H52">
+        <v>1300</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>233.4</v>
+      </c>
+      <c r="K52">
+        <v>117.8</v>
+      </c>
+      <c r="L52">
+        <v>115.6</v>
+      </c>
+      <c r="M52">
+        <v>209.69784</v>
+      </c>
+      <c r="N52">
+        <v>-94.09784000000001</v>
+      </c>
+      <c r="O52">
+        <v>-13.73828464</v>
+      </c>
+      <c r="P52">
+        <v>-80.35955536</v>
+      </c>
+      <c r="Q52">
+        <v>37.44044464</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1174496398336459</v>
+      </c>
+      <c r="T52">
+        <v>1.709774778992303</v>
+      </c>
+      <c r="U52">
+        <v>0.2088</v>
+      </c>
+      <c r="V52">
+        <v>0.08048533070250032</v>
+      </c>
+      <c r="W52">
+        <v>0.1919946629493179</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5512693883732899</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1564221513914819</v>
+      </c>
+      <c r="C53">
+        <v>-117.1732190923385</v>
+      </c>
+      <c r="D53">
+        <v>578.3127809076615</v>
+      </c>
+      <c r="E53">
+        <v>315.7859999999999</v>
+      </c>
+      <c r="F53">
+        <v>1024.386</v>
+      </c>
+      <c r="G53">
+        <v>328.9</v>
+      </c>
+      <c r="H53">
+        <v>1300</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>233.4</v>
+      </c>
+      <c r="K53">
+        <v>117.8</v>
+      </c>
+      <c r="L53">
+        <v>115.6</v>
+      </c>
+      <c r="M53">
+        <v>213.8917968</v>
+      </c>
+      <c r="N53">
+        <v>-98.2917968</v>
+      </c>
+      <c r="O53">
+        <v>-14.3506023328</v>
+      </c>
+      <c r="P53">
+        <v>-83.94119446720001</v>
+      </c>
+      <c r="Q53">
+        <v>33.85880553279999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1190547345241285</v>
+      </c>
+      <c r="T53">
+        <v>1.744668141828881</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.07890718696323559</v>
+      </c>
+      <c r="W53">
+        <v>0.1923241793620764</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5404601846796959</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1581221513914819</v>
+      </c>
+      <c r="C54">
+        <v>-145.4985251732145</v>
+      </c>
+      <c r="D54">
+        <v>570.0734748267855</v>
+      </c>
+      <c r="E54">
+        <v>335.872</v>
+      </c>
+      <c r="F54">
+        <v>1044.472</v>
+      </c>
+      <c r="G54">
+        <v>328.9</v>
+      </c>
+      <c r="H54">
+        <v>1300</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>233.4</v>
+      </c>
+      <c r="K54">
+        <v>117.8</v>
+      </c>
+      <c r="L54">
+        <v>115.6</v>
+      </c>
+      <c r="M54">
+        <v>218.0857536</v>
+      </c>
+      <c r="N54">
+        <v>-102.4857536</v>
+      </c>
+      <c r="O54">
+        <v>-14.9629200256</v>
+      </c>
+      <c r="P54">
+        <v>-87.5228335744</v>
+      </c>
+      <c r="Q54">
+        <v>30.2771664256</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1207267081600478</v>
+      </c>
+      <c r="T54">
+        <v>1.781015394783649</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.07738974106009647</v>
+      </c>
+      <c r="W54">
+        <v>0.1926410220666519</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5300667195897018</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1598221513914819</v>
+      </c>
+      <c r="C55">
+        <v>-173.5923559385972</v>
+      </c>
+      <c r="D55">
+        <v>562.0656440614028</v>
+      </c>
+      <c r="E55">
+        <v>355.958</v>
+      </c>
+      <c r="F55">
+        <v>1064.558</v>
+      </c>
+      <c r="G55">
+        <v>328.9</v>
+      </c>
+      <c r="H55">
+        <v>1300</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>233.4</v>
+      </c>
+      <c r="K55">
+        <v>117.8</v>
+      </c>
+      <c r="L55">
+        <v>115.6</v>
+      </c>
+      <c r="M55">
+        <v>222.2797104</v>
+      </c>
+      <c r="N55">
+        <v>-106.6797104</v>
+      </c>
+      <c r="O55">
+        <v>-15.5752377184</v>
+      </c>
+      <c r="P55">
+        <v>-91.10447268159999</v>
+      </c>
+      <c r="Q55">
+        <v>26.69552731840001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1224698296102616</v>
+      </c>
+      <c r="T55">
+        <v>1.818909339353513</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.07592955726650974</v>
+      </c>
+      <c r="W55">
+        <v>0.1929459084427528</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5200654607295188</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1615221513914819</v>
+      </c>
+      <c r="C56">
+        <v>-201.4643308752353</v>
+      </c>
+      <c r="D56">
+        <v>554.2796691247647</v>
+      </c>
+      <c r="E56">
+        <v>376.044</v>
+      </c>
+      <c r="F56">
+        <v>1084.644</v>
+      </c>
+      <c r="G56">
+        <v>328.9</v>
+      </c>
+      <c r="H56">
+        <v>1300</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>233.4</v>
+      </c>
+      <c r="K56">
+        <v>117.8</v>
+      </c>
+      <c r="L56">
+        <v>115.6</v>
+      </c>
+      <c r="M56">
+        <v>226.4736672</v>
+      </c>
+      <c r="N56">
+        <v>-110.8736672</v>
+      </c>
+      <c r="O56">
+        <v>-16.1875554112</v>
+      </c>
+      <c r="P56">
+        <v>-94.68611178880002</v>
+      </c>
+      <c r="Q56">
+        <v>23.11388821119998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1242887389496151</v>
+      </c>
+      <c r="T56">
+        <v>1.858450846730764</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.07452345435416696</v>
+      </c>
+      <c r="W56">
+        <v>0.1932395027308499</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5104346188641573</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1632221513914819</v>
+      </c>
+      <c r="C57">
+        <v>-229.1235437394571</v>
+      </c>
+      <c r="D57">
+        <v>546.706456260543</v>
+      </c>
+      <c r="E57">
+        <v>396.13</v>
+      </c>
+      <c r="F57">
+        <v>1104.73</v>
+      </c>
+      <c r="G57">
+        <v>328.9</v>
+      </c>
+      <c r="H57">
+        <v>1300</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>233.4</v>
+      </c>
+      <c r="K57">
+        <v>117.8</v>
+      </c>
+      <c r="L57">
+        <v>115.6</v>
+      </c>
+      <c r="M57">
+        <v>230.667624</v>
+      </c>
+      <c r="N57">
+        <v>-115.067624</v>
+      </c>
+      <c r="O57">
+        <v>-16.799873104</v>
+      </c>
+      <c r="P57">
+        <v>-98.26775089600001</v>
+      </c>
+      <c r="Q57">
+        <v>19.53224910399999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.126188488704051</v>
+      </c>
+      <c r="T57">
+        <v>1.899749754435892</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0.07316848245681848</v>
+      </c>
+      <c r="W57">
+        <v>0.1935224208630163</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5011539894302635</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1819292985460974</v>
+      </c>
+      <c r="C58">
+        <v>-320.6646422520124</v>
+      </c>
+      <c r="D58">
+        <v>475.2513577479876</v>
+      </c>
+      <c r="E58">
+        <v>416.216</v>
+      </c>
+      <c r="F58">
+        <v>1124.816</v>
+      </c>
+      <c r="G58">
+        <v>328.9</v>
+      </c>
+      <c r="H58">
+        <v>1300</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>233.4</v>
+      </c>
+      <c r="K58">
+        <v>117.8</v>
+      </c>
+      <c r="L58">
+        <v>115.6</v>
+      </c>
+      <c r="M58">
+        <v>268.6060608</v>
+      </c>
+      <c r="N58">
+        <v>-153.0060608</v>
+      </c>
+      <c r="O58">
+        <v>-22.3388848768</v>
+      </c>
+      <c r="P58">
+        <v>-130.6671759232</v>
+      </c>
+      <c r="Q58">
+        <v>-12.86717592320001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1286453797078146</v>
+      </c>
+      <c r="T58">
+        <v>1.953160428430753</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0628340252253906</v>
+      </c>
+      <c r="W58">
+        <v>0.2237952347761767</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4303700357903466</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1839292985460974</v>
+      </c>
+      <c r="C59">
+        <v>-347.2999932446658</v>
+      </c>
+      <c r="D59">
+        <v>468.7020067553343</v>
+      </c>
+      <c r="E59">
+        <v>436.302</v>
+      </c>
+      <c r="F59">
+        <v>1144.902</v>
+      </c>
+      <c r="G59">
+        <v>328.9</v>
+      </c>
+      <c r="H59">
+        <v>1300</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>233.4</v>
+      </c>
+      <c r="K59">
+        <v>117.8</v>
+      </c>
+      <c r="L59">
+        <v>115.6</v>
+      </c>
+      <c r="M59">
+        <v>273.4025976</v>
+      </c>
+      <c r="N59">
+        <v>-157.8025976</v>
+      </c>
+      <c r="O59">
+        <v>-23.0391792496</v>
+      </c>
+      <c r="P59">
+        <v>-134.7634183504</v>
+      </c>
+      <c r="Q59">
+        <v>-16.9634183504</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1307348071428801</v>
+      </c>
+      <c r="T59">
+        <v>1.998582763975655</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.0617316739056469</v>
+      </c>
+      <c r="W59">
+        <v>0.2240584762713315</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4228196842852527</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1859292985460974</v>
+      </c>
+      <c r="C60">
+        <v>-373.7572872206032</v>
+      </c>
+      <c r="D60">
+        <v>462.3307127793967</v>
+      </c>
+      <c r="E60">
+        <v>456.3879999999998</v>
+      </c>
+      <c r="F60">
+        <v>1164.988</v>
+      </c>
+      <c r="G60">
+        <v>328.9</v>
+      </c>
+      <c r="H60">
+        <v>1300</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>233.4</v>
+      </c>
+      <c r="K60">
+        <v>117.8</v>
+      </c>
+      <c r="L60">
+        <v>115.6</v>
+      </c>
+      <c r="M60">
+        <v>278.1991344</v>
+      </c>
+      <c r="N60">
+        <v>-162.5991344</v>
+      </c>
+      <c r="O60">
+        <v>-23.73947362239999</v>
+      </c>
+      <c r="P60">
+        <v>-138.8596607776</v>
+      </c>
+      <c r="Q60">
+        <v>-21.05966077759997</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1329237311224725</v>
+      </c>
+      <c r="T60">
+        <v>2.046168067879837</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06066733470037713</v>
+      </c>
+      <c r="W60">
+        <v>0.22431264047355</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4155296897286106</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1879292985460974</v>
+      </c>
+      <c r="C61">
+        <v>-400.0436880444088</v>
+      </c>
+      <c r="D61">
+        <v>456.1303119555911</v>
+      </c>
+      <c r="E61">
+        <v>476.4739999999998</v>
+      </c>
+      <c r="F61">
+        <v>1185.074</v>
+      </c>
+      <c r="G61">
+        <v>328.9</v>
+      </c>
+      <c r="H61">
+        <v>1300</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>233.4</v>
+      </c>
+      <c r="K61">
+        <v>117.8</v>
+      </c>
+      <c r="L61">
+        <v>115.6</v>
+      </c>
+      <c r="M61">
+        <v>282.9956712</v>
+      </c>
+      <c r="N61">
+        <v>-167.3956712</v>
+      </c>
+      <c r="O61">
+        <v>-24.4397679952</v>
+      </c>
+      <c r="P61">
+        <v>-142.9559032048</v>
+      </c>
+      <c r="Q61">
+        <v>-25.1559032048</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1352194318815572</v>
+      </c>
+      <c r="T61">
+        <v>2.096074606120808</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05963907479020124</v>
+      </c>
+      <c r="W61">
+        <v>0.2245581889401</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4084868136315154</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1899292985460974</v>
+      </c>
+      <c r="C62">
+        <v>-426.1659803628896</v>
+      </c>
+      <c r="D62">
+        <v>450.0940196371103</v>
+      </c>
+      <c r="E62">
+        <v>496.5599999999998</v>
+      </c>
+      <c r="F62">
+        <v>1205.16</v>
+      </c>
+      <c r="G62">
+        <v>328.9</v>
+      </c>
+      <c r="H62">
+        <v>1300</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>233.4</v>
+      </c>
+      <c r="K62">
+        <v>117.8</v>
+      </c>
+      <c r="L62">
+        <v>115.6</v>
+      </c>
+      <c r="M62">
+        <v>287.792208</v>
+      </c>
+      <c r="N62">
+        <v>-172.1922079999999</v>
+      </c>
+      <c r="O62">
+        <v>-25.14006236799999</v>
+      </c>
+      <c r="P62">
+        <v>-147.052145632</v>
+      </c>
+      <c r="Q62">
+        <v>-29.25214563199997</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1376299176785961</v>
+      </c>
+      <c r="T62">
+        <v>2.148476471273828</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05864509021036457</v>
+      </c>
+      <c r="W62">
+        <v>0.2247955524577649</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4016787000709903</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1919292985460974</v>
+      </c>
+      <c r="C63">
+        <v>-452.1305943696223</v>
+      </c>
+      <c r="D63">
+        <v>444.2154056303777</v>
+      </c>
+      <c r="E63">
+        <v>516.6459999999998</v>
+      </c>
+      <c r="F63">
+        <v>1225.246</v>
+      </c>
+      <c r="G63">
+        <v>328.9</v>
+      </c>
+      <c r="H63">
+        <v>1300</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>233.4</v>
+      </c>
+      <c r="K63">
+        <v>117.8</v>
+      </c>
+      <c r="L63">
+        <v>115.6</v>
+      </c>
+      <c r="M63">
+        <v>292.5887448</v>
+      </c>
+      <c r="N63">
+        <v>-176.9887447999999</v>
+      </c>
+      <c r="O63">
+        <v>-25.84035674079999</v>
+      </c>
+      <c r="P63">
+        <v>-151.1483880592</v>
+      </c>
+      <c r="Q63">
+        <v>-33.34838805919996</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1401640181318934</v>
+      </c>
+      <c r="T63">
+        <v>2.203565611562901</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05768369528888317</v>
+      </c>
+      <c r="W63">
+        <v>0.2250251335650147</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.395093803348515</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1939292985460974</v>
+      </c>
+      <c r="C64">
+        <v>-477.9436286538438</v>
+      </c>
+      <c r="D64">
+        <v>438.4883713461561</v>
+      </c>
+      <c r="E64">
+        <v>536.7319999999999</v>
+      </c>
+      <c r="F64">
+        <v>1245.332</v>
+      </c>
+      <c r="G64">
+        <v>328.9</v>
+      </c>
+      <c r="H64">
+        <v>1300</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>233.4</v>
+      </c>
+      <c r="K64">
+        <v>117.8</v>
+      </c>
+      <c r="L64">
+        <v>115.6</v>
+      </c>
+      <c r="M64">
+        <v>297.3852816</v>
+      </c>
+      <c r="N64">
+        <v>-181.7852816</v>
+      </c>
+      <c r="O64">
+        <v>-26.54065111359999</v>
+      </c>
+      <c r="P64">
+        <v>-155.2446304864</v>
+      </c>
+      <c r="Q64">
+        <v>-37.44463048639996</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1428314922932591</v>
+      </c>
+      <c r="T64">
+        <v>2.261554180288241</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05675331310680441</v>
+      </c>
+      <c r="W64">
+        <v>0.2252473088300951</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3887213226493453</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1959292985460974</v>
+      </c>
+      <c r="C65">
+        <v>-503.6108713043673</v>
+      </c>
+      <c r="D65">
+        <v>432.9071286956327</v>
+      </c>
+      <c r="E65">
+        <v>556.8179999999999</v>
+      </c>
+      <c r="F65">
+        <v>1265.418</v>
+      </c>
+      <c r="G65">
+        <v>328.9</v>
+      </c>
+      <c r="H65">
+        <v>1300</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>233.4</v>
+      </c>
+      <c r="K65">
+        <v>117.8</v>
+      </c>
+      <c r="L65">
+        <v>115.6</v>
+      </c>
+      <c r="M65">
+        <v>302.1818184</v>
+      </c>
+      <c r="N65">
+        <v>-186.5818184</v>
+      </c>
+      <c r="O65">
+        <v>-27.24094548639999</v>
+      </c>
+      <c r="P65">
+        <v>-159.3408729136</v>
+      </c>
+      <c r="Q65">
+        <v>-41.54087291359998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1456431542471309</v>
+      </c>
+      <c r="T65">
+        <v>2.322677266241977</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05585246686701386</v>
+      </c>
+      <c r="W65">
+        <v>0.2254624309121571</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3825511429247526</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1979292985460974</v>
+      </c>
+      <c r="C66">
+        <v>-529.137819422042</v>
+      </c>
+      <c r="D66">
+        <v>427.466180577958</v>
+      </c>
+      <c r="E66">
+        <v>576.9039999999999</v>
+      </c>
+      <c r="F66">
+        <v>1285.504</v>
+      </c>
+      <c r="G66">
+        <v>328.9</v>
+      </c>
+      <c r="H66">
+        <v>1300</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>233.4</v>
+      </c>
+      <c r="K66">
+        <v>117.8</v>
+      </c>
+      <c r="L66">
+        <v>115.6</v>
+      </c>
+      <c r="M66">
+        <v>306.9783552</v>
+      </c>
+      <c r="N66">
+        <v>-191.3783552</v>
+      </c>
+      <c r="O66">
+        <v>-27.9412398592</v>
+      </c>
+      <c r="P66">
+        <v>-163.4371153408</v>
+      </c>
+      <c r="Q66">
+        <v>-45.63711534080001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1486110196428846</v>
+      </c>
+      <c r="T66">
+        <v>2.387196079193143</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05497977207221677</v>
+      </c>
+      <c r="W66">
+        <v>0.2256708304291547</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3765737813165533</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1999292985460974</v>
+      </c>
+      <c r="C67">
+        <v>-554.5296971790367</v>
+      </c>
+      <c r="D67">
+        <v>422.1603028209633</v>
+      </c>
+      <c r="E67">
+        <v>596.9899999999999</v>
+      </c>
+      <c r="F67">
+        <v>1305.59</v>
+      </c>
+      <c r="G67">
+        <v>328.9</v>
+      </c>
+      <c r="H67">
+        <v>1300</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>233.4</v>
+      </c>
+      <c r="K67">
+        <v>117.8</v>
+      </c>
+      <c r="L67">
+        <v>115.6</v>
+      </c>
+      <c r="M67">
+        <v>311.774892</v>
+      </c>
+      <c r="N67">
+        <v>-196.174892</v>
+      </c>
+      <c r="O67">
+        <v>-28.641534232</v>
+      </c>
+      <c r="P67">
+        <v>-167.533357768</v>
+      </c>
+      <c r="Q67">
+        <v>-49.733357768</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.151748477346967</v>
+      </c>
+      <c r="T67">
+        <v>2.455401681455804</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05413392942495189</v>
+      </c>
+      <c r="W67">
+        <v>0.2258728176533215</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3707803385270678</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2019292985460974</v>
+      </c>
+      <c r="C68">
+        <v>-579.7914725496599</v>
+      </c>
+      <c r="D68">
+        <v>416.98452745034</v>
+      </c>
+      <c r="E68">
+        <v>617.0759999999999</v>
+      </c>
+      <c r="F68">
+        <v>1325.676</v>
+      </c>
+      <c r="G68">
+        <v>328.9</v>
+      </c>
+      <c r="H68">
+        <v>1300</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>233.4</v>
+      </c>
+      <c r="K68">
+        <v>117.8</v>
+      </c>
+      <c r="L68">
+        <v>115.6</v>
+      </c>
+      <c r="M68">
+        <v>316.5714288</v>
+      </c>
+      <c r="N68">
+        <v>-200.9714288</v>
+      </c>
+      <c r="O68">
+        <v>-29.34182860479999</v>
+      </c>
+      <c r="P68">
+        <v>-171.6296001952</v>
+      </c>
+      <c r="Q68">
+        <v>-53.82960019519997</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1550704913865837</v>
+      </c>
+      <c r="T68">
+        <v>2.527619377969211</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0533137183730587</v>
+      </c>
+      <c r="W68">
+        <v>0.2260686840525136</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3651624546099911</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2039292985460974</v>
+      </c>
+      <c r="C69">
+        <v>-604.9278728253437</v>
+      </c>
+      <c r="D69">
+        <v>411.9341271746563</v>
+      </c>
+      <c r="E69">
+        <v>637.1619999999999</v>
+      </c>
+      <c r="F69">
+        <v>1345.762</v>
+      </c>
+      <c r="G69">
+        <v>328.9</v>
+      </c>
+      <c r="H69">
+        <v>1300</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>233.4</v>
+      </c>
+      <c r="K69">
+        <v>117.8</v>
+      </c>
+      <c r="L69">
+        <v>115.6</v>
+      </c>
+      <c r="M69">
+        <v>321.3679656</v>
+      </c>
+      <c r="N69">
+        <v>-205.7679656</v>
+      </c>
+      <c r="O69">
+        <v>-30.04212297759999</v>
+      </c>
+      <c r="P69">
+        <v>-175.7258426224</v>
+      </c>
+      <c r="Q69">
+        <v>-57.92584262239997</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1585938396104195</v>
+      </c>
+      <c r="T69">
+        <v>2.604213904574338</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05251799123316229</v>
+      </c>
+      <c r="W69">
+        <v>0.2262587036935209</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3597122687202897</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2059292985460974</v>
+      </c>
+      <c r="C70">
+        <v>-629.9433990156431</v>
+      </c>
+      <c r="D70">
+        <v>407.0046009843569</v>
+      </c>
+      <c r="E70">
+        <v>657.2479999999999</v>
+      </c>
+      <c r="F70">
+        <v>1365.848</v>
+      </c>
+      <c r="G70">
+        <v>328.9</v>
+      </c>
+      <c r="H70">
+        <v>1300</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>233.4</v>
+      </c>
+      <c r="K70">
+        <v>117.8</v>
+      </c>
+      <c r="L70">
+        <v>115.6</v>
+      </c>
+      <c r="M70">
+        <v>326.1645024</v>
+      </c>
+      <c r="N70">
+        <v>-210.5645024</v>
+      </c>
+      <c r="O70">
+        <v>-30.7424173504</v>
+      </c>
+      <c r="P70">
+        <v>-179.8220850496</v>
+      </c>
+      <c r="Q70">
+        <v>-62.02208504959999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1623373970982452</v>
+      </c>
+      <c r="T70">
+        <v>2.685595589092286</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05174566783267461</v>
+      </c>
+      <c r="W70">
+        <v>0.2264431345215573</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3544223824155796</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2079292985460974</v>
+      </c>
+      <c r="C71">
+        <v>-654.8423392274589</v>
+      </c>
+      <c r="D71">
+        <v>402.1916607725411</v>
+      </c>
+      <c r="E71">
+        <v>677.3339999999999</v>
+      </c>
+      <c r="F71">
+        <v>1385.934</v>
+      </c>
+      <c r="G71">
+        <v>328.9</v>
+      </c>
+      <c r="H71">
+        <v>1300</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>233.4</v>
+      </c>
+      <c r="K71">
+        <v>117.8</v>
+      </c>
+      <c r="L71">
+        <v>115.6</v>
+      </c>
+      <c r="M71">
+        <v>330.9610392</v>
+      </c>
+      <c r="N71">
+        <v>-215.3610392</v>
+      </c>
+      <c r="O71">
+        <v>-31.4427117232</v>
+      </c>
+      <c r="P71">
+        <v>-183.9183274768</v>
+      </c>
+      <c r="Q71">
+        <v>-66.11832747679999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.166322474423995</v>
+      </c>
+      <c r="T71">
+        <v>2.772227704869457</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05099573061770831</v>
+      </c>
+      <c r="W71">
+        <v>0.2266222195284913</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3492858261486871</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2099292985460974</v>
+      </c>
+      <c r="C72">
+        <v>-679.6287811060797</v>
+      </c>
+      <c r="D72">
+        <v>397.4912188939203</v>
+      </c>
+      <c r="E72">
+        <v>697.42</v>
+      </c>
+      <c r="F72">
+        <v>1406.02</v>
+      </c>
+      <c r="G72">
+        <v>328.9</v>
+      </c>
+      <c r="H72">
+        <v>1300</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>233.4</v>
+      </c>
+      <c r="K72">
+        <v>117.8</v>
+      </c>
+      <c r="L72">
+        <v>115.6</v>
+      </c>
+      <c r="M72">
+        <v>335.757576</v>
+      </c>
+      <c r="N72">
+        <v>-220.157576</v>
+      </c>
+      <c r="O72">
+        <v>-32.143006096</v>
+      </c>
+      <c r="P72">
+        <v>-188.014569904</v>
+      </c>
+      <c r="Q72">
+        <v>-70.21456990400002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1705732235714615</v>
+      </c>
+      <c r="T72">
+        <v>2.864635295031772</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05026722018031247</v>
+      </c>
+      <c r="W72">
+        <v>0.2267961878209414</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3442960286322773</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2119292985460974</v>
+      </c>
+      <c r="C73">
+        <v>-704.306623413903</v>
+      </c>
+      <c r="D73">
+        <v>392.8993765860967</v>
+      </c>
+      <c r="E73">
+        <v>717.5059999999997</v>
+      </c>
+      <c r="F73">
+        <v>1426.106</v>
+      </c>
+      <c r="G73">
+        <v>328.9</v>
+      </c>
+      <c r="H73">
+        <v>1300</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>233.4</v>
+      </c>
+      <c r="K73">
+        <v>117.8</v>
+      </c>
+      <c r="L73">
+        <v>115.6</v>
+      </c>
+      <c r="M73">
+        <v>340.5541128</v>
+      </c>
+      <c r="N73">
+        <v>-224.9541128</v>
+      </c>
+      <c r="O73">
+        <v>-32.8433004688</v>
+      </c>
+      <c r="P73">
+        <v>-192.1108123312</v>
+      </c>
+      <c r="Q73">
+        <v>-74.31081233119995</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1751171278325463</v>
+      </c>
+      <c r="T73">
+        <v>2.96341582244666</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04955923116368836</v>
+      </c>
+      <c r="W73">
+        <v>0.2269652555981112</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3394467887923861</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2139292985460974</v>
+      </c>
+      <c r="C74">
+        <v>-728.8795868157772</v>
+      </c>
+      <c r="D74">
+        <v>388.4124131842226</v>
+      </c>
+      <c r="E74">
+        <v>737.5919999999998</v>
+      </c>
+      <c r="F74">
+        <v>1446.192</v>
+      </c>
+      <c r="G74">
+        <v>328.9</v>
+      </c>
+      <c r="H74">
+        <v>1300</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>233.4</v>
+      </c>
+      <c r="K74">
+        <v>117.8</v>
+      </c>
+      <c r="L74">
+        <v>115.6</v>
+      </c>
+      <c r="M74">
+        <v>345.3506495999999</v>
+      </c>
+      <c r="N74">
+        <v>-229.7506495999999</v>
+      </c>
+      <c r="O74">
+        <v>-33.54359484159998</v>
+      </c>
+      <c r="P74">
+        <v>-196.2070547583999</v>
+      </c>
+      <c r="Q74">
+        <v>-78.40705475839992</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1799855966837087</v>
+      </c>
+      <c r="T74">
+        <v>3.069252101819754</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04887090850863714</v>
+      </c>
+      <c r="W74">
+        <v>0.2271296270481375</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3347322500591585</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2159292985460974</v>
+      </c>
+      <c r="C75">
+        <v>-753.3512239336607</v>
+      </c>
+      <c r="D75">
+        <v>384.0267760663392</v>
+      </c>
+      <c r="E75">
+        <v>757.6779999999998</v>
+      </c>
+      <c r="F75">
+        <v>1466.278</v>
+      </c>
+      <c r="G75">
+        <v>328.9</v>
+      </c>
+      <c r="H75">
+        <v>1300</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>233.4</v>
+      </c>
+      <c r="K75">
+        <v>117.8</v>
+      </c>
+      <c r="L75">
+        <v>115.6</v>
+      </c>
+      <c r="M75">
+        <v>350.1471864</v>
+      </c>
+      <c r="N75">
+        <v>-234.5471863999999</v>
+      </c>
+      <c r="O75">
+        <v>-34.24388921439999</v>
+      </c>
+      <c r="P75">
+        <v>-200.3032971855999</v>
+      </c>
+      <c r="Q75">
+        <v>-82.50329718559995</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1852146928571794</v>
+      </c>
+      <c r="T75">
+        <v>3.182928105590857</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04820144400851882</v>
+      </c>
+      <c r="W75">
+        <v>0.2272894951707657</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3301468767706769</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2179292985460974</v>
+      </c>
+      <c r="C76">
+        <v>-777.7249287277207</v>
+      </c>
+      <c r="D76">
+        <v>379.7390712722792</v>
+      </c>
+      <c r="E76">
+        <v>777.7639999999998</v>
+      </c>
+      <c r="F76">
+        <v>1486.364</v>
+      </c>
+      <c r="G76">
+        <v>328.9</v>
+      </c>
+      <c r="H76">
+        <v>1300</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>233.4</v>
+      </c>
+      <c r="K76">
+        <v>117.8</v>
+      </c>
+      <c r="L76">
+        <v>115.6</v>
+      </c>
+      <c r="M76">
+        <v>354.9437232</v>
+      </c>
+      <c r="N76">
+        <v>-239.3437231999999</v>
+      </c>
+      <c r="O76">
+        <v>-34.94418358719999</v>
+      </c>
+      <c r="P76">
+        <v>-204.3995396128</v>
+      </c>
+      <c r="Q76">
+        <v>-86.59953961279997</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1908460271978401</v>
+      </c>
+      <c r="T76">
+        <v>3.305348417344351</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04755007314353884</v>
+      </c>
+      <c r="W76">
+        <v>0.2274450425333229</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.325685432489992</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2199292985460974</v>
+      </c>
+      <c r="C77">
+        <v>-802.003945255918</v>
+      </c>
+      <c r="D77">
+        <v>375.5460547440819</v>
+      </c>
+      <c r="E77">
+        <v>797.8499999999998</v>
+      </c>
+      <c r="F77">
+        <v>1506.45</v>
+      </c>
+      <c r="G77">
+        <v>328.9</v>
+      </c>
+      <c r="H77">
+        <v>1300</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>233.4</v>
+      </c>
+      <c r="K77">
+        <v>117.8</v>
+      </c>
+      <c r="L77">
+        <v>115.6</v>
+      </c>
+      <c r="M77">
+        <v>359.74026</v>
+      </c>
+      <c r="N77">
+        <v>-244.14026</v>
+      </c>
+      <c r="O77">
+        <v>-35.64447795999999</v>
+      </c>
+      <c r="P77">
+        <v>-208.49578204</v>
+      </c>
+      <c r="Q77">
+        <v>-90.69578203999997</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1969278682857538</v>
+      </c>
+      <c r="T77">
+        <v>3.437562354038126</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04691607216829165</v>
+      </c>
+      <c r="W77">
+        <v>0.227596441966212</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3213429600567922</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2219292985460974</v>
+      </c>
+      <c r="C78">
+        <v>-826.1913758596024</v>
+      </c>
+      <c r="D78">
+        <v>371.4446241403977</v>
+      </c>
+      <c r="E78">
+        <v>817.936</v>
+      </c>
+      <c r="F78">
+        <v>1526.536</v>
+      </c>
+      <c r="G78">
+        <v>328.9</v>
+      </c>
+      <c r="H78">
+        <v>1300</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>233.4</v>
+      </c>
+      <c r="K78">
+        <v>117.8</v>
+      </c>
+      <c r="L78">
+        <v>115.6</v>
+      </c>
+      <c r="M78">
+        <v>364.5367968</v>
+      </c>
+      <c r="N78">
+        <v>-248.9367968</v>
+      </c>
+      <c r="O78">
+        <v>-36.3447723328</v>
+      </c>
+      <c r="P78">
+        <v>-212.5920244672</v>
+      </c>
+      <c r="Q78">
+        <v>-94.79202446720002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2035165294643269</v>
+      </c>
+      <c r="T78">
+        <v>3.580794118789715</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04629875542923517</v>
+      </c>
+      <c r="W78">
+        <v>0.2277438572034987</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3171147632139396</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2239292985460974</v>
+      </c>
+      <c r="C79">
+        <v>-850.2901888185183</v>
+      </c>
+      <c r="D79">
+        <v>367.4318111814817</v>
+      </c>
+      <c r="E79">
+        <v>838.022</v>
+      </c>
+      <c r="F79">
+        <v>1546.622</v>
+      </c>
+      <c r="G79">
+        <v>328.9</v>
+      </c>
+      <c r="H79">
+        <v>1300</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>233.4</v>
+      </c>
+      <c r="K79">
+        <v>117.8</v>
+      </c>
+      <c r="L79">
+        <v>115.6</v>
+      </c>
+      <c r="M79">
+        <v>369.3333336000001</v>
+      </c>
+      <c r="N79">
+        <v>-253.7333336</v>
+      </c>
+      <c r="O79">
+        <v>-37.0450667056</v>
+      </c>
+      <c r="P79">
+        <v>-216.6882668944</v>
+      </c>
+      <c r="Q79">
+        <v>-98.88826689440005</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2106781177019063</v>
+      </c>
+      <c r="T79">
+        <v>3.736480819606658</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04569747289119315</v>
+      </c>
+      <c r="W79">
+        <v>0.2278874434735831</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3129963896657066</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2259292985460974</v>
+      </c>
+      <c r="C80">
+        <v>-874.3032255149228</v>
+      </c>
+      <c r="D80">
+        <v>363.5047744850773</v>
+      </c>
+      <c r="E80">
+        <v>858.1080000000001</v>
+      </c>
+      <c r="F80">
+        <v>1566.708</v>
+      </c>
+      <c r="G80">
+        <v>328.9</v>
+      </c>
+      <c r="H80">
+        <v>1300</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>233.4</v>
+      </c>
+      <c r="K80">
+        <v>117.8</v>
+      </c>
+      <c r="L80">
+        <v>115.6</v>
+      </c>
+      <c r="M80">
+        <v>374.1298704</v>
+      </c>
+      <c r="N80">
+        <v>-258.5298704</v>
+      </c>
+      <c r="O80">
+        <v>-37.74536107839999</v>
+      </c>
+      <c r="P80">
+        <v>-220.7845093216</v>
+      </c>
+      <c r="Q80">
+        <v>-102.9845093216</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2184907594156293</v>
+      </c>
+      <c r="T80">
+        <v>3.906320856861507</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04511160785412658</v>
+      </c>
+      <c r="W80">
+        <v>0.2280273480444346</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3089836154392233</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2279292985460974</v>
+      </c>
+      <c r="C81">
+        <v>-898.2332071431472</v>
+      </c>
+      <c r="D81">
+        <v>359.660792856853</v>
+      </c>
+      <c r="E81">
+        <v>878.1940000000001</v>
+      </c>
+      <c r="F81">
+        <v>1586.794</v>
+      </c>
+      <c r="G81">
+        <v>328.9</v>
+      </c>
+      <c r="H81">
+        <v>1300</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>233.4</v>
+      </c>
+      <c r="K81">
+        <v>117.8</v>
+      </c>
+      <c r="L81">
+        <v>115.6</v>
+      </c>
+      <c r="M81">
+        <v>378.9264072</v>
+      </c>
+      <c r="N81">
+        <v>-263.3264072</v>
+      </c>
+      <c r="O81">
+        <v>-38.4456554512</v>
+      </c>
+      <c r="P81">
+        <v>-224.8807517488</v>
+      </c>
+      <c r="Q81">
+        <v>-107.0807517488</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.227047462244945</v>
+      </c>
+      <c r="T81">
+        <v>4.092336135759674</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04454057484331485</v>
+      </c>
+      <c r="W81">
+        <v>0.2281637107274164</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3050724304336634</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2299292985460974</v>
+      </c>
+      <c r="C82">
+        <v>-922.0827409979015</v>
+      </c>
+      <c r="D82">
+        <v>355.8972590020986</v>
+      </c>
+      <c r="E82">
+        <v>898.2800000000001</v>
+      </c>
+      <c r="F82">
+        <v>1606.88</v>
+      </c>
+      <c r="G82">
+        <v>328.9</v>
+      </c>
+      <c r="H82">
+        <v>1300</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>233.4</v>
+      </c>
+      <c r="K82">
+        <v>117.8</v>
+      </c>
+      <c r="L82">
+        <v>115.6</v>
+      </c>
+      <c r="M82">
+        <v>383.722944</v>
+      </c>
+      <c r="N82">
+        <v>-268.122944</v>
+      </c>
+      <c r="O82">
+        <v>-39.145949824</v>
+      </c>
+      <c r="P82">
+        <v>-228.976994176</v>
+      </c>
+      <c r="Q82">
+        <v>-111.176994176</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2364598353571923</v>
+      </c>
+      <c r="T82">
+        <v>4.296952942547658</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04398381765777341</v>
+      </c>
+      <c r="W82">
+        <v>0.2282966643433237</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3012590250532426</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2319292985460975</v>
+      </c>
+      <c r="C83">
+        <v>-945.8543263718592</v>
+      </c>
+      <c r="D83">
+        <v>352.2116736281409</v>
+      </c>
+      <c r="E83">
+        <v>918.3660000000001</v>
+      </c>
+      <c r="F83">
+        <v>1626.966</v>
+      </c>
+      <c r="G83">
+        <v>328.9</v>
+      </c>
+      <c r="H83">
+        <v>1300</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>233.4</v>
+      </c>
+      <c r="K83">
+        <v>117.8</v>
+      </c>
+      <c r="L83">
+        <v>115.6</v>
+      </c>
+      <c r="M83">
+        <v>388.5194808000001</v>
+      </c>
+      <c r="N83">
+        <v>-272.9194808</v>
+      </c>
+      <c r="O83">
+        <v>-39.8462441968</v>
+      </c>
+      <c r="P83">
+        <v>-233.0732366032</v>
+      </c>
+      <c r="Q83">
+        <v>-115.2732366032</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2468629845865182</v>
+      </c>
+      <c r="T83">
+        <v>4.523108360576482</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04344080756323299</v>
+      </c>
+      <c r="W83">
+        <v>0.2284263351539</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.297539777830363</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2339292985460975</v>
+      </c>
+      <c r="C84">
+        <v>-969.550360090552</v>
+      </c>
+      <c r="D84">
+        <v>348.6016399094481</v>
+      </c>
+      <c r="E84">
+        <v>938.4520000000001</v>
+      </c>
+      <c r="F84">
+        <v>1647.052</v>
+      </c>
+      <c r="G84">
+        <v>328.9</v>
+      </c>
+      <c r="H84">
+        <v>1300</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>233.4</v>
+      </c>
+      <c r="K84">
+        <v>117.8</v>
+      </c>
+      <c r="L84">
+        <v>115.6</v>
+      </c>
+      <c r="M84">
+        <v>393.3160176000001</v>
+      </c>
+      <c r="N84">
+        <v>-277.7160176</v>
+      </c>
+      <c r="O84">
+        <v>-40.5465385696</v>
+      </c>
+      <c r="P84">
+        <v>-237.1694790304001</v>
+      </c>
+      <c r="Q84">
+        <v>-119.3694790304001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2584220392857692</v>
+      </c>
+      <c r="T84">
+        <v>4.774392158386287</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04291104161733992</v>
+      </c>
+      <c r="W84">
+        <v>0.2285528432617792</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2939112439543831</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2359292985460975</v>
+      </c>
+      <c r="C85">
+        <v>-993.1731417103368</v>
+      </c>
+      <c r="D85">
+        <v>345.0648582896633</v>
+      </c>
+      <c r="E85">
+        <v>958.5380000000001</v>
+      </c>
+      <c r="F85">
+        <v>1667.138</v>
+      </c>
+      <c r="G85">
+        <v>328.9</v>
+      </c>
+      <c r="H85">
+        <v>1300</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>233.4</v>
+      </c>
+      <c r="K85">
+        <v>117.8</v>
+      </c>
+      <c r="L85">
+        <v>115.6</v>
+      </c>
+      <c r="M85">
+        <v>398.1125544000001</v>
+      </c>
+      <c r="N85">
+        <v>-282.5125544000001</v>
+      </c>
+      <c r="O85">
+        <v>-41.2468329424</v>
+      </c>
+      <c r="P85">
+        <v>-241.2657214576001</v>
+      </c>
+      <c r="Q85">
+        <v>-123.4657214576001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2713409827731674</v>
+      </c>
+      <c r="T85">
+        <v>5.055238755938422</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04239404111592617</v>
+      </c>
+      <c r="W85">
+        <v>0.2286763029815168</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2903701446296314</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2379292985460974</v>
+      </c>
+      <c r="C86">
+        <v>-1016.724878403119</v>
+      </c>
+      <c r="D86">
+        <v>341.5991215968808</v>
+      </c>
+      <c r="E86">
+        <v>978.6239999999999</v>
+      </c>
+      <c r="F86">
+        <v>1687.224</v>
+      </c>
+      <c r="G86">
+        <v>328.9</v>
+      </c>
+      <c r="H86">
+        <v>1300</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>233.4</v>
+      </c>
+      <c r="K86">
+        <v>117.8</v>
+      </c>
+      <c r="L86">
+        <v>115.6</v>
+      </c>
+      <c r="M86">
+        <v>402.9090912</v>
+      </c>
+      <c r="N86">
+        <v>-287.3090912</v>
+      </c>
+      <c r="O86">
+        <v>-41.94712731519999</v>
+      </c>
+      <c r="P86">
+        <v>-245.3619638848</v>
+      </c>
+      <c r="Q86">
+        <v>-127.5619638848</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2858747941964903</v>
+      </c>
+      <c r="T86">
+        <v>5.371191178184571</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0418893501502604</v>
+      </c>
+      <c r="W86">
+        <v>0.2287968231841178</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2869133571935645</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2399292985460974</v>
+      </c>
+      <c r="C87">
+        <v>-1040.207689549643</v>
+      </c>
+      <c r="D87">
+        <v>338.2023104503576</v>
+      </c>
+      <c r="E87">
+        <v>998.7099999999999</v>
+      </c>
+      <c r="F87">
+        <v>1707.31</v>
+      </c>
+      <c r="G87">
+        <v>328.9</v>
+      </c>
+      <c r="H87">
+        <v>1300</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>233.4</v>
+      </c>
+      <c r="K87">
+        <v>117.8</v>
+      </c>
+      <c r="L87">
+        <v>115.6</v>
+      </c>
+      <c r="M87">
+        <v>407.705628</v>
+      </c>
+      <c r="N87">
+        <v>-292.105628</v>
+      </c>
+      <c r="O87">
+        <v>-42.64742168799999</v>
+      </c>
+      <c r="P87">
+        <v>-249.458206312</v>
+      </c>
+      <c r="Q87">
+        <v>-131.6582063119999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.302346447142923</v>
+      </c>
+      <c r="T87">
+        <v>5.729270590063543</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04139653426613969</v>
+      </c>
+      <c r="W87">
+        <v>0.2289145076172459</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2835379059324636</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2419292985460974</v>
+      </c>
+      <c r="C88">
+        <v>-1063.623611061419</v>
+      </c>
+      <c r="D88">
+        <v>334.8723889385809</v>
+      </c>
+      <c r="E88">
+        <v>1018.796</v>
+      </c>
+      <c r="F88">
+        <v>1727.396</v>
+      </c>
+      <c r="G88">
+        <v>328.9</v>
+      </c>
+      <c r="H88">
+        <v>1300</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>233.4</v>
+      </c>
+      <c r="K88">
+        <v>117.8</v>
+      </c>
+      <c r="L88">
+        <v>115.6</v>
+      </c>
+      <c r="M88">
+        <v>412.5021648</v>
+      </c>
+      <c r="N88">
+        <v>-296.9021648</v>
+      </c>
+      <c r="O88">
+        <v>-43.3477160608</v>
+      </c>
+      <c r="P88">
+        <v>-253.5544487392</v>
+      </c>
+      <c r="Q88">
+        <v>-135.7544487392</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3211711933674174</v>
+      </c>
+      <c r="T88">
+        <v>6.138504203639509</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04091517921653341</v>
+      </c>
+      <c r="W88">
+        <v>0.2290294552030918</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2802409535379001</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2439292985460974</v>
+      </c>
+      <c r="C89">
+        <v>-1086.974599449836</v>
+      </c>
+      <c r="D89">
+        <v>331.6074005501638</v>
+      </c>
+      <c r="E89">
+        <v>1038.882</v>
+      </c>
+      <c r="F89">
+        <v>1747.482</v>
+      </c>
+      <c r="G89">
+        <v>328.9</v>
+      </c>
+      <c r="H89">
+        <v>1300</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>233.4</v>
+      </c>
+      <c r="K89">
+        <v>117.8</v>
+      </c>
+      <c r="L89">
+        <v>115.6</v>
+      </c>
+      <c r="M89">
+        <v>417.2987016</v>
+      </c>
+      <c r="N89">
+        <v>-301.6987016</v>
+      </c>
+      <c r="O89">
+        <v>-44.0480104336</v>
+      </c>
+      <c r="P89">
+        <v>-257.6506911664</v>
+      </c>
+      <c r="Q89">
+        <v>-139.8506911664</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3428920543956803</v>
+      </c>
+      <c r="T89">
+        <v>6.610696834688703</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04044488980025142</v>
+      </c>
+      <c r="W89">
+        <v>0.2291417603157</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.277019793152407</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2459292985460974</v>
+      </c>
+      <c r="C90">
+        <v>-1110.262535659516</v>
+      </c>
+      <c r="D90">
+        <v>328.4054643404841</v>
+      </c>
+      <c r="E90">
+        <v>1058.968</v>
+      </c>
+      <c r="F90">
+        <v>1767.568</v>
+      </c>
+      <c r="G90">
+        <v>328.9</v>
+      </c>
+      <c r="H90">
+        <v>1300</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>233.4</v>
+      </c>
+      <c r="K90">
+        <v>117.8</v>
+      </c>
+      <c r="L90">
+        <v>115.6</v>
+      </c>
+      <c r="M90">
+        <v>422.0952384</v>
+      </c>
+      <c r="N90">
+        <v>-306.4952384</v>
+      </c>
+      <c r="O90">
+        <v>-44.7483048064</v>
+      </c>
+      <c r="P90">
+        <v>-261.7469335936</v>
+      </c>
+      <c r="Q90">
+        <v>-143.9469335936</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3682330589286537</v>
+      </c>
+      <c r="T90">
+        <v>7.161588237579429</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03998528877979401</v>
+      </c>
+      <c r="W90">
+        <v>0.2292515130393852</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2738718409574933</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2479292985460974</v>
+      </c>
+      <c r="C91">
+        <v>-1133.489228681714</v>
+      </c>
+      <c r="D91">
+        <v>325.2647713182856</v>
+      </c>
+      <c r="E91">
+        <v>1079.054</v>
+      </c>
+      <c r="F91">
+        <v>1787.654</v>
+      </c>
+      <c r="G91">
+        <v>328.9</v>
+      </c>
+      <c r="H91">
+        <v>1300</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>233.4</v>
+      </c>
+      <c r="K91">
+        <v>117.8</v>
+      </c>
+      <c r="L91">
+        <v>115.6</v>
+      </c>
+      <c r="M91">
+        <v>426.8917752</v>
+      </c>
+      <c r="N91">
+        <v>-311.2917752</v>
+      </c>
+      <c r="O91">
+        <v>-45.4485991792</v>
+      </c>
+      <c r="P91">
+        <v>-265.8431760208</v>
+      </c>
+      <c r="Q91">
+        <v>-148.0431760208</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3981815188312586</v>
+      </c>
+      <c r="T91">
+        <v>7.812641713723013</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03953601587215588</v>
+      </c>
+      <c r="W91">
+        <v>0.2293587994097292</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2707946292613417</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2499292985460974</v>
+      </c>
+      <c r="C92">
+        <v>-1156.656418962345</v>
+      </c>
+      <c r="D92">
+        <v>322.1835810376554</v>
+      </c>
+      <c r="E92">
+        <v>1099.14</v>
+      </c>
+      <c r="F92">
+        <v>1807.74</v>
+      </c>
+      <c r="G92">
+        <v>328.9</v>
+      </c>
+      <c r="H92">
+        <v>1300</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>233.4</v>
+      </c>
+      <c r="K92">
+        <v>117.8</v>
+      </c>
+      <c r="L92">
+        <v>115.6</v>
+      </c>
+      <c r="M92">
+        <v>431.688312</v>
+      </c>
+      <c r="N92">
+        <v>-316.088312</v>
+      </c>
+      <c r="O92">
+        <v>-46.14889355199999</v>
+      </c>
+      <c r="P92">
+        <v>-269.939418448</v>
+      </c>
+      <c r="Q92">
+        <v>-152.139418448</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4341196707143845</v>
+      </c>
+      <c r="T92">
+        <v>8.593905885095316</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0390967268069097</v>
+      </c>
+      <c r="W92">
+        <v>0.22946370163851</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2677858000473268</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2519292985460974</v>
+      </c>
+      <c r="C93">
+        <v>-1179.765781618118</v>
+      </c>
+      <c r="D93">
+        <v>319.1602183818824</v>
+      </c>
+      <c r="E93">
+        <v>1119.226</v>
+      </c>
+      <c r="F93">
+        <v>1827.826</v>
+      </c>
+      <c r="G93">
+        <v>328.9</v>
+      </c>
+      <c r="H93">
+        <v>1300</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>233.4</v>
+      </c>
+      <c r="K93">
+        <v>117.8</v>
+      </c>
+      <c r="L93">
+        <v>115.6</v>
+      </c>
+      <c r="M93">
+        <v>436.4848488</v>
+      </c>
+      <c r="N93">
+        <v>-320.8848488</v>
+      </c>
+      <c r="O93">
+        <v>-46.84918792479999</v>
+      </c>
+      <c r="P93">
+        <v>-274.0356608752</v>
+      </c>
+      <c r="Q93">
+        <v>-156.2356608752</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4780440785715384</v>
+      </c>
+      <c r="T93">
+        <v>9.548784316772574</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03866709244639421</v>
+      </c>
+      <c r="W93">
+        <v>0.2295662983238011</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2648430989479056</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2539292985460974</v>
+      </c>
+      <c r="C94">
+        <v>-1202.818929473281</v>
+      </c>
+      <c r="D94">
+        <v>316.1930705267195</v>
+      </c>
+      <c r="E94">
+        <v>1139.312</v>
+      </c>
+      <c r="F94">
+        <v>1847.912</v>
+      </c>
+      <c r="G94">
+        <v>328.9</v>
+      </c>
+      <c r="H94">
+        <v>1300</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>233.4</v>
+      </c>
+      <c r="K94">
+        <v>117.8</v>
+      </c>
+      <c r="L94">
+        <v>115.6</v>
+      </c>
+      <c r="M94">
+        <v>441.2813856</v>
+      </c>
+      <c r="N94">
+        <v>-325.6813856</v>
+      </c>
+      <c r="O94">
+        <v>-47.54948229759999</v>
+      </c>
+      <c r="P94">
+        <v>-278.1319033024</v>
+      </c>
+      <c r="Q94">
+        <v>-160.3319033024</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5329495883929809</v>
+      </c>
+      <c r="T94">
+        <v>10.74238235636915</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03824679796328123</v>
+      </c>
+      <c r="W94">
+        <v>0.2296666646463685</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2619643696115154</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2559292985460974</v>
+      </c>
+      <c r="C95">
+        <v>-1225.817415928531</v>
+      </c>
+      <c r="D95">
+        <v>313.2805840714694</v>
+      </c>
+      <c r="E95">
+        <v>1159.398</v>
+      </c>
+      <c r="F95">
+        <v>1867.998</v>
+      </c>
+      <c r="G95">
+        <v>328.9</v>
+      </c>
+      <c r="H95">
+        <v>1300</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>233.4</v>
+      </c>
+      <c r="K95">
+        <v>117.8</v>
+      </c>
+      <c r="L95">
+        <v>115.6</v>
+      </c>
+      <c r="M95">
+        <v>446.0779224</v>
+      </c>
+      <c r="N95">
+        <v>-330.4779224</v>
+      </c>
+      <c r="O95">
+        <v>-48.2497766704</v>
+      </c>
+      <c r="P95">
+        <v>-282.2281457296</v>
+      </c>
+      <c r="Q95">
+        <v>-164.4281457296</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6035423867348353</v>
+      </c>
+      <c r="T95">
+        <v>12.27700840727903</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03783554207120293</v>
+      </c>
+      <c r="W95">
+        <v>0.2297648725533968</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2591475484328969</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2579292985460975</v>
+      </c>
+      <c r="C96">
+        <v>-1248.762737672816</v>
+      </c>
+      <c r="D96">
+        <v>310.4212623271837</v>
+      </c>
+      <c r="E96">
+        <v>1179.484</v>
+      </c>
+      <c r="F96">
+        <v>1888.084</v>
+      </c>
+      <c r="G96">
+        <v>328.9</v>
+      </c>
+      <c r="H96">
+        <v>1300</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>233.4</v>
+      </c>
+      <c r="K96">
+        <v>117.8</v>
+      </c>
+      <c r="L96">
+        <v>115.6</v>
+      </c>
+      <c r="M96">
+        <v>450.8744592</v>
+      </c>
+      <c r="N96">
+        <v>-335.2744592</v>
+      </c>
+      <c r="O96">
+        <v>-48.9500710432</v>
+      </c>
+      <c r="P96">
+        <v>-286.3243881568</v>
+      </c>
+      <c r="Q96">
+        <v>-168.5243881568</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.697666117857308</v>
+      </c>
+      <c r="T96">
+        <v>14.32317647515887</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03743303630448801</v>
+      </c>
+      <c r="W96">
+        <v>0.2298609909304883</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2563906596197809</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2599292985460974</v>
+      </c>
+      <c r="C97">
+        <v>-1271.65633724798</v>
+      </c>
+      <c r="D97">
+        <v>307.6136627520195</v>
+      </c>
+      <c r="E97">
+        <v>1199.57</v>
+      </c>
+      <c r="F97">
+        <v>1908.17</v>
+      </c>
+      <c r="G97">
+        <v>328.9</v>
+      </c>
+      <c r="H97">
+        <v>1300</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>233.4</v>
+      </c>
+      <c r="K97">
+        <v>117.8</v>
+      </c>
+      <c r="L97">
+        <v>115.6</v>
+      </c>
+      <c r="M97">
+        <v>455.6709960000001</v>
+      </c>
+      <c r="N97">
+        <v>-340.070996</v>
+      </c>
+      <c r="O97">
+        <v>-49.650365416</v>
+      </c>
+      <c r="P97">
+        <v>-290.420630584</v>
+      </c>
+      <c r="Q97">
+        <v>-172.620630584</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8294393414287702</v>
+      </c>
+      <c r="T97">
+        <v>17.18781177019066</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03703900434338814</v>
+      </c>
+      <c r="W97">
+        <v>0.2299550857627989</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2536918105711516</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2619292985460974</v>
+      </c>
+      <c r="C98">
+        <v>-1294.499605475474</v>
+      </c>
+      <c r="D98">
+        <v>304.8563945245262</v>
+      </c>
+      <c r="E98">
+        <v>1219.656</v>
+      </c>
+      <c r="F98">
+        <v>1928.256</v>
+      </c>
+      <c r="G98">
+        <v>328.9</v>
+      </c>
+      <c r="H98">
+        <v>1300</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>233.4</v>
+      </c>
+      <c r="K98">
+        <v>117.8</v>
+      </c>
+      <c r="L98">
+        <v>115.6</v>
+      </c>
+      <c r="M98">
+        <v>460.4675328</v>
+      </c>
+      <c r="N98">
+        <v>-344.8675328</v>
+      </c>
+      <c r="O98">
+        <v>-50.35065978879999</v>
+      </c>
+      <c r="P98">
+        <v>-294.5168730112</v>
+      </c>
+      <c r="Q98">
+        <v>-176.7168730112</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.02709917678596</v>
+      </c>
+      <c r="T98">
+        <v>21.48476471273827</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03665318138147785</v>
+      </c>
+      <c r="W98">
+        <v>0.2300472202861031</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2510491875443689</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2639292985460974</v>
+      </c>
+      <c r="C99">
+        <v>-1317.293883753719</v>
+      </c>
+      <c r="D99">
+        <v>302.1481162462806</v>
+      </c>
+      <c r="E99">
+        <v>1239.742</v>
+      </c>
+      <c r="F99">
+        <v>1948.342</v>
+      </c>
+      <c r="G99">
+        <v>328.9</v>
+      </c>
+      <c r="H99">
+        <v>1300</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>233.4</v>
+      </c>
+      <c r="K99">
+        <v>117.8</v>
+      </c>
+      <c r="L99">
+        <v>115.6</v>
+      </c>
+      <c r="M99">
+        <v>465.2640696</v>
+      </c>
+      <c r="N99">
+        <v>-349.6640695999999</v>
+      </c>
+      <c r="O99">
+        <v>-51.05095416159999</v>
+      </c>
+      <c r="P99">
+        <v>-298.6131154384</v>
+      </c>
+      <c r="Q99">
+        <v>-180.8131154384</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.356532235714614</v>
+      </c>
+      <c r="T99">
+        <v>28.64635295031769</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03627531353218427</v>
+      </c>
+      <c r="W99">
+        <v>0.2301374551285144</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2484610515903032</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2659292985460974</v>
+      </c>
+      <c r="C100">
+        <v>-1340.040466234098</v>
+      </c>
+      <c r="D100">
+        <v>299.4875337659014</v>
+      </c>
+      <c r="E100">
+        <v>1259.828</v>
+      </c>
+      <c r="F100">
+        <v>1968.428</v>
+      </c>
+      <c r="G100">
+        <v>328.9</v>
+      </c>
+      <c r="H100">
+        <v>1300</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>233.4</v>
+      </c>
+      <c r="K100">
+        <v>117.8</v>
+      </c>
+      <c r="L100">
+        <v>115.6</v>
+      </c>
+      <c r="M100">
+        <v>470.0606064</v>
+      </c>
+      <c r="N100">
+        <v>-354.4606064</v>
+      </c>
+      <c r="O100">
+        <v>-51.75124853439999</v>
+      </c>
+      <c r="P100">
+        <v>-302.7093578655999</v>
+      </c>
+      <c r="Q100">
+        <v>-184.9093578655999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.015398353571921</v>
+      </c>
+      <c r="T100">
+        <v>42.96952942547654</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03590515727165177</v>
+      </c>
+      <c r="W100">
+        <v>0.2302258484435296</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2459257347373409</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2679292985460974</v>
+      </c>
+      <c r="C101">
+        <v>-1362.740601882977</v>
+      </c>
+      <c r="D101">
+        <v>296.8733981170232</v>
+      </c>
+      <c r="E101">
+        <v>1279.914</v>
+      </c>
+      <c r="F101">
+        <v>1988.514</v>
+      </c>
+      <c r="G101">
+        <v>328.9</v>
+      </c>
+      <c r="H101">
+        <v>1300</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>233.4</v>
+      </c>
+      <c r="K101">
+        <v>117.8</v>
+      </c>
+      <c r="L101">
+        <v>115.6</v>
+      </c>
+      <c r="M101">
+        <v>474.8571432</v>
+      </c>
+      <c r="N101">
+        <v>-359.2571432</v>
+      </c>
+      <c r="O101">
+        <v>-52.45154290719999</v>
+      </c>
+      <c r="P101">
+        <v>-306.8056002928</v>
+      </c>
+      <c r="Q101">
+        <v>-189.0056002928</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.991996707143842</v>
+      </c>
+      <c r="T101">
+        <v>85.93905885095307</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03554247891537246</v>
+      </c>
+      <c r="W101">
+        <v>0.2303124560350091</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2434416364066607</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_aerospace_defense.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08436873256272705</v>
+        <v>0.08428398421318546</v>
       </c>
       <c r="C2">
-        <v>1462.906893505983</v>
+        <v>1449.840447534943</v>
       </c>
       <c r="D2">
-        <v>1332.906893505983</v>
+        <v>1334.801447534943</v>
       </c>
       <c r="E2">
-        <v>-516.2</v>
+        <v>-501.239</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.961</v>
       </c>
       <c r="G2">
         <v>130</v>
@@ -1433,28 +1433,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7525382999999999</v>
       </c>
       <c r="N2">
-        <v>186.9333333333334</v>
+        <v>186.1807950333334</v>
       </c>
       <c r="O2">
-        <v>27.29226666666667</v>
+        <v>27.18239607486667</v>
       </c>
       <c r="P2">
-        <v>159.6410666666667</v>
+        <v>158.9983989584667</v>
       </c>
       <c r="Q2">
-        <v>268.5410666666667</v>
+        <v>267.8983989584667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08436873256272705</v>
+        <v>0.08470143657897522</v>
       </c>
       <c r="T2">
-        <v>0.890732853642657</v>
+        <v>0.8984165491680188</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>248.4037468037619</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08428398421318546</v>
+        <v>0.08419923586364388</v>
       </c>
       <c r="C3">
-        <v>1449.840447534943</v>
+        <v>1436.779394954877</v>
       </c>
       <c r="D3">
-        <v>1334.801447534943</v>
+        <v>1336.701394954878</v>
       </c>
       <c r="E3">
-        <v>-501.239</v>
+        <v>-486.278</v>
       </c>
       <c r="F3">
-        <v>14.961</v>
+        <v>29.922</v>
       </c>
       <c r="G3">
         <v>130</v>
@@ -1515,28 +1515,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M3">
-        <v>0.7525382999999999</v>
+        <v>1.5050766</v>
       </c>
       <c r="N3">
-        <v>186.1807950333334</v>
+        <v>185.4282567333334</v>
       </c>
       <c r="O3">
-        <v>27.18239607486667</v>
+        <v>27.07252548306667</v>
       </c>
       <c r="P3">
-        <v>158.9983989584667</v>
+        <v>158.3557312502667</v>
       </c>
       <c r="Q3">
-        <v>267.8983989584667</v>
+        <v>267.2557312502667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08470143657897522</v>
+        <v>0.085040930473106</v>
       </c>
       <c r="T3">
-        <v>0.8984165491680188</v>
+        <v>0.9062570548061432</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>248.4037468037619</v>
+        <v>124.2018734018809</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08419923586364388</v>
+        <v>0.08411448751410229</v>
       </c>
       <c r="C4">
-        <v>1436.779394954877</v>
+        <v>1423.723758829363</v>
       </c>
       <c r="D4">
-        <v>1336.701394954878</v>
+        <v>1338.606758829363</v>
       </c>
       <c r="E4">
-        <v>-486.278</v>
+        <v>-471.3170000000001</v>
       </c>
       <c r="F4">
-        <v>29.922</v>
+        <v>44.883</v>
       </c>
       <c r="G4">
         <v>130</v>
@@ -1597,28 +1597,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M4">
-        <v>1.5050766</v>
+        <v>2.2576149</v>
       </c>
       <c r="N4">
-        <v>185.4282567333334</v>
+        <v>184.6757184333334</v>
       </c>
       <c r="O4">
-        <v>27.07252548306667</v>
+        <v>26.96265489126667</v>
       </c>
       <c r="P4">
-        <v>158.3557312502667</v>
+        <v>157.7130635420667</v>
       </c>
       <c r="Q4">
-        <v>267.2557312502667</v>
+        <v>266.6130635420667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.085040930473106</v>
+        <v>0.08538742424134257</v>
       </c>
       <c r="T4">
-        <v>0.9062570548061432</v>
+        <v>0.914259220354332</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>124.2018734018809</v>
+        <v>82.80124893458729</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08411448751410229</v>
+        <v>0.08402973916456072</v>
       </c>
       <c r="C5">
-        <v>1423.723758829363</v>
+        <v>1410.673562353667</v>
       </c>
       <c r="D5">
-        <v>1338.606758829363</v>
+        <v>1340.517562353667</v>
       </c>
       <c r="E5">
-        <v>-471.3170000000001</v>
+        <v>-456.3560000000001</v>
       </c>
       <c r="F5">
-        <v>44.883</v>
+        <v>59.84399999999999</v>
       </c>
       <c r="G5">
         <v>130</v>
@@ -1679,28 +1679,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M5">
-        <v>2.2576149</v>
+        <v>3.0101532</v>
       </c>
       <c r="N5">
-        <v>184.6757184333334</v>
+        <v>183.9231801333334</v>
       </c>
       <c r="O5">
-        <v>26.96265489126667</v>
+        <v>26.85278429946667</v>
       </c>
       <c r="P5">
-        <v>157.7130635420667</v>
+        <v>157.0703958338667</v>
       </c>
       <c r="Q5">
-        <v>266.6130635420667</v>
+        <v>265.9703958338667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08538742424134257</v>
+        <v>0.08574113662975075</v>
       </c>
       <c r="T5">
-        <v>0.914259220354332</v>
+        <v>0.9224280976847749</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.80124893458729</v>
+        <v>62.10093670094047</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08402973916456072</v>
+        <v>0.08394499081501913</v>
       </c>
       <c r="C6">
-        <v>1410.673562353667</v>
+        <v>1397.628828855687</v>
       </c>
       <c r="D6">
-        <v>1340.517562353667</v>
+        <v>1342.433828855687</v>
       </c>
       <c r="E6">
-        <v>-456.3560000000001</v>
+        <v>-441.395</v>
       </c>
       <c r="F6">
-        <v>59.84399999999999</v>
+        <v>74.80499999999999</v>
       </c>
       <c r="G6">
         <v>130</v>
@@ -1761,28 +1761,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M6">
-        <v>3.0101532</v>
+        <v>3.762691499999999</v>
       </c>
       <c r="N6">
-        <v>183.9231801333334</v>
+        <v>183.1706418333334</v>
       </c>
       <c r="O6">
-        <v>26.85278429946667</v>
+        <v>26.74291370766667</v>
       </c>
       <c r="P6">
-        <v>157.0703958338667</v>
+        <v>156.4277281256667</v>
       </c>
       <c r="Q6">
-        <v>265.9703958338667</v>
+        <v>265.3277281256667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08574113662975075</v>
+        <v>0.08610229559475699</v>
       </c>
       <c r="T6">
-        <v>0.9224280976847749</v>
+        <v>0.930768951380069</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.10093670094047</v>
+        <v>49.68074936075238</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08394499081501913</v>
+        <v>0.08386024246547755</v>
       </c>
       <c r="C7">
-        <v>1397.628828855687</v>
+        <v>1384.589581796901</v>
       </c>
       <c r="D7">
-        <v>1342.433828855687</v>
+        <v>1344.355581796901</v>
       </c>
       <c r="E7">
-        <v>-441.395</v>
+        <v>-426.434</v>
       </c>
       <c r="F7">
-        <v>74.80499999999999</v>
+        <v>89.76600000000001</v>
       </c>
       <c r="G7">
         <v>130</v>
@@ -1843,28 +1843,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M7">
-        <v>3.762691499999999</v>
+        <v>4.5152298</v>
       </c>
       <c r="N7">
-        <v>183.1706418333334</v>
+        <v>182.4181035333334</v>
       </c>
       <c r="O7">
-        <v>26.74291370766667</v>
+        <v>26.63304311586667</v>
       </c>
       <c r="P7">
-        <v>156.4277281256667</v>
+        <v>155.7850604174667</v>
       </c>
       <c r="Q7">
-        <v>265.3277281256667</v>
+        <v>264.6850604174667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08610229559475699</v>
+        <v>0.08647113879306123</v>
       </c>
       <c r="T7">
-        <v>0.930768951380069</v>
+        <v>0.9392872700476036</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.68074936075238</v>
+        <v>41.40062446729363</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08386024246547755</v>
+        <v>0.08377549411593599</v>
       </c>
       <c r="C8">
-        <v>1384.589581796901</v>
+        <v>1371.555844773321</v>
       </c>
       <c r="D8">
-        <v>1344.355581796901</v>
+        <v>1346.282844773321</v>
       </c>
       <c r="E8">
-        <v>-426.4340000000001</v>
+        <v>-411.4730000000001</v>
       </c>
       <c r="F8">
-        <v>89.76599999999999</v>
+        <v>104.727</v>
       </c>
       <c r="G8">
         <v>130</v>
@@ -1925,28 +1925,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M8">
-        <v>4.515229799999999</v>
+        <v>5.2677681</v>
       </c>
       <c r="N8">
-        <v>182.4181035333334</v>
+        <v>181.6655652333334</v>
       </c>
       <c r="O8">
-        <v>26.63304311586667</v>
+        <v>26.52317252406667</v>
       </c>
       <c r="P8">
-        <v>155.7850604174667</v>
+        <v>155.1423927092667</v>
       </c>
       <c r="Q8">
-        <v>264.6850604174667</v>
+        <v>264.0423927092667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08647113879306123</v>
+        <v>0.08684791410315697</v>
       </c>
       <c r="T8">
-        <v>0.9392872700476036</v>
+        <v>0.9479887783639023</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.40062446729365</v>
+        <v>35.48624954339455</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08377549411593598</v>
+        <v>0.0836907457663944</v>
       </c>
       <c r="C9">
-        <v>1371.555844773321</v>
+        <v>1358.527641516466</v>
       </c>
       <c r="D9">
-        <v>1346.282844773321</v>
+        <v>1348.215641516466</v>
       </c>
       <c r="E9">
-        <v>-411.4730000000001</v>
+        <v>-396.5120000000001</v>
       </c>
       <c r="F9">
-        <v>104.727</v>
+        <v>119.688</v>
       </c>
       <c r="G9">
         <v>130</v>
@@ -2007,28 +2007,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M9">
-        <v>5.2677681</v>
+        <v>6.020306399999999</v>
       </c>
       <c r="N9">
-        <v>181.6655652333334</v>
+        <v>180.9130269333334</v>
       </c>
       <c r="O9">
-        <v>26.52317252406667</v>
+        <v>26.41330193226667</v>
       </c>
       <c r="P9">
-        <v>155.1423927092667</v>
+        <v>154.4997250010667</v>
       </c>
       <c r="Q9">
-        <v>264.0423927092667</v>
+        <v>263.3997250010667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08684791410315697</v>
+        <v>0.08723288018086348</v>
       </c>
       <c r="T9">
-        <v>0.9479887783639023</v>
+        <v>0.9568794499044682</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.48624954339455</v>
+        <v>31.05046835047023</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0836907457663944</v>
+        <v>0.08360599741685282</v>
       </c>
       <c r="C10">
-        <v>1358.527641516466</v>
+        <v>1345.50499589433</v>
       </c>
       <c r="D10">
-        <v>1348.215641516466</v>
+        <v>1350.15399589433</v>
       </c>
       <c r="E10">
-        <v>-396.5120000000001</v>
+        <v>-381.551</v>
       </c>
       <c r="F10">
-        <v>119.688</v>
+        <v>134.649</v>
       </c>
       <c r="G10">
         <v>130</v>
@@ -2089,28 +2089,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M10">
-        <v>6.020306399999999</v>
+        <v>6.772844699999999</v>
       </c>
       <c r="N10">
-        <v>180.9130269333334</v>
+        <v>180.1604886333334</v>
       </c>
       <c r="O10">
-        <v>26.41330193226667</v>
+        <v>26.30343134046667</v>
       </c>
       <c r="P10">
-        <v>154.4997250010667</v>
+        <v>153.8570572928667</v>
       </c>
       <c r="Q10">
-        <v>263.3997250010667</v>
+        <v>262.7570572928667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08723288018086348</v>
+        <v>0.08762630705148661</v>
       </c>
       <c r="T10">
-        <v>0.9568794499044682</v>
+        <v>0.9659655208195521</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.05046835047023</v>
+        <v>27.6004163115291</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08360599741685282</v>
+        <v>0.08352124906731123</v>
       </c>
       <c r="C11">
-        <v>1345.50499589433</v>
+        <v>1332.487931912366</v>
       </c>
       <c r="D11">
-        <v>1350.15399589433</v>
+        <v>1352.097931912366</v>
       </c>
       <c r="E11">
-        <v>-381.551</v>
+        <v>-366.59</v>
       </c>
       <c r="F11">
-        <v>134.649</v>
+        <v>149.61</v>
       </c>
       <c r="G11">
         <v>130</v>
@@ -2171,28 +2171,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M11">
-        <v>6.772844699999999</v>
+        <v>7.525382999999999</v>
       </c>
       <c r="N11">
-        <v>180.1604886333334</v>
+        <v>179.4079503333334</v>
       </c>
       <c r="O11">
-        <v>26.30343134046667</v>
+        <v>26.19356074866667</v>
       </c>
       <c r="P11">
-        <v>153.8570572928667</v>
+        <v>153.2143895846667</v>
       </c>
       <c r="Q11">
-        <v>262.7570572928667</v>
+        <v>262.1143895846667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08762630705148661</v>
+        <v>0.08802847674145692</v>
       </c>
       <c r="T11">
-        <v>0.9659655208195521</v>
+        <v>0.9752535044216379</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.6004163115291</v>
+        <v>24.84037468037619</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08352124906731123</v>
+        <v>0.08343650071776965</v>
       </c>
       <c r="C12">
-        <v>1332.487931912366</v>
+        <v>1319.476473714477</v>
       </c>
       <c r="D12">
-        <v>1352.097931912366</v>
+        <v>1354.047473714477</v>
       </c>
       <c r="E12">
-        <v>-366.59</v>
+        <v>-351.629</v>
       </c>
       <c r="F12">
-        <v>149.61</v>
+        <v>164.571</v>
       </c>
       <c r="G12">
         <v>130</v>
@@ -2253,28 +2253,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M12">
-        <v>7.525382999999999</v>
+        <v>8.277921299999999</v>
       </c>
       <c r="N12">
-        <v>179.4079503333334</v>
+        <v>178.6554120333334</v>
       </c>
       <c r="O12">
-        <v>26.19356074866667</v>
+        <v>26.08369015686667</v>
       </c>
       <c r="P12">
-        <v>153.2143895846667</v>
+        <v>152.5717218764667</v>
       </c>
       <c r="Q12">
-        <v>262.1143895846667</v>
+        <v>261.4717218764667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08802847674145692</v>
+        <v>0.08843968395255017</v>
       </c>
       <c r="T12">
-        <v>0.9752535044216379</v>
+        <v>0.9847502067563549</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.84037468037619</v>
+        <v>22.58215880034199</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08343650071776965</v>
+        <v>0.08335175236822807</v>
       </c>
       <c r="C13">
-        <v>1319.476473714477</v>
+        <v>1306.470645584017</v>
       </c>
       <c r="D13">
-        <v>1354.047473714477</v>
+        <v>1356.002645584017</v>
       </c>
       <c r="E13">
-        <v>-351.629</v>
+        <v>-336.6680000000001</v>
       </c>
       <c r="F13">
-        <v>164.571</v>
+        <v>179.532</v>
       </c>
       <c r="G13">
         <v>130</v>
@@ -2335,28 +2335,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M13">
-        <v>8.277921299999999</v>
+        <v>9.030459599999999</v>
       </c>
       <c r="N13">
-        <v>178.6554120333334</v>
+        <v>177.9028737333334</v>
       </c>
       <c r="O13">
-        <v>26.08369015686667</v>
+        <v>25.97381956506667</v>
       </c>
       <c r="P13">
-        <v>152.5717218764667</v>
+        <v>151.9290541682667</v>
       </c>
       <c r="Q13">
-        <v>261.4717218764667</v>
+        <v>260.8290541682667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08843968395255017</v>
+        <v>0.08886023678207736</v>
       </c>
       <c r="T13">
-        <v>0.9847502067563549</v>
+        <v>0.9944627432350427</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.58215880034199</v>
+        <v>20.70031223364682</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08335175236822807</v>
+        <v>0.08326700401868649</v>
       </c>
       <c r="C14">
-        <v>1306.470645584017</v>
+        <v>1293.4704719448</v>
       </c>
       <c r="D14">
-        <v>1356.002645584017</v>
+        <v>1357.9634719448</v>
       </c>
       <c r="E14">
-        <v>-336.6680000000001</v>
+        <v>-321.7070000000001</v>
       </c>
       <c r="F14">
-        <v>179.532</v>
+        <v>194.493</v>
       </c>
       <c r="G14">
         <v>130</v>
@@ -2417,28 +2417,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M14">
-        <v>9.030459599999999</v>
+        <v>9.7829979</v>
       </c>
       <c r="N14">
-        <v>177.9028737333334</v>
+        <v>177.1503354333334</v>
       </c>
       <c r="O14">
-        <v>25.97381956506667</v>
+        <v>25.86394897326667</v>
       </c>
       <c r="P14">
-        <v>151.9290541682667</v>
+        <v>151.2863864600667</v>
       </c>
       <c r="Q14">
-        <v>260.8290541682667</v>
+        <v>260.1863864600667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08886023678207736</v>
+        <v>0.08929045749274309</v>
       </c>
       <c r="T14">
-        <v>0.9944627432350427</v>
+        <v>1.00439855641439</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.70031223364682</v>
+        <v>19.1079805233663</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08326700401868649</v>
+        <v>0.0831822556691449</v>
       </c>
       <c r="C15">
-        <v>1293.4704719448</v>
+        <v>1280.475977362112</v>
       </c>
       <c r="D15">
-        <v>1357.9634719448</v>
+        <v>1359.929977362112</v>
       </c>
       <c r="E15">
-        <v>-321.7070000000001</v>
+        <v>-306.746</v>
       </c>
       <c r="F15">
-        <v>194.493</v>
+        <v>209.454</v>
       </c>
       <c r="G15">
         <v>130</v>
@@ -2499,28 +2499,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M15">
-        <v>9.7829979</v>
+        <v>10.5355362</v>
       </c>
       <c r="N15">
-        <v>177.1503354333334</v>
+        <v>176.3977971333334</v>
       </c>
       <c r="O15">
-        <v>25.86394897326667</v>
+        <v>25.75407838146667</v>
       </c>
       <c r="P15">
-        <v>151.2863864600667</v>
+        <v>150.6437187518667</v>
       </c>
       <c r="Q15">
-        <v>260.1863864600667</v>
+        <v>259.5437187518667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08929045749274309</v>
+        <v>0.08973068333621501</v>
       </c>
       <c r="T15">
-        <v>1.00439855641439</v>
+        <v>1.014565435016513</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.1079805233663</v>
+        <v>17.74312477169727</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0831822556691449</v>
+        <v>0.08309750731960332</v>
       </c>
       <c r="C16">
-        <v>1280.475977362112</v>
+        <v>1267.487186543741</v>
       </c>
       <c r="D16">
-        <v>1359.929977362112</v>
+        <v>1361.902186543741</v>
       </c>
       <c r="E16">
-        <v>-306.746</v>
+        <v>-291.785</v>
       </c>
       <c r="F16">
-        <v>209.454</v>
+        <v>224.415</v>
       </c>
       <c r="G16">
         <v>130</v>
@@ -2581,28 +2581,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M16">
-        <v>10.5355362</v>
+        <v>11.2880745</v>
       </c>
       <c r="N16">
-        <v>176.3977971333334</v>
+        <v>175.6452588333334</v>
       </c>
       <c r="O16">
-        <v>25.75407838146667</v>
+        <v>25.64420778966667</v>
       </c>
       <c r="P16">
-        <v>150.6437187518667</v>
+        <v>150.0010510436667</v>
       </c>
       <c r="Q16">
-        <v>259.5437187518667</v>
+        <v>258.9010510436667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08973068333621501</v>
+        <v>0.09018126743482743</v>
       </c>
       <c r="T16">
-        <v>1.014565435016513</v>
+        <v>1.024971534291627</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.74312477169727</v>
+        <v>16.56024978691746</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08309750731960332</v>
+        <v>0.08301275897006173</v>
       </c>
       <c r="C17">
-        <v>1267.487186543741</v>
+        <v>1254.504124341013</v>
       </c>
       <c r="D17">
-        <v>1361.902186543741</v>
+        <v>1363.880124341013</v>
       </c>
       <c r="E17">
-        <v>-291.7850000000001</v>
+        <v>-276.8240000000001</v>
       </c>
       <c r="F17">
-        <v>224.415</v>
+        <v>239.376</v>
       </c>
       <c r="G17">
         <v>130</v>
@@ -2663,28 +2663,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M17">
-        <v>11.2880745</v>
+        <v>12.0406128</v>
       </c>
       <c r="N17">
-        <v>175.6452588333334</v>
+        <v>174.8927205333334</v>
       </c>
       <c r="O17">
-        <v>25.64420778966667</v>
+        <v>25.53433719786667</v>
       </c>
       <c r="P17">
-        <v>150.0010510436667</v>
+        <v>149.3583833354667</v>
       </c>
       <c r="Q17">
-        <v>258.9010510436667</v>
+        <v>258.2583833354667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09018126743482743</v>
+        <v>0.09064257972626398</v>
       </c>
       <c r="T17">
-        <v>1.024971534291627</v>
+        <v>1.035625397835196</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.56024978691746</v>
+        <v>15.52523417523512</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08301275897006173</v>
+        <v>0.08292801062052016</v>
       </c>
       <c r="C18">
-        <v>1254.504124341013</v>
+        <v>1241.526815749831</v>
       </c>
       <c r="D18">
-        <v>1363.880124341013</v>
+        <v>1365.863815749831</v>
       </c>
       <c r="E18">
-        <v>-276.8240000000001</v>
+        <v>-261.8630000000001</v>
       </c>
       <c r="F18">
-        <v>239.376</v>
+        <v>254.337</v>
       </c>
       <c r="G18">
         <v>130</v>
@@ -2745,28 +2745,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M18">
-        <v>12.0406128</v>
+        <v>12.7931511</v>
       </c>
       <c r="N18">
-        <v>174.8927205333334</v>
+        <v>174.1401822333334</v>
       </c>
       <c r="O18">
-        <v>25.53433719786667</v>
+        <v>25.42446660606667</v>
       </c>
       <c r="P18">
-        <v>149.3583833354667</v>
+        <v>148.7157156272667</v>
       </c>
       <c r="Q18">
-        <v>258.2583833354667</v>
+        <v>257.6157156272667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09064257972626398</v>
+        <v>0.09111500797653031</v>
       </c>
       <c r="T18">
-        <v>1.035625397835196</v>
+        <v>1.046535980982224</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.52523417523512</v>
+        <v>14.61198510610364</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08292801062052016</v>
+        <v>0.08284326227097856</v>
       </c>
       <c r="C19">
-        <v>1241.526815749831</v>
+        <v>1228.555285911733</v>
       </c>
       <c r="D19">
-        <v>1365.863815749831</v>
+        <v>1367.853285911733</v>
       </c>
       <c r="E19">
-        <v>-261.8630000000001</v>
+        <v>-246.902</v>
       </c>
       <c r="F19">
-        <v>254.337</v>
+        <v>269.298</v>
       </c>
       <c r="G19">
         <v>130</v>
@@ -2827,28 +2827,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M19">
-        <v>12.7931511</v>
+        <v>13.5456894</v>
       </c>
       <c r="N19">
-        <v>174.1401822333334</v>
+        <v>173.3876439333334</v>
       </c>
       <c r="O19">
-        <v>25.42446660606667</v>
+        <v>25.31459601426667</v>
       </c>
       <c r="P19">
-        <v>148.7157156272667</v>
+        <v>148.0730479190667</v>
       </c>
       <c r="Q19">
-        <v>257.6157156272667</v>
+        <v>256.9730479190667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09111500797653031</v>
+        <v>0.09159895886704704</v>
       </c>
       <c r="T19">
-        <v>1.046535980982224</v>
+        <v>1.057712675913327</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.61198510610364</v>
+        <v>13.80020815576455</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08284326227097857</v>
+        <v>0.082758513921437</v>
       </c>
       <c r="C20">
-        <v>1228.555285911732</v>
+        <v>1215.589560114948</v>
       </c>
       <c r="D20">
-        <v>1367.853285911732</v>
+        <v>1369.848560114948</v>
       </c>
       <c r="E20">
-        <v>-246.902</v>
+        <v>-231.9410000000001</v>
       </c>
       <c r="F20">
-        <v>269.298</v>
+        <v>284.259</v>
       </c>
       <c r="G20">
         <v>130</v>
@@ -2909,28 +2909,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M20">
-        <v>13.5456894</v>
+        <v>14.2982277</v>
       </c>
       <c r="N20">
-        <v>173.3876439333334</v>
+        <v>172.6351056333334</v>
       </c>
       <c r="O20">
-        <v>25.31459601426667</v>
+        <v>25.20472542246667</v>
       </c>
       <c r="P20">
-        <v>148.0730479190667</v>
+        <v>147.4303802108667</v>
       </c>
       <c r="Q20">
-        <v>256.9730479190667</v>
+        <v>256.3303802108667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09159895886704704</v>
+        <v>0.09209485916226789</v>
       </c>
       <c r="T20">
-        <v>1.057712675913327</v>
+        <v>1.069165338620506</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.80020815576455</v>
+        <v>13.07388141072431</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.082758513921437</v>
+        <v>0.08292996557189541</v>
       </c>
       <c r="C21">
-        <v>1215.589560114948</v>
+        <v>1196.597991490735</v>
       </c>
       <c r="D21">
-        <v>1369.848560114948</v>
+        <v>1365.817991490735</v>
       </c>
       <c r="E21">
-        <v>-231.9410000000001</v>
+        <v>-216.9800000000001</v>
       </c>
       <c r="F21">
-        <v>284.259</v>
+        <v>299.22</v>
       </c>
       <c r="G21">
         <v>130</v>
@@ -2991,45 +2991,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M21">
-        <v>14.2982277</v>
+        <v>15.499596</v>
       </c>
       <c r="N21">
-        <v>172.6351056333334</v>
+        <v>171.4337373333334</v>
       </c>
       <c r="O21">
-        <v>25.20472542246667</v>
+        <v>25.02932565066667</v>
       </c>
       <c r="P21">
-        <v>147.4303802108667</v>
+        <v>146.4044116826667</v>
       </c>
       <c r="Q21">
-        <v>256.3303802108667</v>
+        <v>255.3044116826667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09209485916226789</v>
+        <v>0.09260315696486927</v>
       </c>
       <c r="T21">
-        <v>1.069165338620506</v>
+        <v>1.080904317895364</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.07388141072431</v>
+        <v>12.06052940562666</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08292996557189541</v>
+        <v>0.08285802722235382</v>
       </c>
       <c r="C22">
-        <v>1196.597991490735</v>
+        <v>1183.325261421053</v>
       </c>
       <c r="D22">
-        <v>1365.817991490735</v>
+        <v>1367.506261421053</v>
       </c>
       <c r="E22">
-        <v>-216.9800000000001</v>
+        <v>-202.0190000000001</v>
       </c>
       <c r="F22">
-        <v>299.22</v>
+        <v>314.181</v>
       </c>
       <c r="G22">
         <v>130</v>
@@ -3073,28 +3073,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M22">
-        <v>15.499596</v>
+        <v>16.2745758</v>
       </c>
       <c r="N22">
-        <v>171.4337373333334</v>
+        <v>170.6587575333334</v>
       </c>
       <c r="O22">
-        <v>25.02932565066667</v>
+        <v>24.91617859986667</v>
       </c>
       <c r="P22">
-        <v>146.4044116826667</v>
+        <v>145.7425789334667</v>
       </c>
       <c r="Q22">
-        <v>255.3044116826667</v>
+        <v>254.6425789334667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09260315696486927</v>
+        <v>0.09312432306627066</v>
       </c>
       <c r="T22">
-        <v>1.080904317895364</v>
+        <v>1.092940486518953</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.06052940562666</v>
+        <v>11.4862184815492</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08285802722235382</v>
+        <v>0.08278608887281226</v>
       </c>
       <c r="C23">
-        <v>1183.325261421053</v>
+        <v>1170.056710214</v>
       </c>
       <c r="D23">
-        <v>1367.506261421053</v>
+        <v>1369.198710214</v>
       </c>
       <c r="E23">
-        <v>-202.0190000000001</v>
+        <v>-187.058</v>
       </c>
       <c r="F23">
-        <v>314.181</v>
+        <v>329.142</v>
       </c>
       <c r="G23">
         <v>130</v>
@@ -3155,28 +3155,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M23">
-        <v>16.2745758</v>
+        <v>17.0495556</v>
       </c>
       <c r="N23">
-        <v>170.6587575333334</v>
+        <v>169.8837777333334</v>
       </c>
       <c r="O23">
-        <v>24.91617859986667</v>
+        <v>24.80303154906667</v>
       </c>
       <c r="P23">
-        <v>145.7425789334667</v>
+        <v>145.0807461842667</v>
       </c>
       <c r="Q23">
-        <v>254.6425789334667</v>
+        <v>253.9807461842667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09312432306627066</v>
+        <v>0.09365885240104135</v>
       </c>
       <c r="T23">
-        <v>1.092940486518953</v>
+        <v>1.105285274850839</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.4862184815492</v>
+        <v>10.96411764147878</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08278608887281226</v>
+        <v>0.08271415052327066</v>
       </c>
       <c r="C24">
-        <v>1170.056710214</v>
+        <v>1156.792353404296</v>
       </c>
       <c r="D24">
-        <v>1369.198710214</v>
+        <v>1370.895353404296</v>
       </c>
       <c r="E24">
-        <v>-187.058</v>
+        <v>-172.097</v>
       </c>
       <c r="F24">
-        <v>329.142</v>
+        <v>344.103</v>
       </c>
       <c r="G24">
         <v>130</v>
@@ -3237,28 +3237,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M24">
-        <v>17.0495556</v>
+        <v>17.8245354</v>
       </c>
       <c r="N24">
-        <v>169.8837777333334</v>
+        <v>169.1087979333334</v>
       </c>
       <c r="O24">
-        <v>24.80303154906667</v>
+        <v>24.68988449826667</v>
       </c>
       <c r="P24">
-        <v>145.0807461842667</v>
+        <v>144.4189134350667</v>
       </c>
       <c r="Q24">
-        <v>253.9807461842667</v>
+        <v>253.3189134350667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09365885240104135</v>
+        <v>0.09420726561463723</v>
       </c>
       <c r="T24">
-        <v>1.105285274850839</v>
+        <v>1.117950707035502</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.96411764147878</v>
+        <v>10.48741687445797</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08271415052327066</v>
+        <v>0.08264221217372908</v>
       </c>
       <c r="C25">
-        <v>1156.792353404296</v>
+        <v>1143.532206603752</v>
       </c>
       <c r="D25">
-        <v>1370.895353404296</v>
+        <v>1372.596206603753</v>
       </c>
       <c r="E25">
-        <v>-172.097</v>
+        <v>-157.136</v>
       </c>
       <c r="F25">
-        <v>344.103</v>
+        <v>359.064</v>
       </c>
       <c r="G25">
         <v>130</v>
@@ -3319,28 +3319,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M25">
-        <v>17.8245354</v>
+        <v>18.5995152</v>
       </c>
       <c r="N25">
-        <v>169.1087979333334</v>
+        <v>168.3338181333334</v>
       </c>
       <c r="O25">
-        <v>24.68988449826667</v>
+        <v>24.57673744746667</v>
       </c>
       <c r="P25">
-        <v>144.4189134350667</v>
+        <v>143.7570806858667</v>
       </c>
       <c r="Q25">
-        <v>253.3189134350667</v>
+        <v>252.6570806858667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09420726561463723</v>
+        <v>0.09477011075490668</v>
       </c>
       <c r="T25">
-        <v>1.117950707035502</v>
+        <v>1.130949440067129</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.48741687445797</v>
+        <v>10.05044117135555</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08264221217372908</v>
+        <v>0.0829332238241875</v>
       </c>
       <c r="C26">
-        <v>1143.532206603752</v>
+        <v>1121.716624558029</v>
       </c>
       <c r="D26">
-        <v>1372.596206603753</v>
+        <v>1365.741624558029</v>
       </c>
       <c r="E26">
-        <v>-157.1360000000001</v>
+        <v>-142.1750000000001</v>
       </c>
       <c r="F26">
-        <v>359.064</v>
+        <v>374.025</v>
       </c>
       <c r="G26">
         <v>130</v>
@@ -3401,45 +3401,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M26">
-        <v>18.5995152</v>
+        <v>20.0103375</v>
       </c>
       <c r="N26">
-        <v>168.3338181333334</v>
+        <v>166.9229958333334</v>
       </c>
       <c r="O26">
-        <v>24.57673744746667</v>
+        <v>24.37075739166667</v>
       </c>
       <c r="P26">
-        <v>143.7570806858667</v>
+        <v>142.5522384416667</v>
       </c>
       <c r="Q26">
-        <v>252.6570806858667</v>
+        <v>251.4522384416667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09477011075490668</v>
+        <v>0.09534796509891667</v>
       </c>
       <c r="T26">
-        <v>1.130949440067129</v>
+        <v>1.1442948059796</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.05044117135555</v>
+        <v>9.341838104096615</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0829332238241875</v>
+        <v>0.08287580347464592</v>
       </c>
       <c r="C27">
-        <v>1121.716624558029</v>
+        <v>1108.102695080237</v>
       </c>
       <c r="D27">
-        <v>1365.741624558029</v>
+        <v>1367.088695080237</v>
       </c>
       <c r="E27">
-        <v>-142.1750000000001</v>
+        <v>-127.2140000000001</v>
       </c>
       <c r="F27">
-        <v>374.025</v>
+        <v>388.986</v>
       </c>
       <c r="G27">
         <v>130</v>
@@ -3483,28 +3483,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M27">
-        <v>20.0103375</v>
+        <v>20.810751</v>
       </c>
       <c r="N27">
-        <v>166.9229958333334</v>
+        <v>166.1225823333334</v>
       </c>
       <c r="O27">
-        <v>24.37075739166667</v>
+        <v>24.25389702066667</v>
       </c>
       <c r="P27">
-        <v>142.5522384416667</v>
+        <v>141.8686853126667</v>
       </c>
       <c r="Q27">
-        <v>251.4522384416667</v>
+        <v>250.7686853126667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09534796509891667</v>
+        <v>0.0959414371278999</v>
       </c>
       <c r="T27">
-        <v>1.1442948059796</v>
+        <v>1.158000857457272</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.341838104096615</v>
+        <v>8.982536638554436</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08287580347464592</v>
+        <v>0.08281838312510435</v>
       </c>
       <c r="C28">
-        <v>1108.102695080237</v>
+        <v>1094.491425535361</v>
       </c>
       <c r="D28">
-        <v>1367.088695080237</v>
+        <v>1368.43842553536</v>
       </c>
       <c r="E28">
-        <v>-127.2140000000001</v>
+        <v>-112.253</v>
       </c>
       <c r="F28">
-        <v>388.986</v>
+        <v>403.947</v>
       </c>
       <c r="G28">
         <v>130</v>
@@ -3565,28 +3565,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M28">
-        <v>20.810751</v>
+        <v>21.6111645</v>
       </c>
       <c r="N28">
-        <v>166.1225823333334</v>
+        <v>165.3221688333334</v>
       </c>
       <c r="O28">
-        <v>24.25389702066667</v>
+        <v>24.13703664966667</v>
       </c>
       <c r="P28">
-        <v>141.8686853126667</v>
+        <v>141.1851321836667</v>
       </c>
       <c r="Q28">
-        <v>250.7686853126667</v>
+        <v>250.0851321836667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0959414371278999</v>
+        <v>0.09655116866452651</v>
       </c>
       <c r="T28">
-        <v>1.158000857457272</v>
+        <v>1.172082417194608</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.982536638554436</v>
+        <v>8.649850096385752</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08281838312510435</v>
+        <v>0.08276096277556276</v>
       </c>
       <c r="C29">
-        <v>1094.491425535361</v>
+        <v>1080.882823809663</v>
       </c>
       <c r="D29">
-        <v>1368.43842553536</v>
+        <v>1369.790823809663</v>
       </c>
       <c r="E29">
-        <v>-112.253</v>
+        <v>-97.29200000000003</v>
       </c>
       <c r="F29">
-        <v>403.947</v>
+        <v>418.908</v>
       </c>
       <c r="G29">
         <v>130</v>
@@ -3647,28 +3647,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M29">
-        <v>21.6111645</v>
+        <v>22.411578</v>
       </c>
       <c r="N29">
-        <v>165.3221688333334</v>
+        <v>164.5217553333334</v>
       </c>
       <c r="O29">
-        <v>24.13703664966667</v>
+        <v>24.02017627866667</v>
       </c>
       <c r="P29">
-        <v>141.1851321836667</v>
+        <v>140.5015790546667</v>
       </c>
       <c r="Q29">
-        <v>250.0851321836667</v>
+        <v>249.4015790546667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09655116866452651</v>
+        <v>0.09717783718828162</v>
       </c>
       <c r="T29">
-        <v>1.172082417194608</v>
+        <v>1.186555131369091</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.649850096385752</v>
+        <v>8.34092687865769</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08276096277556276</v>
+        <v>0.08270354242602118</v>
       </c>
       <c r="C30">
-        <v>1080.882823809663</v>
+        <v>1067.276897820614</v>
       </c>
       <c r="D30">
-        <v>1369.790823809663</v>
+        <v>1371.145897820614</v>
       </c>
       <c r="E30">
-        <v>-97.29200000000003</v>
+        <v>-82.33100000000002</v>
       </c>
       <c r="F30">
-        <v>418.908</v>
+        <v>433.869</v>
       </c>
       <c r="G30">
         <v>130</v>
@@ -3729,28 +3729,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M30">
-        <v>22.411578</v>
+        <v>23.2119915</v>
       </c>
       <c r="N30">
-        <v>164.5217553333334</v>
+        <v>163.7213418333334</v>
       </c>
       <c r="O30">
-        <v>24.02017627866667</v>
+        <v>23.90331590766667</v>
       </c>
       <c r="P30">
-        <v>140.5015790546667</v>
+        <v>139.8180259256667</v>
       </c>
       <c r="Q30">
-        <v>249.4015790546667</v>
+        <v>248.7180259256667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09717783718828162</v>
+        <v>0.09782215834650872</v>
       </c>
       <c r="T30">
-        <v>1.186555131369091</v>
+        <v>1.201435527632996</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.34092687865769</v>
+        <v>8.053308710428116</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08270354242602118</v>
+        <v>0.0826461220764796</v>
       </c>
       <c r="C31">
-        <v>1067.276897820614</v>
+        <v>1053.673655517043</v>
       </c>
       <c r="D31">
-        <v>1371.145897820614</v>
+        <v>1372.503655517043</v>
       </c>
       <c r="E31">
-        <v>-82.33100000000007</v>
+        <v>-67.37000000000006</v>
       </c>
       <c r="F31">
-        <v>433.869</v>
+        <v>448.83</v>
       </c>
       <c r="G31">
         <v>130</v>
@@ -3811,28 +3811,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M31">
-        <v>23.2119915</v>
+        <v>24.012405</v>
       </c>
       <c r="N31">
-        <v>163.7213418333334</v>
+        <v>162.9209283333334</v>
       </c>
       <c r="O31">
-        <v>23.90331590766667</v>
+        <v>23.78645553666667</v>
       </c>
       <c r="P31">
-        <v>139.8180259256667</v>
+        <v>139.1344727966667</v>
       </c>
       <c r="Q31">
-        <v>248.7180259256667</v>
+        <v>248.0344727966667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09782215834650872</v>
+        <v>0.09848488868068515</v>
       </c>
       <c r="T31">
-        <v>1.201435527632996</v>
+        <v>1.21674107807587</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.053308710428116</v>
+        <v>7.784865086747178</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0826461220764796</v>
+        <v>0.08280049372693803</v>
       </c>
       <c r="C32">
-        <v>1053.673655517043</v>
+        <v>1035.068480819533</v>
       </c>
       <c r="D32">
-        <v>1372.503655517043</v>
+        <v>1368.859480819533</v>
       </c>
       <c r="E32">
-        <v>-67.37000000000006</v>
+        <v>-52.40900000000005</v>
       </c>
       <c r="F32">
-        <v>448.83</v>
+        <v>463.791</v>
       </c>
       <c r="G32">
         <v>130</v>
@@ -3893,45 +3893,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M32">
-        <v>24.012405</v>
+        <v>25.1838513</v>
       </c>
       <c r="N32">
-        <v>162.9209283333334</v>
+        <v>161.7494820333334</v>
       </c>
       <c r="O32">
-        <v>23.78645553666667</v>
+        <v>23.61542437686667</v>
       </c>
       <c r="P32">
-        <v>139.1344727966667</v>
+        <v>138.1340576564667</v>
       </c>
       <c r="Q32">
-        <v>248.0344727966667</v>
+        <v>247.0340576564667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09848488868068515</v>
+        <v>0.09916682858976525</v>
       </c>
       <c r="T32">
-        <v>1.21674107807587</v>
+        <v>1.232490267662015</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.784865086747178</v>
+        <v>7.422746072731671</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08280049372693803</v>
+        <v>0.08274990537739645</v>
       </c>
       <c r="C33">
-        <v>1035.068480819533</v>
+        <v>1021.2995612368</v>
       </c>
       <c r="D33">
-        <v>1368.859480819533</v>
+        <v>1370.0515612368</v>
       </c>
       <c r="E33">
-        <v>-52.40900000000005</v>
+        <v>-37.44800000000009</v>
       </c>
       <c r="F33">
-        <v>463.791</v>
+        <v>478.752</v>
       </c>
       <c r="G33">
         <v>130</v>
@@ -3975,28 +3975,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M33">
-        <v>25.1838513</v>
+        <v>25.9962336</v>
       </c>
       <c r="N33">
-        <v>161.7494820333334</v>
+        <v>160.9370997333334</v>
       </c>
       <c r="O33">
-        <v>23.61542437686667</v>
+        <v>23.49681656106667</v>
       </c>
       <c r="P33">
-        <v>138.1340576564667</v>
+        <v>137.4402831722667</v>
       </c>
       <c r="Q33">
-        <v>247.0340576564667</v>
+        <v>246.3402831722667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09916682858976525</v>
+        <v>0.09986882555499477</v>
       </c>
       <c r="T33">
-        <v>1.232490267662015</v>
+        <v>1.248702668706577</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.422746072731671</v>
+        <v>7.190785257958806</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08274990537739645</v>
+        <v>0.08269931702785485</v>
       </c>
       <c r="C34">
-        <v>1021.2995612368</v>
+        <v>1007.532719726149</v>
       </c>
       <c r="D34">
-        <v>1370.0515612368</v>
+        <v>1371.245719726149</v>
       </c>
       <c r="E34">
-        <v>-37.44800000000009</v>
+        <v>-22.48700000000008</v>
       </c>
       <c r="F34">
-        <v>478.752</v>
+        <v>493.713</v>
       </c>
       <c r="G34">
         <v>130</v>
@@ -4057,28 +4057,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M34">
-        <v>25.9962336</v>
+        <v>26.8086159</v>
       </c>
       <c r="N34">
-        <v>160.9370997333334</v>
+        <v>160.1247174333334</v>
       </c>
       <c r="O34">
-        <v>23.49681656106667</v>
+        <v>23.37820874526667</v>
       </c>
       <c r="P34">
-        <v>137.4402831722667</v>
+        <v>136.7465086880667</v>
       </c>
       <c r="Q34">
-        <v>246.3402831722667</v>
+        <v>245.6465086880667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09986882555499477</v>
+        <v>0.1005917776535147</v>
       </c>
       <c r="T34">
-        <v>1.248702668706577</v>
+        <v>1.265399022021125</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.190785257958806</v>
+        <v>6.972882674384296</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08269931702785485</v>
+        <v>0.08264872867831327</v>
       </c>
       <c r="C35">
-        <v>1007.532719726149</v>
+        <v>993.7679617261608</v>
       </c>
       <c r="D35">
-        <v>1371.245719726149</v>
+        <v>1372.441961726161</v>
       </c>
       <c r="E35">
-        <v>-22.48700000000008</v>
+        <v>-7.526000000000067</v>
       </c>
       <c r="F35">
-        <v>493.713</v>
+        <v>508.674</v>
       </c>
       <c r="G35">
         <v>130</v>
@@ -4139,28 +4139,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M35">
-        <v>26.8086159</v>
+        <v>27.6209982</v>
       </c>
       <c r="N35">
-        <v>160.1247174333334</v>
+        <v>159.3123351333334</v>
       </c>
       <c r="O35">
-        <v>23.37820874526667</v>
+        <v>23.25960092946667</v>
       </c>
       <c r="P35">
-        <v>136.7465086880667</v>
+        <v>136.0527342038667</v>
       </c>
       <c r="Q35">
-        <v>245.6465086880667</v>
+        <v>244.9527342038667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1005917776535147</v>
+        <v>0.1013366373913838</v>
       </c>
       <c r="T35">
-        <v>1.265399022021125</v>
+        <v>1.282601325436114</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.972882674384296</v>
+        <v>6.767797889843582</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08264872867831327</v>
+        <v>0.08259814032877169</v>
       </c>
       <c r="C36">
-        <v>993.7679617261608</v>
+        <v>980.0052926944124</v>
       </c>
       <c r="D36">
-        <v>1372.441961726161</v>
+        <v>1373.640292694412</v>
       </c>
       <c r="E36">
-        <v>-7.526000000000067</v>
+        <v>7.434999999999945</v>
       </c>
       <c r="F36">
-        <v>508.674</v>
+        <v>523.635</v>
       </c>
       <c r="G36">
         <v>130</v>
@@ -4221,28 +4221,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M36">
-        <v>27.6209982</v>
+        <v>28.4333805</v>
       </c>
       <c r="N36">
-        <v>159.3123351333334</v>
+        <v>158.4999528333334</v>
       </c>
       <c r="O36">
-        <v>23.25960092946667</v>
+        <v>23.14099311366667</v>
       </c>
       <c r="P36">
-        <v>136.0527342038667</v>
+        <v>135.3589597196667</v>
       </c>
       <c r="Q36">
-        <v>244.9527342038667</v>
+        <v>244.2589597196667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1013366373913838</v>
+        <v>0.102104415890418</v>
       </c>
       <c r="T36">
-        <v>1.282601325436114</v>
+        <v>1.300332930494642</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.767797889843582</v>
+        <v>6.574432235848051</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08259814032877169</v>
+        <v>0.08254755197923011</v>
       </c>
       <c r="C37">
-        <v>980.0052926944124</v>
+        <v>966.2447181075563</v>
       </c>
       <c r="D37">
-        <v>1373.640292694412</v>
+        <v>1374.840718107556</v>
       </c>
       <c r="E37">
-        <v>7.434999999999945</v>
+        <v>22.39599999999996</v>
       </c>
       <c r="F37">
-        <v>523.635</v>
+        <v>538.596</v>
       </c>
       <c r="G37">
         <v>130</v>
@@ -4303,28 +4303,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M37">
-        <v>28.4333805</v>
+        <v>29.2457628</v>
       </c>
       <c r="N37">
-        <v>158.4999528333334</v>
+        <v>157.6875705333334</v>
       </c>
       <c r="O37">
-        <v>23.14099311366667</v>
+        <v>23.02238529786667</v>
       </c>
       <c r="P37">
-        <v>135.3589597196667</v>
+        <v>134.6651852354667</v>
       </c>
       <c r="Q37">
-        <v>244.2589597196667</v>
+        <v>243.5651852354667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.102104415890418</v>
+        <v>0.1028961874675471</v>
       </c>
       <c r="T37">
-        <v>1.300332930494642</v>
+        <v>1.318618648211248</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.574432235848051</v>
+        <v>6.391809118185605</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08254755197923012</v>
+        <v>0.08249696362968853</v>
       </c>
       <c r="C38">
-        <v>966.2447181075561</v>
+        <v>952.4862434614072</v>
       </c>
       <c r="D38">
-        <v>1374.840718107556</v>
+        <v>1376.043243461407</v>
       </c>
       <c r="E38">
-        <v>22.39599999999996</v>
+        <v>37.35699999999997</v>
       </c>
       <c r="F38">
-        <v>538.596</v>
+        <v>553.557</v>
       </c>
       <c r="G38">
         <v>130</v>
@@ -4385,28 +4385,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M38">
-        <v>29.2457628</v>
+        <v>30.0581451</v>
       </c>
       <c r="N38">
-        <v>157.6875705333334</v>
+        <v>156.8751882333334</v>
       </c>
       <c r="O38">
-        <v>23.02238529786667</v>
+        <v>22.90377748206667</v>
       </c>
       <c r="P38">
-        <v>134.6651852354667</v>
+        <v>133.9714107512667</v>
       </c>
       <c r="Q38">
-        <v>243.5651852354667</v>
+        <v>242.8714107512667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1028961874675471</v>
+        <v>0.1037130946502993</v>
       </c>
       <c r="T38">
-        <v>1.318618648211248</v>
+        <v>1.337484864902985</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.391809118185605</v>
+        <v>6.219057520396805</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08249696362968853</v>
+        <v>0.08277089528014694</v>
       </c>
       <c r="C39">
-        <v>952.4862434614072</v>
+        <v>931.0386963756899</v>
       </c>
       <c r="D39">
-        <v>1376.043243461407</v>
+        <v>1369.55669637569</v>
       </c>
       <c r="E39">
-        <v>37.35699999999997</v>
+        <v>52.31799999999987</v>
       </c>
       <c r="F39">
-        <v>553.557</v>
+        <v>568.5179999999999</v>
       </c>
       <c r="G39">
         <v>130</v>
@@ -4467,45 +4467,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M39">
-        <v>30.0581451</v>
+        <v>31.4390454</v>
       </c>
       <c r="N39">
-        <v>156.8751882333334</v>
+        <v>155.4942879333334</v>
       </c>
       <c r="O39">
-        <v>22.90377748206667</v>
+        <v>22.70216603826667</v>
       </c>
       <c r="P39">
-        <v>133.9714107512667</v>
+        <v>132.7921218950667</v>
       </c>
       <c r="Q39">
-        <v>242.8714107512667</v>
+        <v>241.6921218950667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1037130946502993</v>
+        <v>0.1045563536776564</v>
       </c>
       <c r="T39">
-        <v>1.337484864902985</v>
+        <v>1.356959669229939</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.219057520396805</v>
+        <v>5.945897241947854</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08277089528014694</v>
+        <v>0.08272884693060537</v>
       </c>
       <c r="C40">
-        <v>931.0386963756899</v>
+        <v>917.0694016199412</v>
       </c>
       <c r="D40">
-        <v>1369.55669637569</v>
+        <v>1370.548401619941</v>
       </c>
       <c r="E40">
-        <v>52.31799999999987</v>
+        <v>67.27899999999988</v>
       </c>
       <c r="F40">
-        <v>568.5179999999999</v>
+        <v>583.4789999999999</v>
       </c>
       <c r="G40">
         <v>130</v>
@@ -4549,28 +4549,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M40">
-        <v>31.4390454</v>
+        <v>32.2663887</v>
       </c>
       <c r="N40">
-        <v>155.4942879333334</v>
+        <v>154.6669446333334</v>
       </c>
       <c r="O40">
-        <v>22.70216603826667</v>
+        <v>22.58137391646667</v>
       </c>
       <c r="P40">
-        <v>132.7921218950667</v>
+        <v>132.0855707168667</v>
       </c>
       <c r="Q40">
-        <v>241.6921218950667</v>
+        <v>240.9855707168667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1045563536776564</v>
+        <v>0.105427260541976</v>
       </c>
       <c r="T40">
-        <v>1.356959669229939</v>
+        <v>1.377072991731548</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.945897241947854</v>
+        <v>5.793438338308166</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08272884693060537</v>
+        <v>0.08268679858106379</v>
       </c>
       <c r="C41">
-        <v>917.0694016199412</v>
+        <v>903.1015441058258</v>
       </c>
       <c r="D41">
-        <v>1370.548401619941</v>
+        <v>1371.541544105826</v>
       </c>
       <c r="E41">
-        <v>67.27899999999988</v>
+        <v>82.2399999999999</v>
       </c>
       <c r="F41">
-        <v>583.4789999999999</v>
+        <v>598.4399999999999</v>
       </c>
       <c r="G41">
         <v>130</v>
@@ -4631,28 +4631,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M41">
-        <v>32.2663887</v>
+        <v>33.093732</v>
       </c>
       <c r="N41">
-        <v>154.6669446333334</v>
+        <v>153.8396013333334</v>
       </c>
       <c r="O41">
-        <v>22.58137391646667</v>
+        <v>22.46058179466667</v>
       </c>
       <c r="P41">
-        <v>132.0855707168667</v>
+        <v>131.3790195386667</v>
       </c>
       <c r="Q41">
-        <v>240.9855707168667</v>
+        <v>240.2790195386667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.105427260541976</v>
+        <v>0.1063271976351063</v>
       </c>
       <c r="T41">
-        <v>1.377072991731548</v>
+        <v>1.397856758316543</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.793438338308166</v>
+        <v>5.648602379850463</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08268679858106379</v>
+        <v>0.08264475023152221</v>
       </c>
       <c r="C42">
-        <v>903.1015441058258</v>
+        <v>889.1351269600203</v>
       </c>
       <c r="D42">
-        <v>1371.541544105826</v>
+        <v>1372.53612696002</v>
       </c>
       <c r="E42">
-        <v>82.2399999999999</v>
+        <v>97.20099999999991</v>
       </c>
       <c r="F42">
-        <v>598.4399999999999</v>
+        <v>613.401</v>
       </c>
       <c r="G42">
         <v>130</v>
@@ -4713,28 +4713,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M42">
-        <v>33.093732</v>
+        <v>33.9210753</v>
       </c>
       <c r="N42">
-        <v>153.8396013333334</v>
+        <v>153.0122580333334</v>
       </c>
       <c r="O42">
-        <v>22.46058179466667</v>
+        <v>22.33978967286667</v>
       </c>
       <c r="P42">
-        <v>131.3790195386667</v>
+        <v>130.6724683604667</v>
       </c>
       <c r="Q42">
-        <v>240.2790195386667</v>
+        <v>239.5724683604667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1063271976351063</v>
+        <v>0.1072576410703766</v>
       </c>
       <c r="T42">
-        <v>1.397856758316543</v>
+        <v>1.419345059362047</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.648602379850463</v>
+        <v>5.510831590098011</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08264475023152221</v>
+        <v>0.08260270188198063</v>
       </c>
       <c r="C43">
-        <v>889.1351269600203</v>
+        <v>875.1701533182785</v>
       </c>
       <c r="D43">
-        <v>1372.53612696002</v>
+        <v>1373.532153318278</v>
       </c>
       <c r="E43">
-        <v>97.20099999999991</v>
+        <v>112.1619999999999</v>
       </c>
       <c r="F43">
-        <v>613.401</v>
+        <v>628.362</v>
       </c>
       <c r="G43">
         <v>130</v>
@@ -4795,28 +4795,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M43">
-        <v>33.9210753</v>
+        <v>34.7484186</v>
       </c>
       <c r="N43">
-        <v>153.0122580333334</v>
+        <v>152.1849147333334</v>
       </c>
       <c r="O43">
-        <v>22.33978967286667</v>
+        <v>22.21899755106667</v>
       </c>
       <c r="P43">
-        <v>130.6724683604667</v>
+        <v>129.9659171822667</v>
       </c>
       <c r="Q43">
-        <v>239.5724683604667</v>
+        <v>238.8659171822667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1072576410703766</v>
+        <v>0.1082201687620356</v>
       </c>
       <c r="T43">
-        <v>1.419345059362047</v>
+        <v>1.441574336305671</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.510831590098011</v>
+        <v>5.379621314143296</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08260270188198063</v>
+        <v>0.08256065353243905</v>
       </c>
       <c r="C44">
-        <v>875.1701533182785</v>
+        <v>861.206626325462</v>
       </c>
       <c r="D44">
-        <v>1373.532153318278</v>
+        <v>1374.529626325462</v>
       </c>
       <c r="E44">
-        <v>112.1619999999999</v>
+        <v>127.1229999999999</v>
       </c>
       <c r="F44">
-        <v>628.362</v>
+        <v>643.323</v>
       </c>
       <c r="G44">
         <v>130</v>
@@ -4877,28 +4877,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M44">
-        <v>34.7484186</v>
+        <v>35.5757619</v>
       </c>
       <c r="N44">
-        <v>152.1849147333334</v>
+        <v>151.3575714333334</v>
       </c>
       <c r="O44">
-        <v>22.21899755106667</v>
+        <v>22.09820542926667</v>
       </c>
       <c r="P44">
-        <v>129.9659171822667</v>
+        <v>129.2593660040667</v>
       </c>
       <c r="Q44">
-        <v>238.8659171822667</v>
+        <v>238.1593660040667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1082201687620356</v>
+        <v>0.1092164693551562</v>
       </c>
       <c r="T44">
-        <v>1.441574336305671</v>
+        <v>1.464583587878896</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.379621314143296</v>
+        <v>5.254513841721359</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08256065353243905</v>
+        <v>0.08251860518289747</v>
       </c>
       <c r="C45">
-        <v>861.206626325462</v>
+        <v>847.2445491355749</v>
       </c>
       <c r="D45">
-        <v>1374.529626325462</v>
+        <v>1375.528549135575</v>
       </c>
       <c r="E45">
-        <v>127.1229999999999</v>
+        <v>142.0839999999999</v>
       </c>
       <c r="F45">
-        <v>643.323</v>
+        <v>658.284</v>
       </c>
       <c r="G45">
         <v>130</v>
@@ -4959,28 +4959,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M45">
-        <v>35.5757619</v>
+        <v>36.4031052</v>
       </c>
       <c r="N45">
-        <v>151.3575714333334</v>
+        <v>150.5302281333334</v>
       </c>
       <c r="O45">
-        <v>22.09820542926667</v>
+        <v>21.97741330746667</v>
       </c>
       <c r="P45">
-        <v>129.2593660040667</v>
+        <v>128.5528148258667</v>
       </c>
       <c r="Q45">
-        <v>238.1593660040667</v>
+        <v>237.4528148258667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1092164693551562</v>
+        <v>0.1102483521123169</v>
       </c>
       <c r="T45">
-        <v>1.464583587878896</v>
+        <v>1.48841459843688</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.254513841721359</v>
+        <v>5.135093072591329</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08251860518289747</v>
+        <v>0.08247655683335588</v>
       </c>
       <c r="C46">
-        <v>847.2445491355749</v>
+        <v>833.2839249117966</v>
       </c>
       <c r="D46">
-        <v>1375.528549135575</v>
+        <v>1376.528924911797</v>
       </c>
       <c r="E46">
-        <v>142.0839999999999</v>
+        <v>157.045</v>
       </c>
       <c r="F46">
-        <v>658.284</v>
+        <v>673.245</v>
       </c>
       <c r="G46">
         <v>130</v>
@@ -5041,28 +5041,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M46">
-        <v>36.4031052</v>
+        <v>37.2304485</v>
       </c>
       <c r="N46">
-        <v>150.5302281333334</v>
+        <v>149.7028848333334</v>
       </c>
       <c r="O46">
-        <v>21.97741330746667</v>
+        <v>21.85662118566667</v>
       </c>
       <c r="P46">
-        <v>128.5528148258667</v>
+        <v>127.8462636476667</v>
       </c>
       <c r="Q46">
-        <v>237.4528148258667</v>
+        <v>236.7462636476667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1102483521123169</v>
+        <v>0.1113177578788289</v>
       </c>
       <c r="T46">
-        <v>1.48841459843688</v>
+        <v>1.513112191196972</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.135093072591329</v>
+        <v>5.02097989320041</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08247655683335588</v>
+        <v>0.08243450848381431</v>
       </c>
       <c r="C47">
-        <v>833.2839249117966</v>
+        <v>819.3247568265136</v>
       </c>
       <c r="D47">
-        <v>1376.528924911797</v>
+        <v>1377.530756826514</v>
       </c>
       <c r="E47">
-        <v>157.045</v>
+        <v>172.006</v>
       </c>
       <c r="F47">
-        <v>673.245</v>
+        <v>688.206</v>
       </c>
       <c r="G47">
         <v>130</v>
@@ -5123,28 +5123,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M47">
-        <v>37.2304485</v>
+        <v>38.0577918</v>
       </c>
       <c r="N47">
-        <v>149.7028848333334</v>
+        <v>148.8755415333334</v>
       </c>
       <c r="O47">
-        <v>21.85662118566667</v>
+        <v>21.73582906386667</v>
       </c>
       <c r="P47">
-        <v>127.8462636476667</v>
+        <v>127.1397124694667</v>
       </c>
       <c r="Q47">
-        <v>236.7462636476667</v>
+        <v>236.0397124694667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1113177578788289</v>
+        <v>0.1124267712663228</v>
       </c>
       <c r="T47">
-        <v>1.513112191196972</v>
+        <v>1.538724509614845</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.02097989320041</v>
+        <v>4.911828156391705</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08243450848381431</v>
+        <v>0.08239246013427273</v>
       </c>
       <c r="C48">
-        <v>819.3247568265136</v>
+        <v>805.3670480613572</v>
       </c>
       <c r="D48">
-        <v>1377.530756826514</v>
+        <v>1378.534048061357</v>
       </c>
       <c r="E48">
-        <v>172.006</v>
+        <v>186.967</v>
       </c>
       <c r="F48">
-        <v>688.206</v>
+        <v>703.167</v>
       </c>
       <c r="G48">
         <v>130</v>
@@ -5205,28 +5205,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M48">
-        <v>38.0577918</v>
+        <v>38.88513510000001</v>
       </c>
       <c r="N48">
-        <v>148.8755415333334</v>
+        <v>148.0481982333334</v>
       </c>
       <c r="O48">
-        <v>21.73582906386667</v>
+        <v>21.61503694206667</v>
       </c>
       <c r="P48">
-        <v>127.1397124694667</v>
+        <v>126.4331612912667</v>
       </c>
       <c r="Q48">
-        <v>236.0397124694667</v>
+        <v>235.3331612912667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1124267712663228</v>
+        <v>0.1135776342156089</v>
       </c>
       <c r="T48">
-        <v>1.538724509614845</v>
+        <v>1.565303330614524</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.911828156391705</v>
+        <v>4.807321174340817</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08239246013427273</v>
+        <v>0.08235041178473114</v>
       </c>
       <c r="C49">
-        <v>805.3670480613572</v>
+        <v>791.4108018072326</v>
       </c>
       <c r="D49">
-        <v>1378.534048061357</v>
+        <v>1379.538801807233</v>
       </c>
       <c r="E49">
-        <v>186.967</v>
+        <v>201.928</v>
       </c>
       <c r="F49">
-        <v>703.167</v>
+        <v>718.128</v>
       </c>
       <c r="G49">
         <v>130</v>
@@ -5287,28 +5287,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M49">
-        <v>38.88513510000001</v>
+        <v>39.7124784</v>
       </c>
       <c r="N49">
-        <v>148.0481982333334</v>
+        <v>147.2208549333334</v>
       </c>
       <c r="O49">
-        <v>21.61503694206667</v>
+        <v>21.49424482026667</v>
       </c>
       <c r="P49">
-        <v>126.4331612912667</v>
+        <v>125.7266101130667</v>
       </c>
       <c r="Q49">
-        <v>235.3331612912667</v>
+        <v>234.6266101130667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1135776342156089</v>
+        <v>0.114772761124483</v>
       </c>
       <c r="T49">
-        <v>1.565303330614524</v>
+        <v>1.592904413960345</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.807321174340817</v>
+        <v>4.707168649875384</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08235041178473114</v>
+        <v>0.08230836343518955</v>
       </c>
       <c r="C50">
-        <v>791.4108018072327</v>
+        <v>777.4560212643553</v>
       </c>
       <c r="D50">
-        <v>1379.538801807233</v>
+        <v>1380.545021264355</v>
       </c>
       <c r="E50">
-        <v>201.9279999999999</v>
+        <v>216.8889999999999</v>
       </c>
       <c r="F50">
-        <v>718.1279999999999</v>
+        <v>733.0889999999999</v>
       </c>
       <c r="G50">
         <v>130</v>
@@ -5369,28 +5369,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M50">
-        <v>39.71247839999999</v>
+        <v>40.5398217</v>
       </c>
       <c r="N50">
-        <v>147.2208549333334</v>
+        <v>146.3935116333334</v>
       </c>
       <c r="O50">
-        <v>21.49424482026667</v>
+        <v>21.37345269846667</v>
       </c>
       <c r="P50">
-        <v>125.7266101130667</v>
+        <v>125.0200589348667</v>
       </c>
       <c r="Q50">
-        <v>234.6266101130667</v>
+        <v>233.9200589348667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.114772761124483</v>
+        <v>0.1160147557552736</v>
       </c>
       <c r="T50">
-        <v>1.592904413960345</v>
+        <v>1.621587892731493</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.707168649875385</v>
+        <v>4.611103983551397</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08230836343518955</v>
+        <v>0.08226631508564797</v>
       </c>
       <c r="C51">
-        <v>777.4560212643553</v>
+        <v>763.5027096422834</v>
       </c>
       <c r="D51">
-        <v>1380.545021264355</v>
+        <v>1381.552709642283</v>
       </c>
       <c r="E51">
-        <v>216.8889999999999</v>
+        <v>231.8499999999999</v>
       </c>
       <c r="F51">
-        <v>733.0889999999999</v>
+        <v>748.05</v>
       </c>
       <c r="G51">
         <v>130</v>
@@ -5451,28 +5451,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M51">
-        <v>40.5398217</v>
+        <v>41.367165</v>
       </c>
       <c r="N51">
-        <v>146.3935116333334</v>
+        <v>145.5661683333334</v>
       </c>
       <c r="O51">
-        <v>21.37345269846667</v>
+        <v>21.25266057666667</v>
       </c>
       <c r="P51">
-        <v>125.0200589348667</v>
+        <v>124.3135077566667</v>
       </c>
       <c r="Q51">
-        <v>233.9200589348667</v>
+        <v>233.2135077566667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1160147557552736</v>
+        <v>0.1173064301712959</v>
       </c>
       <c r="T51">
-        <v>1.621587892731493</v>
+        <v>1.651418710653486</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.611103983551397</v>
+        <v>4.518881903880369</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08226631508564797</v>
+        <v>0.08331311673610639</v>
       </c>
       <c r="C52">
-        <v>763.5027096422834</v>
+        <v>723.8848571507449</v>
       </c>
       <c r="D52">
-        <v>1381.552709642283</v>
+        <v>1356.895857150745</v>
       </c>
       <c r="E52">
-        <v>231.8499999999999</v>
+        <v>246.8109999999999</v>
       </c>
       <c r="F52">
-        <v>748.05</v>
+        <v>763.011</v>
       </c>
       <c r="G52">
         <v>130</v>
@@ -5533,45 +5533,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M52">
-        <v>41.367165</v>
+        <v>44.1020358</v>
       </c>
       <c r="N52">
-        <v>145.5661683333334</v>
+        <v>142.8312975333334</v>
       </c>
       <c r="O52">
-        <v>21.25266057666667</v>
+        <v>20.85336943986667</v>
       </c>
       <c r="P52">
-        <v>124.3135077566667</v>
+        <v>121.9779280934667</v>
       </c>
       <c r="Q52">
-        <v>233.2135077566667</v>
+        <v>230.8779280934667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1173064301712959</v>
+        <v>0.1186508259920538</v>
       </c>
       <c r="T52">
-        <v>1.651418710653486</v>
+        <v>1.682467112980458</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.518881903880369</v>
+        <v>4.23865542581899</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08331311673610639</v>
+        <v>0.08329241838656481</v>
       </c>
       <c r="C53">
-        <v>723.8848571507449</v>
+        <v>709.402863531493</v>
       </c>
       <c r="D53">
-        <v>1356.895857150745</v>
+        <v>1357.374863531493</v>
       </c>
       <c r="E53">
-        <v>246.8109999999999</v>
+        <v>261.7719999999999</v>
       </c>
       <c r="F53">
-        <v>763.011</v>
+        <v>777.972</v>
       </c>
       <c r="G53">
         <v>130</v>
@@ -5615,28 +5615,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M53">
-        <v>44.1020358</v>
+        <v>44.9667816</v>
       </c>
       <c r="N53">
-        <v>142.8312975333334</v>
+        <v>141.9665517333333</v>
       </c>
       <c r="O53">
-        <v>20.85336943986667</v>
+        <v>20.72711655306667</v>
       </c>
       <c r="P53">
-        <v>121.9779280934667</v>
+        <v>121.2394351802667</v>
       </c>
       <c r="Q53">
-        <v>230.8779280934667</v>
+        <v>230.1394351802667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1186508259920538</v>
+        <v>0.1200512383053434</v>
       </c>
       <c r="T53">
-        <v>1.682467112980458</v>
+        <v>1.714809198737722</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.23865542581899</v>
+        <v>4.157142821476317</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08329241838656481</v>
+        <v>0.08327172003702324</v>
       </c>
       <c r="C54">
-        <v>709.402863531493</v>
+        <v>694.92120822581</v>
       </c>
       <c r="D54">
-        <v>1357.374863531493</v>
+        <v>1357.85420822581</v>
       </c>
       <c r="E54">
-        <v>261.7719999999999</v>
+        <v>276.7329999999999</v>
       </c>
       <c r="F54">
-        <v>777.972</v>
+        <v>792.933</v>
       </c>
       <c r="G54">
         <v>130</v>
@@ -5697,28 +5697,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M54">
-        <v>44.9667816</v>
+        <v>45.83152740000001</v>
       </c>
       <c r="N54">
-        <v>141.9665517333333</v>
+        <v>141.1018059333334</v>
       </c>
       <c r="O54">
-        <v>20.72711655306667</v>
+        <v>20.60086366626667</v>
       </c>
       <c r="P54">
-        <v>121.2394351802667</v>
+        <v>120.5009422670667</v>
       </c>
       <c r="Q54">
-        <v>230.1394351802667</v>
+        <v>229.4009422670667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1200512383053434</v>
+        <v>0.1215112426319643</v>
       </c>
       <c r="T54">
-        <v>1.714809198737722</v>
+        <v>1.748527543463379</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.157142821476317</v>
+        <v>4.078706164467331</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08327172003702324</v>
+        <v>0.08325102168748164</v>
       </c>
       <c r="C55">
-        <v>694.92120822581</v>
+        <v>680.4398915922402</v>
       </c>
       <c r="D55">
-        <v>1357.85420822581</v>
+        <v>1358.33389159224</v>
       </c>
       <c r="E55">
-        <v>276.7329999999999</v>
+        <v>291.694</v>
       </c>
       <c r="F55">
-        <v>792.933</v>
+        <v>807.894</v>
       </c>
       <c r="G55">
         <v>130</v>
@@ -5779,28 +5779,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M55">
-        <v>45.83152740000001</v>
+        <v>46.6962732</v>
       </c>
       <c r="N55">
-        <v>141.1018059333334</v>
+        <v>140.2370601333334</v>
       </c>
       <c r="O55">
-        <v>20.60086366626667</v>
+        <v>20.47461077946667</v>
       </c>
       <c r="P55">
-        <v>120.5009422670667</v>
+        <v>119.7624493538667</v>
       </c>
       <c r="Q55">
-        <v>229.4009422670667</v>
+        <v>228.6624493538667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1215112426319643</v>
+        <v>0.1230347254075688</v>
       </c>
       <c r="T55">
-        <v>1.748527543463379</v>
+        <v>1.783711903177108</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.078706164467331</v>
+        <v>4.003174568829047</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08325102168748164</v>
+        <v>0.08487427333794006</v>
       </c>
       <c r="C56">
-        <v>680.4398915922402</v>
+        <v>628.8612899719742</v>
       </c>
       <c r="D56">
-        <v>1358.33389159224</v>
+        <v>1321.716289971974</v>
       </c>
       <c r="E56">
-        <v>291.694</v>
+        <v>306.655</v>
       </c>
       <c r="F56">
-        <v>807.894</v>
+        <v>822.855</v>
       </c>
       <c r="G56">
         <v>130</v>
@@ -5861,45 +5861,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M56">
-        <v>46.6962732</v>
+        <v>50.4410115</v>
       </c>
       <c r="N56">
-        <v>140.2370601333334</v>
+        <v>136.4923218333334</v>
       </c>
       <c r="O56">
-        <v>20.47461077946667</v>
+        <v>19.92787898766667</v>
       </c>
       <c r="P56">
-        <v>119.7624493538667</v>
+        <v>116.5644428456667</v>
       </c>
       <c r="Q56">
-        <v>228.6624493538667</v>
+        <v>225.4644428456667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1230347254075688</v>
+        <v>0.1246259185287557</v>
       </c>
       <c r="T56">
-        <v>1.783711903177108</v>
+        <v>1.820460012211448</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.003174568829047</v>
+        <v>3.705979078816319</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08487427333794006</v>
+        <v>0.08488346498839848</v>
       </c>
       <c r="C57">
-        <v>628.8612899719742</v>
+        <v>613.6985634691193</v>
       </c>
       <c r="D57">
-        <v>1321.716289971974</v>
+        <v>1321.514563469119</v>
       </c>
       <c r="E57">
-        <v>306.655</v>
+        <v>321.616</v>
       </c>
       <c r="F57">
-        <v>822.855</v>
+        <v>837.816</v>
       </c>
       <c r="G57">
         <v>130</v>
@@ -5943,28 +5943,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M57">
-        <v>50.4410115</v>
+        <v>51.3581208</v>
       </c>
       <c r="N57">
-        <v>136.4923218333334</v>
+        <v>135.5752125333334</v>
       </c>
       <c r="O57">
-        <v>19.92787898766667</v>
+        <v>19.79398102986667</v>
       </c>
       <c r="P57">
-        <v>116.5644428456667</v>
+        <v>115.7812315034667</v>
       </c>
       <c r="Q57">
-        <v>225.4644428456667</v>
+        <v>224.6812315034667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1246259185287557</v>
+        <v>0.1262894386099966</v>
       </c>
       <c r="T57">
-        <v>1.820460012211448</v>
+        <v>1.858878489838258</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.705979078816319</v>
+        <v>3.639800880980314</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08488346498839848</v>
+        <v>0.08489265663885689</v>
       </c>
       <c r="C58">
-        <v>613.6985634691193</v>
+        <v>598.5358985337466</v>
       </c>
       <c r="D58">
-        <v>1321.514563469119</v>
+        <v>1321.312898533747</v>
       </c>
       <c r="E58">
-        <v>321.616</v>
+        <v>336.577</v>
       </c>
       <c r="F58">
-        <v>837.816</v>
+        <v>852.777</v>
       </c>
       <c r="G58">
         <v>130</v>
@@ -6025,28 +6025,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M58">
-        <v>51.3581208</v>
+        <v>52.2752301</v>
       </c>
       <c r="N58">
-        <v>135.5752125333334</v>
+        <v>134.6581032333333</v>
       </c>
       <c r="O58">
-        <v>19.79398102986667</v>
+        <v>19.66008307206667</v>
       </c>
       <c r="P58">
-        <v>115.7812315034667</v>
+        <v>114.9980201612667</v>
       </c>
       <c r="Q58">
-        <v>224.6812315034667</v>
+        <v>223.8980201612667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1262894386099966</v>
+        <v>0.1280303317182719</v>
       </c>
       <c r="T58">
-        <v>1.858878489838258</v>
+        <v>1.899083873401198</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.639800880980314</v>
+        <v>3.575944725173641</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08489265663885689</v>
+        <v>0.08490184828931531</v>
       </c>
       <c r="C59">
-        <v>598.5358985337466</v>
+        <v>583.3732951376746</v>
       </c>
       <c r="D59">
-        <v>1321.312898533747</v>
+        <v>1321.111295137675</v>
       </c>
       <c r="E59">
-        <v>336.577</v>
+        <v>351.538</v>
       </c>
       <c r="F59">
-        <v>852.777</v>
+        <v>867.7380000000001</v>
       </c>
       <c r="G59">
         <v>130</v>
@@ -6107,28 +6107,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M59">
-        <v>52.2752301</v>
+        <v>53.1923394</v>
       </c>
       <c r="N59">
-        <v>134.6581032333333</v>
+        <v>133.7409939333334</v>
       </c>
       <c r="O59">
-        <v>19.66008307206667</v>
+        <v>19.52618511426667</v>
       </c>
       <c r="P59">
-        <v>114.9980201612667</v>
+        <v>114.2148088190667</v>
       </c>
       <c r="Q59">
-        <v>223.8980201612667</v>
+        <v>223.1148088190667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1280303317182719</v>
+        <v>0.1298541244983698</v>
       </c>
       <c r="T59">
-        <v>1.899083873401198</v>
+        <v>1.941203799038564</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.575944725173641</v>
+        <v>3.514290505774095</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08490184828931532</v>
+        <v>0.08632184793977374</v>
       </c>
       <c r="C60">
-        <v>583.3732951376743</v>
+        <v>537.9888680679225</v>
       </c>
       <c r="D60">
-        <v>1321.111295137674</v>
+        <v>1290.687868067922</v>
       </c>
       <c r="E60">
-        <v>351.5379999999999</v>
+        <v>366.4989999999999</v>
       </c>
       <c r="F60">
-        <v>867.7379999999999</v>
+        <v>882.699</v>
       </c>
       <c r="G60">
         <v>130</v>
@@ -6189,45 +6189,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M60">
-        <v>53.19233939999999</v>
+        <v>56.5810059</v>
       </c>
       <c r="N60">
-        <v>133.7409939333334</v>
+        <v>130.3523274333334</v>
       </c>
       <c r="O60">
-        <v>19.52618511426667</v>
+        <v>19.03143980526667</v>
       </c>
       <c r="P60">
-        <v>114.2148088190667</v>
+        <v>111.3208876280667</v>
       </c>
       <c r="Q60">
-        <v>223.1148088190667</v>
+        <v>220.2208876280667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1298541244983698</v>
+        <v>0.131766882779936</v>
       </c>
       <c r="T60">
-        <v>1.941203799038564</v>
+        <v>1.985378355194826</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.514290505774096</v>
+        <v>3.30381778054132</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08632184793977374</v>
+        <v>0.08635495159023215</v>
       </c>
       <c r="C61">
-        <v>537.9888680679225</v>
+        <v>522.3353286206544</v>
       </c>
       <c r="D61">
-        <v>1290.687868067922</v>
+        <v>1289.995328620654</v>
       </c>
       <c r="E61">
-        <v>366.4989999999999</v>
+        <v>381.4599999999999</v>
       </c>
       <c r="F61">
-        <v>882.699</v>
+        <v>897.66</v>
       </c>
       <c r="G61">
         <v>130</v>
@@ -6271,28 +6271,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M61">
-        <v>56.5810059</v>
+        <v>57.540006</v>
       </c>
       <c r="N61">
-        <v>130.3523274333334</v>
+        <v>129.3933273333334</v>
       </c>
       <c r="O61">
-        <v>19.03143980526667</v>
+        <v>18.89142579066667</v>
       </c>
       <c r="P61">
-        <v>111.3208876280667</v>
+        <v>110.5019015426667</v>
       </c>
       <c r="Q61">
-        <v>220.2208876280667</v>
+        <v>219.4019015426667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.131766882779936</v>
+        <v>0.1337752789755804</v>
       </c>
       <c r="T61">
-        <v>1.985378355194826</v>
+        <v>2.0317616391589</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.30381778054132</v>
+        <v>3.248754150865632</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08635495159023215</v>
+        <v>0.08638805524069057</v>
       </c>
       <c r="C62">
-        <v>522.3353286206544</v>
+        <v>506.6825319613107</v>
       </c>
       <c r="D62">
-        <v>1289.995328620654</v>
+        <v>1289.303531961311</v>
       </c>
       <c r="E62">
-        <v>381.4599999999999</v>
+        <v>396.4209999999999</v>
       </c>
       <c r="F62">
-        <v>897.66</v>
+        <v>912.621</v>
       </c>
       <c r="G62">
         <v>130</v>
@@ -6353,28 +6353,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M62">
-        <v>57.540006</v>
+        <v>58.4990061</v>
       </c>
       <c r="N62">
-        <v>129.3933273333334</v>
+        <v>128.4343272333334</v>
       </c>
       <c r="O62">
-        <v>18.89142579066667</v>
+        <v>18.75141177606667</v>
       </c>
       <c r="P62">
-        <v>110.5019015426667</v>
+        <v>109.6829154572667</v>
       </c>
       <c r="Q62">
-        <v>219.4019015426667</v>
+        <v>218.5829154572667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1337752789755804</v>
+        <v>0.1358866698479246</v>
       </c>
       <c r="T62">
-        <v>2.0317616391589</v>
+        <v>2.080523553069851</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.248754150865632</v>
+        <v>3.195495886097343</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08638805524069057</v>
+        <v>0.08642115889114899</v>
       </c>
       <c r="C63">
-        <v>506.6825319613107</v>
+        <v>491.0304768955078</v>
       </c>
       <c r="D63">
-        <v>1289.303531961311</v>
+        <v>1288.612476895508</v>
       </c>
       <c r="E63">
-        <v>396.4209999999999</v>
+        <v>411.3819999999999</v>
       </c>
       <c r="F63">
-        <v>912.621</v>
+        <v>927.582</v>
       </c>
       <c r="G63">
         <v>130</v>
@@ -6435,28 +6435,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M63">
-        <v>58.4990061</v>
+        <v>59.45800620000001</v>
       </c>
       <c r="N63">
-        <v>128.4343272333334</v>
+        <v>127.4753271333334</v>
       </c>
       <c r="O63">
-        <v>18.75141177606667</v>
+        <v>18.61139776146667</v>
       </c>
       <c r="P63">
-        <v>109.6829154572667</v>
+        <v>108.8639293718667</v>
       </c>
       <c r="Q63">
-        <v>218.5829154572667</v>
+        <v>217.7639293718667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1358866698479246</v>
+        <v>0.1381091865556552</v>
       </c>
       <c r="T63">
-        <v>2.080523553069851</v>
+        <v>2.13185188350243</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.195495886097343</v>
+        <v>3.143955629869966</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08642115889114899</v>
+        <v>0.08645426254160742</v>
       </c>
       <c r="C64">
-        <v>491.0304768955078</v>
+        <v>475.3791622314225</v>
       </c>
       <c r="D64">
-        <v>1288.612476895508</v>
+        <v>1287.922162231422</v>
       </c>
       <c r="E64">
-        <v>411.3819999999999</v>
+        <v>426.3429999999998</v>
       </c>
       <c r="F64">
-        <v>927.582</v>
+        <v>942.5429999999999</v>
       </c>
       <c r="G64">
         <v>130</v>
@@ -6517,28 +6517,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M64">
-        <v>59.45800620000001</v>
+        <v>60.4170063</v>
       </c>
       <c r="N64">
-        <v>127.4753271333334</v>
+        <v>126.5163270333334</v>
       </c>
       <c r="O64">
-        <v>18.61139776146667</v>
+        <v>18.47138374686667</v>
       </c>
       <c r="P64">
-        <v>108.8639293718667</v>
+        <v>108.0449432864667</v>
       </c>
       <c r="Q64">
-        <v>217.7639293718667</v>
+        <v>216.9449432864667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1381091865556552</v>
+        <v>0.1404518393016417</v>
       </c>
       <c r="T64">
-        <v>2.13185188350243</v>
+        <v>2.185954718282717</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.143955629869966</v>
+        <v>3.094051572252983</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08645426254160742</v>
+        <v>0.08648736619206585</v>
       </c>
       <c r="C65">
-        <v>475.3791622314225</v>
+        <v>459.7285867797834</v>
       </c>
       <c r="D65">
-        <v>1287.922162231422</v>
+        <v>1287.232586779783</v>
       </c>
       <c r="E65">
-        <v>426.3429999999998</v>
+        <v>441.3039999999999</v>
       </c>
       <c r="F65">
-        <v>942.5429999999999</v>
+        <v>957.5039999999999</v>
       </c>
       <c r="G65">
         <v>130</v>
@@ -6599,28 +6599,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M65">
-        <v>60.4170063</v>
+        <v>61.3760064</v>
       </c>
       <c r="N65">
-        <v>126.5163270333334</v>
+        <v>125.5573269333334</v>
       </c>
       <c r="O65">
-        <v>18.47138374686667</v>
+        <v>18.33136973226667</v>
       </c>
       <c r="P65">
-        <v>108.0449432864667</v>
+        <v>107.2259572010667</v>
       </c>
       <c r="Q65">
-        <v>216.9449432864667</v>
+        <v>216.1259572010667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1404518393016417</v>
+        <v>0.1429246394224051</v>
       </c>
       <c r="T65">
-        <v>2.185954718282717</v>
+        <v>2.243063266106353</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.094051572252983</v>
+        <v>3.04570701643653</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08648736619206585</v>
+        <v>0.09085024984252425</v>
       </c>
       <c r="C66">
-        <v>459.7285867797834</v>
+        <v>359.9210995428723</v>
       </c>
       <c r="D66">
-        <v>1287.232586779783</v>
+        <v>1202.386099542872</v>
       </c>
       <c r="E66">
-        <v>441.3039999999999</v>
+        <v>456.2649999999999</v>
       </c>
       <c r="F66">
-        <v>957.5039999999999</v>
+        <v>972.4649999999999</v>
       </c>
       <c r="G66">
         <v>130</v>
@@ -6681,45 +6681,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M66">
-        <v>61.3760064</v>
+        <v>69.92023349999999</v>
       </c>
       <c r="N66">
-        <v>125.5573269333334</v>
+        <v>117.0130998333334</v>
       </c>
       <c r="O66">
-        <v>18.33136973226667</v>
+        <v>17.08391257566667</v>
       </c>
       <c r="P66">
-        <v>107.2259572010667</v>
+        <v>99.9291872576667</v>
       </c>
       <c r="Q66">
-        <v>216.1259572010667</v>
+        <v>208.8291872576667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1429246394224051</v>
+        <v>0.1455387424072122</v>
       </c>
       <c r="T66">
-        <v>2.243063266106353</v>
+        <v>2.303435159519911</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.146</v>
       </c>
       <c r="W66">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.04570701643653</v>
+        <v>2.673522726913282</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09085024984252425</v>
+        <v>0.09094996549298268</v>
       </c>
       <c r="C67">
-        <v>359.9210995428723</v>
+        <v>343.1514404557188</v>
       </c>
       <c r="D67">
-        <v>1202.386099542872</v>
+        <v>1200.577440455719</v>
       </c>
       <c r="E67">
-        <v>456.2649999999999</v>
+        <v>471.2259999999999</v>
       </c>
       <c r="F67">
-        <v>972.4649999999999</v>
+        <v>987.4259999999999</v>
       </c>
       <c r="G67">
         <v>130</v>
@@ -6763,28 +6763,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M67">
-        <v>69.92023349999999</v>
+        <v>70.99592939999999</v>
       </c>
       <c r="N67">
-        <v>117.0130998333334</v>
+        <v>115.9374039333334</v>
       </c>
       <c r="O67">
-        <v>17.08391257566667</v>
+        <v>16.92686097426667</v>
       </c>
       <c r="P67">
-        <v>99.9291872576667</v>
+        <v>99.0105429590667</v>
       </c>
       <c r="Q67">
-        <v>208.8291872576667</v>
+        <v>207.9105429590667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1455387424072122</v>
+        <v>0.1483066161558314</v>
       </c>
       <c r="T67">
-        <v>2.303435159519911</v>
+        <v>2.367358340781325</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.673522726913282</v>
+        <v>2.633014806808535</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09094996549298268</v>
+        <v>0.09104968114344109</v>
       </c>
       <c r="C68">
-        <v>343.1514404557188</v>
+        <v>326.3872144559796</v>
       </c>
       <c r="D68">
-        <v>1200.577440455719</v>
+        <v>1198.77421445598</v>
       </c>
       <c r="E68">
-        <v>471.2259999999999</v>
+        <v>486.1869999999999</v>
       </c>
       <c r="F68">
-        <v>987.4259999999999</v>
+        <v>1002.387</v>
       </c>
       <c r="G68">
         <v>130</v>
@@ -6845,28 +6845,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M68">
-        <v>70.99592939999999</v>
+        <v>72.07162530000001</v>
       </c>
       <c r="N68">
-        <v>115.9374039333334</v>
+        <v>114.8617080333334</v>
       </c>
       <c r="O68">
-        <v>16.92686097426667</v>
+        <v>16.76980937286667</v>
       </c>
       <c r="P68">
-        <v>99.0105429590667</v>
+        <v>98.09189866046668</v>
       </c>
       <c r="Q68">
-        <v>207.9105429590667</v>
+        <v>206.9918986604667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1483066161558314</v>
+        <v>0.1512422398286093</v>
       </c>
       <c r="T68">
-        <v>2.367358340781325</v>
+        <v>2.435155654240401</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.633014806808535</v>
+        <v>2.593716078348705</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09104968114344109</v>
+        <v>0.0911493967938995</v>
       </c>
       <c r="C69">
-        <v>326.3872144559796</v>
+        <v>309.6283970994377</v>
       </c>
       <c r="D69">
-        <v>1198.77421445598</v>
+        <v>1196.976397099438</v>
       </c>
       <c r="E69">
-        <v>486.1869999999999</v>
+        <v>501.1479999999999</v>
       </c>
       <c r="F69">
-        <v>1002.387</v>
+        <v>1017.348</v>
       </c>
       <c r="G69">
         <v>130</v>
@@ -6927,28 +6927,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M69">
-        <v>72.07162530000001</v>
+        <v>73.14732120000001</v>
       </c>
       <c r="N69">
-        <v>114.8617080333334</v>
+        <v>113.7860121333334</v>
       </c>
       <c r="O69">
-        <v>16.76980937286667</v>
+        <v>16.61275777146667</v>
       </c>
       <c r="P69">
-        <v>98.09189866046668</v>
+        <v>97.1732543618667</v>
       </c>
       <c r="Q69">
-        <v>206.9918986604667</v>
+        <v>206.0732543618667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1512422398286093</v>
+        <v>0.154361339980936</v>
       </c>
       <c r="T69">
-        <v>2.435155654240401</v>
+        <v>2.507190299790669</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.593716078348705</v>
+        <v>2.555573194843578</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0911493967938995</v>
+        <v>0.09124911244435793</v>
       </c>
       <c r="C70">
-        <v>309.6283970994377</v>
+        <v>292.8749640882941</v>
       </c>
       <c r="D70">
-        <v>1196.976397099438</v>
+        <v>1195.183964088294</v>
       </c>
       <c r="E70">
-        <v>501.1479999999999</v>
+        <v>516.1089999999999</v>
       </c>
       <c r="F70">
-        <v>1017.348</v>
+        <v>1032.309</v>
       </c>
       <c r="G70">
         <v>130</v>
@@ -7009,28 +7009,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M70">
-        <v>73.14732120000001</v>
+        <v>74.22301710000001</v>
       </c>
       <c r="N70">
-        <v>113.7860121333334</v>
+        <v>112.7103162333334</v>
       </c>
       <c r="O70">
-        <v>16.61275777146667</v>
+        <v>16.45570617006667</v>
       </c>
       <c r="P70">
-        <v>97.1732543618667</v>
+        <v>96.25461006326668</v>
       </c>
       <c r="Q70">
-        <v>206.0732543618667</v>
+        <v>205.1546100632667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.154361339980936</v>
+        <v>0.1576816724011546</v>
       </c>
       <c r="T70">
-        <v>2.507190299790669</v>
+        <v>2.583872341828052</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.555573194843578</v>
+        <v>2.518535902164685</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09124911244435793</v>
+        <v>0.09368024809481634</v>
       </c>
       <c r="C71">
-        <v>292.8749640882941</v>
+        <v>235.8156429149899</v>
       </c>
       <c r="D71">
-        <v>1195.183964088294</v>
+        <v>1153.08564291499</v>
       </c>
       <c r="E71">
-        <v>516.1089999999999</v>
+        <v>531.0699999999999</v>
       </c>
       <c r="F71">
-        <v>1032.309</v>
+        <v>1047.27</v>
       </c>
       <c r="G71">
         <v>130</v>
@@ -7091,45 +7091,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M71">
-        <v>74.22301710000001</v>
+        <v>79.383066</v>
       </c>
       <c r="N71">
-        <v>112.7103162333334</v>
+        <v>107.5502673333334</v>
       </c>
       <c r="O71">
-        <v>16.45570617006667</v>
+        <v>15.70233903066667</v>
       </c>
       <c r="P71">
-        <v>96.25461006326668</v>
+        <v>91.8479283026667</v>
       </c>
       <c r="Q71">
-        <v>205.1546100632667</v>
+        <v>200.7479283026667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1576816724011546</v>
+        <v>0.1612233603160545</v>
       </c>
       <c r="T71">
-        <v>2.583872341828052</v>
+        <v>2.665666520001258</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.518535902164685</v>
+        <v>2.354826321942936</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09368024809481634</v>
+        <v>0.09381326974527476</v>
       </c>
       <c r="C72">
-        <v>235.8156429149899</v>
+        <v>218.6366072452197</v>
       </c>
       <c r="D72">
-        <v>1153.08564291499</v>
+        <v>1150.86760724522</v>
       </c>
       <c r="E72">
-        <v>531.0699999999999</v>
+        <v>546.0309999999999</v>
       </c>
       <c r="F72">
-        <v>1047.27</v>
+        <v>1062.231</v>
       </c>
       <c r="G72">
         <v>130</v>
@@ -7173,28 +7173,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M72">
-        <v>79.383066</v>
+        <v>80.5171098</v>
       </c>
       <c r="N72">
-        <v>107.5502673333334</v>
+        <v>106.4162235333334</v>
       </c>
       <c r="O72">
-        <v>15.70233903066667</v>
+        <v>15.53676863586667</v>
       </c>
       <c r="P72">
-        <v>91.8479283026667</v>
+        <v>90.8794548974667</v>
       </c>
       <c r="Q72">
-        <v>200.7479283026667</v>
+        <v>199.7794548974667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1612233603160545</v>
+        <v>0.165009302569913</v>
       </c>
       <c r="T72">
-        <v>2.665666520001258</v>
+        <v>2.753101675979515</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.354826321942936</v>
+        <v>2.321659754028247</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09381326974527476</v>
+        <v>0.09394629139573318</v>
       </c>
       <c r="C73">
-        <v>218.6366072452197</v>
+        <v>201.4660882664696</v>
       </c>
       <c r="D73">
-        <v>1150.86760724522</v>
+        <v>1148.65808826647</v>
       </c>
       <c r="E73">
-        <v>546.0309999999999</v>
+        <v>560.992</v>
       </c>
       <c r="F73">
-        <v>1062.231</v>
+        <v>1077.192</v>
       </c>
       <c r="G73">
         <v>130</v>
@@ -7255,28 +7255,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M73">
-        <v>80.5171098</v>
+        <v>81.6511536</v>
       </c>
       <c r="N73">
-        <v>106.4162235333334</v>
+        <v>105.2821797333334</v>
       </c>
       <c r="O73">
-        <v>15.53676863586667</v>
+        <v>15.37119824106667</v>
       </c>
       <c r="P73">
-        <v>90.8794548974667</v>
+        <v>89.9109814922667</v>
       </c>
       <c r="Q73">
-        <v>199.7794548974667</v>
+        <v>198.8109814922667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1650093025699129</v>
+        <v>0.1690656692704756</v>
       </c>
       <c r="T73">
-        <v>2.753101675979514</v>
+        <v>2.846782200241932</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.321659754028247</v>
+        <v>2.289414479666743</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09394629139573318</v>
+        <v>0.09407931304619159</v>
       </c>
       <c r="C74">
-        <v>201.4660882664696</v>
+        <v>184.3040370198541</v>
       </c>
       <c r="D74">
-        <v>1148.65808826647</v>
+        <v>1146.457037019854</v>
       </c>
       <c r="E74">
-        <v>560.992</v>
+        <v>575.953</v>
       </c>
       <c r="F74">
-        <v>1077.192</v>
+        <v>1092.153</v>
       </c>
       <c r="G74">
         <v>130</v>
@@ -7337,28 +7337,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M74">
-        <v>81.6511536</v>
+        <v>82.7851974</v>
       </c>
       <c r="N74">
-        <v>105.2821797333334</v>
+        <v>104.1481359333334</v>
       </c>
       <c r="O74">
-        <v>15.37119824106667</v>
+        <v>15.20562784626667</v>
       </c>
       <c r="P74">
-        <v>89.9109814922667</v>
+        <v>88.9425080870667</v>
       </c>
       <c r="Q74">
-        <v>198.8109814922667</v>
+        <v>197.8425080870667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1690656692704756</v>
+        <v>0.1734225075784874</v>
       </c>
       <c r="T74">
-        <v>2.846782200241932</v>
+        <v>2.947402022597861</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.289414479666743</v>
+        <v>2.258052637479528</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09407931304619159</v>
+        <v>0.09421233469665002</v>
       </c>
       <c r="C75">
-        <v>184.3040370198541</v>
+        <v>167.1504049210275</v>
       </c>
       <c r="D75">
-        <v>1146.457037019854</v>
+        <v>1144.264404921028</v>
       </c>
       <c r="E75">
-        <v>575.953</v>
+        <v>590.914</v>
       </c>
       <c r="F75">
-        <v>1092.153</v>
+        <v>1107.114</v>
       </c>
       <c r="G75">
         <v>130</v>
@@ -7419,28 +7419,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M75">
-        <v>82.7851974</v>
+        <v>83.91924120000002</v>
       </c>
       <c r="N75">
-        <v>104.1481359333334</v>
+        <v>103.0140921333333</v>
       </c>
       <c r="O75">
-        <v>15.20562784626667</v>
+        <v>15.04005745146667</v>
       </c>
       <c r="P75">
-        <v>88.9425080870667</v>
+        <v>87.97403468186668</v>
       </c>
       <c r="Q75">
-        <v>197.8425080870667</v>
+        <v>196.8740346818667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1734225075784874</v>
+        <v>0.1781144872948077</v>
       </c>
       <c r="T75">
-        <v>2.947402022597861</v>
+        <v>3.055761831288863</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.258052637479528</v>
+        <v>2.227538412648723</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09421233469665002</v>
+        <v>0.09434535634710844</v>
       </c>
       <c r="C76">
-        <v>167.1504049210275</v>
+        <v>150.0051437566126</v>
       </c>
       <c r="D76">
-        <v>1144.264404921028</v>
+        <v>1142.080143756612</v>
       </c>
       <c r="E76">
-        <v>590.914</v>
+        <v>605.8749999999998</v>
       </c>
       <c r="F76">
-        <v>1107.114</v>
+        <v>1122.075</v>
       </c>
       <c r="G76">
         <v>130</v>
@@ -7501,28 +7501,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M76">
-        <v>83.91924120000002</v>
+        <v>85.05328499999999</v>
       </c>
       <c r="N76">
-        <v>103.0140921333333</v>
+        <v>101.8800483333334</v>
       </c>
       <c r="O76">
-        <v>15.04005745146667</v>
+        <v>14.87448705666667</v>
       </c>
       <c r="P76">
-        <v>87.97403468186668</v>
+        <v>87.00556127666671</v>
       </c>
       <c r="Q76">
-        <v>196.8740346818667</v>
+        <v>195.9055612766667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1781144872948077</v>
+        <v>0.1831818253884337</v>
       </c>
       <c r="T76">
-        <v>3.055761831288863</v>
+        <v>3.172790424675144</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.227538412648723</v>
+        <v>2.197837900480074</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09434535634710844</v>
+        <v>0.09447837799756686</v>
       </c>
       <c r="C77">
-        <v>150.0051437566126</v>
+        <v>132.8682056806626</v>
       </c>
       <c r="D77">
-        <v>1142.080143756612</v>
+        <v>1139.904205680662</v>
       </c>
       <c r="E77">
-        <v>605.8749999999998</v>
+        <v>620.8359999999998</v>
       </c>
       <c r="F77">
-        <v>1122.075</v>
+        <v>1137.036</v>
       </c>
       <c r="G77">
         <v>130</v>
@@ -7583,28 +7583,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M77">
-        <v>85.05328499999999</v>
+        <v>86.18732879999999</v>
       </c>
       <c r="N77">
-        <v>101.8800483333334</v>
+        <v>100.7460045333334</v>
       </c>
       <c r="O77">
-        <v>14.87448705666667</v>
+        <v>14.70891666186667</v>
       </c>
       <c r="P77">
-        <v>87.00556127666671</v>
+        <v>86.03708787146671</v>
       </c>
       <c r="Q77">
-        <v>195.9055612766667</v>
+        <v>194.9370878714667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1831818253884337</v>
+        <v>0.1886714416565286</v>
       </c>
       <c r="T77">
-        <v>3.172790424675144</v>
+        <v>3.299571400843616</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.197837900480074</v>
+        <v>2.168918980736915</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09447837799756686</v>
+        <v>0.09461139964802529</v>
       </c>
       <c r="C78">
-        <v>132.8682056806626</v>
+        <v>115.7395432111709</v>
       </c>
       <c r="D78">
-        <v>1139.904205680662</v>
+        <v>1137.736543211171</v>
       </c>
       <c r="E78">
-        <v>620.8359999999998</v>
+        <v>635.7969999999998</v>
       </c>
       <c r="F78">
-        <v>1137.036</v>
+        <v>1151.997</v>
       </c>
       <c r="G78">
         <v>130</v>
@@ -7665,28 +7665,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M78">
-        <v>86.18732879999999</v>
+        <v>87.32137259999999</v>
       </c>
       <c r="N78">
-        <v>100.7460045333334</v>
+        <v>99.61196073333338</v>
       </c>
       <c r="O78">
-        <v>14.70891666186667</v>
+        <v>14.54334626706667</v>
       </c>
       <c r="P78">
-        <v>86.03708787146671</v>
+        <v>85.06861446626671</v>
       </c>
       <c r="Q78">
-        <v>194.9370878714667</v>
+        <v>193.9686144662667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1886714416565286</v>
+        <v>0.1946384158609795</v>
       </c>
       <c r="T78">
-        <v>3.299571400843616</v>
+        <v>3.437376809722389</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.168918980736915</v>
+        <v>2.140751201766306</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09461139964802529</v>
+        <v>0.09474442129848369</v>
       </c>
       <c r="C79">
-        <v>115.7395432111709</v>
+        <v>98.61910922661582</v>
       </c>
       <c r="D79">
-        <v>1137.736543211171</v>
+        <v>1135.577109226616</v>
       </c>
       <c r="E79">
-        <v>635.7969999999998</v>
+        <v>650.7579999999998</v>
       </c>
       <c r="F79">
-        <v>1151.997</v>
+        <v>1166.958</v>
       </c>
       <c r="G79">
         <v>130</v>
@@ -7747,28 +7747,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M79">
-        <v>87.32137259999999</v>
+        <v>88.45541639999999</v>
       </c>
       <c r="N79">
-        <v>99.61196073333338</v>
+        <v>98.47791693333338</v>
       </c>
       <c r="O79">
-        <v>14.54334626706667</v>
+        <v>14.37777587226667</v>
       </c>
       <c r="P79">
-        <v>85.06861446626671</v>
+        <v>84.10014106106671</v>
       </c>
       <c r="Q79">
-        <v>193.9686144662667</v>
+        <v>193.0001410610667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1946384158609795</v>
+        <v>0.201147842265835</v>
       </c>
       <c r="T79">
-        <v>3.437376809722389</v>
+        <v>3.587709983044687</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.140751201766306</v>
+        <v>2.113305673538533</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09474442129848369</v>
+        <v>0.09487744294894213</v>
       </c>
       <c r="C80">
-        <v>98.61910922661582</v>
+        <v>81.50685696254527</v>
       </c>
       <c r="D80">
-        <v>1135.577109226616</v>
+        <v>1133.425856962545</v>
       </c>
       <c r="E80">
-        <v>650.7579999999998</v>
+        <v>665.7189999999998</v>
       </c>
       <c r="F80">
-        <v>1166.958</v>
+        <v>1181.919</v>
       </c>
       <c r="G80">
         <v>130</v>
@@ -7829,28 +7829,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M80">
-        <v>88.45541639999999</v>
+        <v>89.58946019999999</v>
       </c>
       <c r="N80">
-        <v>98.47791693333338</v>
+        <v>97.34387313333337</v>
       </c>
       <c r="O80">
-        <v>14.37777587226667</v>
+        <v>14.21220547746667</v>
       </c>
       <c r="P80">
-        <v>84.10014106106671</v>
+        <v>83.13166765586671</v>
       </c>
       <c r="Q80">
-        <v>193.0001410610667</v>
+        <v>192.0316676558667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.201147842265835</v>
+        <v>0.2082772140425815</v>
       </c>
       <c r="T80">
-        <v>3.587709983044687</v>
+        <v>3.7523606014453</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.113305673538533</v>
+        <v>2.086554968810197</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09487744294894213</v>
+        <v>0.09501046459940053</v>
       </c>
       <c r="C81">
-        <v>81.50685696254527</v>
+        <v>64.40274000820341</v>
       </c>
       <c r="D81">
-        <v>1133.425856962545</v>
+        <v>1131.282740008203</v>
       </c>
       <c r="E81">
-        <v>665.7189999999998</v>
+        <v>680.6799999999998</v>
       </c>
       <c r="F81">
-        <v>1181.919</v>
+        <v>1196.88</v>
       </c>
       <c r="G81">
         <v>130</v>
@@ -7911,28 +7911,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M81">
-        <v>89.58946019999999</v>
+        <v>90.72350400000001</v>
       </c>
       <c r="N81">
-        <v>97.34387313333337</v>
+        <v>96.20982933333336</v>
       </c>
       <c r="O81">
-        <v>14.21220547746667</v>
+        <v>14.04663508266667</v>
       </c>
       <c r="P81">
-        <v>83.13166765586671</v>
+        <v>82.16319425066669</v>
       </c>
       <c r="Q81">
-        <v>192.0316676558667</v>
+        <v>191.0631942506667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2082772140425815</v>
+        <v>0.2161195229970027</v>
       </c>
       <c r="T81">
-        <v>3.7523606014453</v>
+        <v>3.933476281685973</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.086554968810197</v>
+        <v>2.060473031700069</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09501046459940053</v>
+        <v>0.09514348624985895</v>
       </c>
       <c r="C82">
-        <v>64.40274000820341</v>
+        <v>47.3067123031899</v>
       </c>
       <c r="D82">
-        <v>1131.282740008203</v>
+        <v>1129.14771230319</v>
       </c>
       <c r="E82">
-        <v>680.6799999999998</v>
+        <v>695.6409999999998</v>
       </c>
       <c r="F82">
-        <v>1196.88</v>
+        <v>1211.841</v>
       </c>
       <c r="G82">
         <v>130</v>
@@ -7993,28 +7993,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M82">
-        <v>90.72350400000001</v>
+        <v>91.85754780000001</v>
       </c>
       <c r="N82">
-        <v>96.20982933333336</v>
+        <v>95.07578553333336</v>
       </c>
       <c r="O82">
-        <v>14.04663508266667</v>
+        <v>13.88106468786667</v>
       </c>
       <c r="P82">
-        <v>82.16319425066669</v>
+        <v>81.19472084546669</v>
       </c>
       <c r="Q82">
-        <v>191.0631942506667</v>
+        <v>190.0947208454667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2161195229970027</v>
+        <v>0.2247873381571524</v>
       </c>
       <c r="T82">
-        <v>3.933476281685973</v>
+        <v>4.133656770373034</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.060473031700069</v>
+        <v>2.035035093037105</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09514348624985895</v>
+        <v>0.09527650790031737</v>
       </c>
       <c r="C83">
-        <v>47.3067123031899</v>
+        <v>30.21872813416326</v>
       </c>
       <c r="D83">
-        <v>1129.14771230319</v>
+        <v>1127.020728134163</v>
       </c>
       <c r="E83">
-        <v>695.6409999999998</v>
+        <v>710.6019999999999</v>
       </c>
       <c r="F83">
-        <v>1211.841</v>
+        <v>1226.802</v>
       </c>
       <c r="G83">
         <v>130</v>
@@ -8075,28 +8075,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M83">
-        <v>91.85754780000001</v>
+        <v>92.99159160000001</v>
       </c>
       <c r="N83">
-        <v>95.07578553333336</v>
+        <v>93.94174173333336</v>
       </c>
       <c r="O83">
-        <v>13.88106468786667</v>
+        <v>13.71549429306667</v>
       </c>
       <c r="P83">
-        <v>81.19472084546669</v>
+        <v>80.22624744026669</v>
       </c>
       <c r="Q83">
-        <v>190.0947208454667</v>
+        <v>189.1262474402667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2247873381571524</v>
+        <v>0.2344182438906521</v>
       </c>
       <c r="T83">
-        <v>4.133656770373034</v>
+        <v>4.356079535580879</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.035035093037105</v>
+        <v>2.010217591902506</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09527650790031737</v>
+        <v>0.1054747735507758</v>
       </c>
       <c r="C84">
-        <v>30.21872813416326</v>
+        <v>-126.9637523449501</v>
       </c>
       <c r="D84">
-        <v>1127.020728134163</v>
+        <v>984.7992476550498</v>
       </c>
       <c r="E84">
-        <v>710.6019999999999</v>
+        <v>725.5629999999999</v>
       </c>
       <c r="F84">
-        <v>1226.802</v>
+        <v>1241.763</v>
       </c>
       <c r="G84">
         <v>130</v>
@@ -8157,45 +8157,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M84">
-        <v>92.99159160000001</v>
+        <v>111.75867</v>
       </c>
       <c r="N84">
-        <v>93.94174173333336</v>
+        <v>75.17466333333337</v>
       </c>
       <c r="O84">
-        <v>13.71549429306667</v>
+        <v>10.97550084666667</v>
       </c>
       <c r="P84">
-        <v>80.22624744026669</v>
+        <v>64.19916248666669</v>
       </c>
       <c r="Q84">
-        <v>189.1262474402667</v>
+        <v>173.0991624866667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2344182438906521</v>
+        <v>0.2451821973575047</v>
       </c>
       <c r="T84">
-        <v>4.356079535580879</v>
+        <v>4.604669684930824</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.146</v>
       </c>
       <c r="W84">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.010217591902506</v>
+        <v>1.67265173550592</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1054747735507758</v>
+        <v>0.1057290632012342</v>
       </c>
       <c r="C85">
-        <v>-126.9637523449501</v>
+        <v>-145.0137599455838</v>
       </c>
       <c r="D85">
-        <v>984.7992476550498</v>
+        <v>981.7102400544161</v>
       </c>
       <c r="E85">
-        <v>725.5629999999999</v>
+        <v>740.5239999999999</v>
       </c>
       <c r="F85">
-        <v>1241.763</v>
+        <v>1256.724</v>
       </c>
       <c r="G85">
         <v>130</v>
@@ -8239,28 +8239,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M85">
-        <v>111.75867</v>
+        <v>113.10516</v>
       </c>
       <c r="N85">
-        <v>75.17466333333337</v>
+        <v>73.82817333333338</v>
       </c>
       <c r="O85">
-        <v>10.97550084666667</v>
+        <v>10.77891330666667</v>
       </c>
       <c r="P85">
-        <v>64.19916248666669</v>
+        <v>63.04926002666671</v>
       </c>
       <c r="Q85">
-        <v>173.0991624866667</v>
+        <v>171.9492600266667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2451821973575047</v>
+        <v>0.2572916450077138</v>
       </c>
       <c r="T85">
-        <v>4.604669684930824</v>
+        <v>4.884333602949512</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.67265173550592</v>
+        <v>1.652739214845135</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1057290632012342</v>
+        <v>0.1059833528516926</v>
       </c>
       <c r="C86">
-        <v>-145.0137599455836</v>
+        <v>-163.0444496367149</v>
       </c>
       <c r="D86">
-        <v>981.7102400544162</v>
+        <v>978.6405503632849</v>
       </c>
       <c r="E86">
-        <v>740.5239999999999</v>
+        <v>755.4849999999999</v>
       </c>
       <c r="F86">
-        <v>1256.724</v>
+        <v>1271.685</v>
       </c>
       <c r="G86">
         <v>130</v>
@@ -8321,28 +8321,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M86">
-        <v>113.10516</v>
+        <v>114.45165</v>
       </c>
       <c r="N86">
-        <v>73.82817333333338</v>
+        <v>72.48168333333338</v>
       </c>
       <c r="O86">
-        <v>10.77891330666667</v>
+        <v>10.58232576666667</v>
       </c>
       <c r="P86">
-        <v>63.04926002666671</v>
+        <v>61.89935756666671</v>
       </c>
       <c r="Q86">
-        <v>171.9492600266667</v>
+        <v>170.7993575666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2572916450077137</v>
+        <v>0.2710156856779508</v>
       </c>
       <c r="T86">
-        <v>4.884333602949509</v>
+        <v>5.201286043370687</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.652739214845135</v>
+        <v>1.633295224082251</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1059833528516926</v>
+        <v>0.106237642502151</v>
       </c>
       <c r="C87">
-        <v>-163.0444496367149</v>
+        <v>-181.0560020678042</v>
       </c>
       <c r="D87">
-        <v>978.6405503632849</v>
+        <v>975.5899979321956</v>
       </c>
       <c r="E87">
-        <v>755.4849999999999</v>
+        <v>770.4459999999999</v>
       </c>
       <c r="F87">
-        <v>1271.685</v>
+        <v>1286.646</v>
       </c>
       <c r="G87">
         <v>130</v>
@@ -8403,28 +8403,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M87">
-        <v>114.45165</v>
+        <v>115.79814</v>
       </c>
       <c r="N87">
-        <v>72.48168333333338</v>
+        <v>71.13519333333338</v>
       </c>
       <c r="O87">
-        <v>10.58232576666667</v>
+        <v>10.38573822666667</v>
       </c>
       <c r="P87">
-        <v>61.89935756666671</v>
+        <v>60.7494551066667</v>
       </c>
       <c r="Q87">
-        <v>170.7993575666667</v>
+        <v>169.6494551066667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2710156856779508</v>
+        <v>0.2867003035867931</v>
       </c>
       <c r="T87">
-        <v>5.201286043370687</v>
+        <v>5.563517403852035</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.633295224082251</v>
+        <v>1.614303419151062</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.106237642502151</v>
+        <v>0.1064919321526095</v>
       </c>
       <c r="C88">
-        <v>-181.0560020678042</v>
+        <v>-199.0485956428784</v>
       </c>
       <c r="D88">
-        <v>975.5899979321956</v>
+        <v>972.5584043571217</v>
       </c>
       <c r="E88">
-        <v>770.4459999999999</v>
+        <v>785.4069999999999</v>
       </c>
       <c r="F88">
-        <v>1286.646</v>
+        <v>1301.607</v>
       </c>
       <c r="G88">
         <v>130</v>
@@ -8485,28 +8485,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M88">
-        <v>115.79814</v>
+        <v>117.14463</v>
       </c>
       <c r="N88">
-        <v>71.13519333333338</v>
+        <v>69.78870333333337</v>
       </c>
       <c r="O88">
-        <v>10.38573822666667</v>
+        <v>10.18915068666667</v>
       </c>
       <c r="P88">
-        <v>60.7494551066667</v>
+        <v>59.5995526466667</v>
       </c>
       <c r="Q88">
-        <v>169.6494551066667</v>
+        <v>168.4995526466667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2867003035867931</v>
+        <v>0.3047979396354574</v>
       </c>
       <c r="T88">
-        <v>5.563517403852035</v>
+        <v>5.981476665945897</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.614303419151062</v>
+        <v>1.595748207436682</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1064919321526095</v>
+        <v>0.1067462218030679</v>
       </c>
       <c r="C89">
-        <v>-199.0485956428784</v>
+        <v>-217.0224065553082</v>
       </c>
       <c r="D89">
-        <v>972.5584043571217</v>
+        <v>969.5455934446917</v>
       </c>
       <c r="E89">
-        <v>785.4069999999999</v>
+        <v>800.3679999999999</v>
       </c>
       <c r="F89">
-        <v>1301.607</v>
+        <v>1316.568</v>
       </c>
       <c r="G89">
         <v>130</v>
@@ -8567,28 +8567,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M89">
-        <v>117.14463</v>
+        <v>118.49112</v>
       </c>
       <c r="N89">
-        <v>69.78870333333337</v>
+        <v>68.44221333333337</v>
       </c>
       <c r="O89">
-        <v>10.18915068666667</v>
+        <v>9.992563146666672</v>
       </c>
       <c r="P89">
-        <v>59.5995526466667</v>
+        <v>58.4496501866667</v>
       </c>
       <c r="Q89">
-        <v>168.4995526466667</v>
+        <v>167.3496501866667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3047979396354574</v>
+        <v>0.325911848358899</v>
       </c>
       <c r="T89">
-        <v>5.981476665945897</v>
+        <v>6.469095805055404</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.595748207436682</v>
+        <v>1.577614705079447</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1067462218030679</v>
+        <v>0.1070005114535263</v>
       </c>
       <c r="C90">
-        <v>-217.0224065553082</v>
+        <v>-234.9776088219487</v>
       </c>
       <c r="D90">
-        <v>969.5455934446917</v>
+        <v>966.5513911780514</v>
       </c>
       <c r="E90">
-        <v>800.3679999999999</v>
+        <v>815.329</v>
       </c>
       <c r="F90">
-        <v>1316.568</v>
+        <v>1331.529</v>
       </c>
       <c r="G90">
         <v>130</v>
@@ -8649,28 +8649,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M90">
-        <v>118.49112</v>
+        <v>119.83761</v>
       </c>
       <c r="N90">
-        <v>68.44221333333337</v>
+        <v>67.09572333333337</v>
       </c>
       <c r="O90">
-        <v>9.992563146666672</v>
+        <v>9.795975606666671</v>
       </c>
       <c r="P90">
-        <v>58.4496501866667</v>
+        <v>57.29974772666669</v>
       </c>
       <c r="Q90">
-        <v>167.3496501866667</v>
+        <v>166.1997477266667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.325911848358899</v>
+        <v>0.3508646495775118</v>
       </c>
       <c r="T90">
-        <v>6.469095805055404</v>
+        <v>7.045372969457548</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.577614705079447</v>
+        <v>1.559888697157206</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1070005114535263</v>
+        <v>0.1072548011039847</v>
       </c>
       <c r="C91">
-        <v>-234.9776088219487</v>
+        <v>-252.9143743166371</v>
       </c>
       <c r="D91">
-        <v>966.5513911780514</v>
+        <v>963.5756256833628</v>
       </c>
       <c r="E91">
-        <v>815.329</v>
+        <v>830.29</v>
       </c>
       <c r="F91">
-        <v>1331.529</v>
+        <v>1346.49</v>
       </c>
       <c r="G91">
         <v>130</v>
@@ -8731,28 +8731,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M91">
-        <v>119.83761</v>
+        <v>121.1841</v>
       </c>
       <c r="N91">
-        <v>67.09572333333337</v>
+        <v>65.74923333333336</v>
       </c>
       <c r="O91">
-        <v>9.795975606666671</v>
+        <v>9.59938806666667</v>
       </c>
       <c r="P91">
-        <v>57.29974772666669</v>
+        <v>56.14984526666669</v>
       </c>
       <c r="Q91">
-        <v>166.1997477266667</v>
+        <v>165.0498452666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3508646495775118</v>
+        <v>0.3808080110398472</v>
       </c>
       <c r="T91">
-        <v>7.045372969457548</v>
+        <v>7.73690556674012</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.559888697157206</v>
+        <v>1.542556600522126</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1072548011039847</v>
+        <v>0.1075090907544431</v>
       </c>
       <c r="C92">
-        <v>-252.9143743166371</v>
+        <v>-270.832872803087</v>
       </c>
       <c r="D92">
-        <v>963.5756256833628</v>
+        <v>960.618127196913</v>
       </c>
       <c r="E92">
-        <v>830.29</v>
+        <v>845.251</v>
       </c>
       <c r="F92">
-        <v>1346.49</v>
+        <v>1361.451</v>
       </c>
       <c r="G92">
         <v>130</v>
@@ -8813,28 +8813,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M92">
-        <v>121.1841</v>
+        <v>122.53059</v>
       </c>
       <c r="N92">
-        <v>65.74923333333336</v>
+        <v>64.40274333333336</v>
       </c>
       <c r="O92">
-        <v>9.59938806666667</v>
+        <v>9.40280052666667</v>
       </c>
       <c r="P92">
-        <v>56.14984526666669</v>
+        <v>54.9999428066667</v>
       </c>
       <c r="Q92">
-        <v>165.0498452666667</v>
+        <v>163.8999428066667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3808080110398472</v>
+        <v>0.417405452827146</v>
       </c>
       <c r="T92">
-        <v>7.73690556674012</v>
+        <v>8.582112074529931</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.542556600522126</v>
+        <v>1.525605429087817</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1075090907544431</v>
+        <v>0.1077633804049015</v>
       </c>
       <c r="C93">
-        <v>-270.832872803087</v>
+        <v>-288.7332719671679</v>
       </c>
       <c r="D93">
-        <v>960.618127196913</v>
+        <v>957.6787280328322</v>
       </c>
       <c r="E93">
-        <v>845.251</v>
+        <v>860.212</v>
       </c>
       <c r="F93">
-        <v>1361.451</v>
+        <v>1376.412</v>
       </c>
       <c r="G93">
         <v>130</v>
@@ -8895,28 +8895,28 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M93">
-        <v>122.53059</v>
+        <v>123.87708</v>
       </c>
       <c r="N93">
-        <v>64.40274333333336</v>
+        <v>63.05625333333337</v>
       </c>
       <c r="O93">
-        <v>9.40280052666667</v>
+        <v>9.206212986666673</v>
       </c>
       <c r="P93">
-        <v>54.9999428066667</v>
+        <v>53.8500403466667</v>
       </c>
       <c r="Q93">
-        <v>163.8999428066667</v>
+        <v>162.7500403466667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.417405452827146</v>
+        <v>0.4631522550612696</v>
       </c>
       <c r="T93">
-        <v>8.582112074529931</v>
+        <v>9.638620209267195</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.525605429087817</v>
+        <v>1.509022761380341</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1077633804049015</v>
+        <v>0.1552636693695239</v>
       </c>
       <c r="C94">
-        <v>-288.7332719671679</v>
+        <v>-651.9989520454251</v>
       </c>
       <c r="D94">
-        <v>957.6787280328322</v>
+        <v>609.374047954575</v>
       </c>
       <c r="E94">
-        <v>860.212</v>
+        <v>875.173</v>
       </c>
       <c r="F94">
-        <v>1376.412</v>
+        <v>1391.373</v>
       </c>
       <c r="G94">
         <v>130</v>
@@ -8977,45 +8977,45 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M94">
-        <v>123.87708</v>
+        <v>204.2535564</v>
       </c>
       <c r="N94">
-        <v>63.05625333333337</v>
+        <v>-17.32022306666667</v>
       </c>
       <c r="O94">
-        <v>9.206212986666673</v>
+        <v>-2.528752567733334</v>
       </c>
       <c r="P94">
-        <v>53.8500403466667</v>
+        <v>-14.79147049893334</v>
       </c>
       <c r="Q94">
-        <v>162.7500403466667</v>
+        <v>94.10852950106667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4631522550612696</v>
+        <v>0.528313481818551</v>
       </c>
       <c r="T94">
-        <v>9.638620209267195</v>
+        <v>11.14349842537069</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.146</v>
+        <v>0.1336195420422392</v>
       </c>
       <c r="W94">
-        <v>0.07686</v>
+        <v>0.1271846512281993</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.509022761380341</v>
+        <v>0.9152023427550627</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1552636693695239</v>
+        <v>0.1562736693695239</v>
       </c>
       <c r="C95">
-        <v>-651.9989520454251</v>
+        <v>-671.6362582166355</v>
       </c>
       <c r="D95">
-        <v>609.374047954575</v>
+        <v>604.6977417833646</v>
       </c>
       <c r="E95">
-        <v>875.173</v>
+        <v>890.134</v>
       </c>
       <c r="F95">
-        <v>1391.373</v>
+        <v>1406.334</v>
       </c>
       <c r="G95">
         <v>130</v>
@@ -9059,37 +9059,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M95">
-        <v>204.2535564</v>
+        <v>206.4498312</v>
       </c>
       <c r="N95">
-        <v>-17.32022306666667</v>
+        <v>-19.51649786666667</v>
       </c>
       <c r="O95">
-        <v>-2.528752567733334</v>
+        <v>-2.849408688533333</v>
       </c>
       <c r="P95">
-        <v>-14.79147049893334</v>
+        <v>-16.66708917813333</v>
       </c>
       <c r="Q95">
-        <v>94.10852950106667</v>
+        <v>92.23291082186667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.528313481818551</v>
+        <v>0.6087323954549763</v>
       </c>
       <c r="T95">
-        <v>11.14349842537069</v>
+        <v>13.00074816293248</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1336195420422392</v>
+        <v>0.1321980575524281</v>
       </c>
       <c r="W95">
-        <v>0.1271846512281993</v>
+        <v>0.1273933251513036</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9152023427550627</v>
+        <v>0.9054661476193706</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1562736693695239</v>
+        <v>0.1572836693695239</v>
       </c>
       <c r="C96">
-        <v>-671.6362582166355</v>
+        <v>-691.2023394817448</v>
       </c>
       <c r="D96">
-        <v>604.6977417833646</v>
+        <v>600.0926605182552</v>
       </c>
       <c r="E96">
-        <v>890.134</v>
+        <v>905.095</v>
       </c>
       <c r="F96">
-        <v>1406.334</v>
+        <v>1421.295</v>
       </c>
       <c r="G96">
         <v>130</v>
@@ -9141,37 +9141,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M96">
-        <v>206.4498312</v>
+        <v>208.646106</v>
       </c>
       <c r="N96">
-        <v>-19.51649786666667</v>
+        <v>-21.71277266666667</v>
       </c>
       <c r="O96">
-        <v>-2.849408688533333</v>
+        <v>-3.170064809333333</v>
       </c>
       <c r="P96">
-        <v>-16.66708917813333</v>
+        <v>-18.54270785733333</v>
       </c>
       <c r="Q96">
-        <v>92.23291082186667</v>
+        <v>90.35729214266667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6087323954549763</v>
+        <v>0.7213188745459718</v>
       </c>
       <c r="T96">
-        <v>13.00074816293248</v>
+        <v>15.60089779551898</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1321980575524281</v>
+        <v>0.1308064990518762</v>
       </c>
       <c r="W96">
-        <v>0.1273933251513036</v>
+        <v>0.1275976059391846</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9054661476193706</v>
+        <v>0.8959349250128509</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1572836693695239</v>
+        <v>0.1582936693695239</v>
       </c>
       <c r="C97">
-        <v>-691.2023394817448</v>
+        <v>-710.6988107839394</v>
       </c>
       <c r="D97">
-        <v>600.0926605182552</v>
+        <v>595.5571892160607</v>
       </c>
       <c r="E97">
-        <v>905.095</v>
+        <v>920.056</v>
       </c>
       <c r="F97">
-        <v>1421.295</v>
+        <v>1436.256</v>
       </c>
       <c r="G97">
         <v>130</v>
@@ -9223,37 +9223,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M97">
-        <v>208.646106</v>
+        <v>210.8423808</v>
       </c>
       <c r="N97">
-        <v>-21.71277266666667</v>
+        <v>-23.90904746666666</v>
       </c>
       <c r="O97">
-        <v>-3.170064809333333</v>
+        <v>-3.490720930133333</v>
       </c>
       <c r="P97">
-        <v>-18.54270785733333</v>
+        <v>-20.41832653653333</v>
       </c>
       <c r="Q97">
-        <v>90.35729214266667</v>
+        <v>88.48167346346668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7213188745459718</v>
+        <v>0.8901985931824652</v>
       </c>
       <c r="T97">
-        <v>15.60089779551898</v>
+        <v>19.50112224439874</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1308064990518762</v>
+        <v>0.1294439313534192</v>
       </c>
       <c r="W97">
-        <v>0.1275976059391846</v>
+        <v>0.1277976308773181</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8959349250128509</v>
+        <v>0.886602269543967</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1582936693695239</v>
+        <v>0.1593036693695239</v>
       </c>
       <c r="C98">
-        <v>-710.6988107839388</v>
+        <v>-730.1272386099851</v>
       </c>
       <c r="D98">
-        <v>595.557189216061</v>
+        <v>591.0897613900148</v>
       </c>
       <c r="E98">
-        <v>920.0559999999998</v>
+        <v>935.0169999999998</v>
       </c>
       <c r="F98">
-        <v>1436.256</v>
+        <v>1451.217</v>
       </c>
       <c r="G98">
         <v>130</v>
@@ -9305,37 +9305,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M98">
-        <v>210.8423808</v>
+        <v>213.0386556</v>
       </c>
       <c r="N98">
-        <v>-23.90904746666664</v>
+        <v>-26.10532226666663</v>
       </c>
       <c r="O98">
-        <v>-3.490720930133329</v>
+        <v>-3.811377050933328</v>
       </c>
       <c r="P98">
-        <v>-20.41832653653331</v>
+        <v>-22.29394521573331</v>
       </c>
       <c r="Q98">
-        <v>88.48167346346671</v>
+        <v>86.6060547842667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8901985931824627</v>
+        <v>1.171664790909951</v>
       </c>
       <c r="T98">
-        <v>19.50112224439868</v>
+        <v>26.00149632586491</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1294439313534192</v>
+        <v>0.1281094578343118</v>
       </c>
       <c r="W98">
-        <v>0.1277976308773181</v>
+        <v>0.127993531589923</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8866022695439671</v>
+        <v>0.8774620399610397</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1593036693695239</v>
+        <v>0.1603136693695239</v>
       </c>
       <c r="C99">
-        <v>-730.1272386099851</v>
+        <v>-749.4891427941203</v>
       </c>
       <c r="D99">
-        <v>591.0897613900148</v>
+        <v>586.6888572058796</v>
       </c>
       <c r="E99">
-        <v>935.0169999999998</v>
+        <v>949.9779999999998</v>
       </c>
       <c r="F99">
-        <v>1451.217</v>
+        <v>1466.178</v>
       </c>
       <c r="G99">
         <v>130</v>
@@ -9387,37 +9387,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M99">
-        <v>213.0386556</v>
+        <v>215.2349304</v>
       </c>
       <c r="N99">
-        <v>-26.10532226666663</v>
+        <v>-28.30159706666663</v>
       </c>
       <c r="O99">
-        <v>-3.811377050933328</v>
+        <v>-4.132033171733328</v>
       </c>
       <c r="P99">
-        <v>-22.29394521573331</v>
+        <v>-24.1695638949333</v>
       </c>
       <c r="Q99">
-        <v>86.6060547842667</v>
+        <v>84.7304361050667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.171664790909951</v>
+        <v>1.734597186364926</v>
       </c>
       <c r="T99">
-        <v>26.00149632586491</v>
+        <v>39.00224448879736</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1281094578343118</v>
+        <v>0.1268022184686556</v>
       </c>
       <c r="W99">
-        <v>0.127993531589923</v>
+        <v>0.1281854343288014</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8774620399610397</v>
+        <v>0.868508345675723</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1603136693695239</v>
+        <v>0.1613236693695239</v>
       </c>
       <c r="C100">
-        <v>-749.4891427941203</v>
+        <v>-768.7859982419524</v>
       </c>
       <c r="D100">
-        <v>586.6888572058796</v>
+        <v>582.3530017580475</v>
       </c>
       <c r="E100">
-        <v>949.9779999999998</v>
+        <v>964.9389999999999</v>
       </c>
       <c r="F100">
-        <v>1466.178</v>
+        <v>1481.139</v>
       </c>
       <c r="G100">
         <v>130</v>
@@ -9469,37 +9469,37 @@
         <v>186.9333333333334</v>
       </c>
       <c r="M100">
-        <v>215.2349304</v>
+        <v>217.4312052</v>
       </c>
       <c r="N100">
-        <v>-28.30159706666663</v>
+        <v>-30.49787186666663</v>
       </c>
       <c r="O100">
-        <v>-4.132033171733328</v>
+        <v>-4.452689292533328</v>
       </c>
       <c r="P100">
-        <v>-24.1695638949333</v>
+        <v>-26.0451825741333</v>
       </c>
       <c r="Q100">
-        <v>84.7304361050667</v>
+        <v>82.85481742586671</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.734597186364926</v>
+        <v>3.423394372729851</v>
       </c>
       <c r="T100">
-        <v>39.00224448879736</v>
+        <v>78.00448897759472</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1268022184686556</v>
+        <v>0.1255213879790732</v>
       </c>
       <c r="W100">
-        <v>0.1281854343288014</v>
+        <v>0.1283734602446721</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.868508345675723</v>
+        <v>0.8597355341032409</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1613236693695239</v>
-      </c>
-      <c r="C101">
-        <v>-768.7859982419524</v>
-      </c>
-      <c r="D101">
-        <v>582.3530017580475</v>
-      </c>
-      <c r="E101">
-        <v>964.9389999999999</v>
-      </c>
-      <c r="F101">
-        <v>1481.139</v>
-      </c>
-      <c r="G101">
-        <v>130</v>
-      </c>
-      <c r="H101">
-        <v>979.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>295.8333333333334</v>
-      </c>
-      <c r="K101">
-        <v>108.9</v>
-      </c>
-      <c r="L101">
-        <v>186.9333333333334</v>
-      </c>
-      <c r="M101">
-        <v>217.4312052</v>
-      </c>
-      <c r="N101">
-        <v>-30.49787186666663</v>
-      </c>
-      <c r="O101">
-        <v>-4.452689292533328</v>
-      </c>
-      <c r="P101">
-        <v>-26.0451825741333</v>
-      </c>
-      <c r="Q101">
-        <v>82.85481742586671</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.423394372729851</v>
-      </c>
-      <c r="T101">
-        <v>78.00448897759472</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1255213879790732</v>
-      </c>
-      <c r="W101">
-        <v>0.1283734602446721</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8597355341032409</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
